--- a/documents/新需求/数值管理.xlsx
+++ b/documents/新需求/数值管理.xlsx
@@ -1,43 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5-workspace\code\CombatDebugStudio\documents\新需求\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4-softworkspace\java\CombatDebugStudio\documents\新需求\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED608F39-A368-451C-B82A-C0F3DCE5378D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="17055" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="装备" sheetId="2" r:id="rId2"/>
-    <sheet name="流派" sheetId="3" r:id="rId3"/>
-    <sheet name="宠物与坐骑" sheetId="4" r:id="rId4"/>
-    <sheet name="天赋系统" sheetId="5" r:id="rId5"/>
-    <sheet name="属性来源预算比例" sheetId="6" r:id="rId6"/>
+    <sheet name="属性" sheetId="7" r:id="rId2"/>
+    <sheet name="装备" sheetId="2" r:id="rId3"/>
+    <sheet name="流派" sheetId="3" r:id="rId4"/>
+    <sheet name="宠物与坐骑" sheetId="4" r:id="rId5"/>
+    <sheet name="天赋系统" sheetId="5" r:id="rId6"/>
+    <sheet name="属性来源预算比例" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="353">
   <si>
     <t>B类属性</t>
   </si>
@@ -799,19 +788,391 @@
   </si>
   <si>
     <t>天赋不建议大量给速度，否则终极天赋会变成速度竞赛。</t>
+  </si>
+  <si>
+    <t>基础属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输出属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">真实伤害率 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对抗属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击抵抗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴伤减免</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>生存属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>五行属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>机制属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">控制成功率 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>五行攻击%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>免伤率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害反弹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制豁免</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>统一属性价值模型 = 基础价值 + 期望收益 + 条件覆盖率 + 乘区位置 + 边际衰减</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾削减</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害反弹削减</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血效果削减</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗强度削减</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>破甲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>易伤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1标准属性点</t>
+  </si>
+  <si>
+    <t>=</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>12气血</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2攻击</t>
+  </si>
+  <si>
+    <t>2防御</t>
+  </si>
+  <si>
+    <t>2命中</t>
+  </si>
+  <si>
+    <t>2闪避</t>
+  </si>
+  <si>
+    <t>2速度</t>
+  </si>
+  <si>
+    <t>第四层</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三层</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二层</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>层级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一层</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础数值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>独立乘区</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终乘区</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BASE+ADDITIVE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PERCENTAGE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MULTIPLICATIVE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FINAL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>+100攻击</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>+10%攻击系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>+10%最终攻击力</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>气血系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>气血  攻击  防御  命中  闪避  速度</t>
+  </si>
+  <si>
+    <t>防御系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果命中</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果抵抗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害加成</t>
+  </si>
+  <si>
+    <t>伤害加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>免伤系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>五行抗性%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻伤害减免%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害减免%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>气血加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>+10%攻击加成</t>
+  </si>
+  <si>
+    <t>防御加成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">命中加成 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">闪避加成 </t>
+  </si>
+  <si>
+    <t>速度加成</t>
+  </si>
+  <si>
+    <t>气血回复(%)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>气血回复(固定)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真伤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾加成</t>
+  </si>
+  <si>
+    <t>伤害反弹加成</t>
+  </si>
+  <si>
+    <t>吸血效果加成</t>
+  </si>
+  <si>
+    <t>治疗强度加成</t>
+  </si>
+  <si>
+    <t>真伤加成</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -829,7 +1190,7 @@
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -840,345 +1201,35 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FFF2858C"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1186,255 +1237,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1450,93 +1259,177 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1547,7 +1440,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1575,154 +1468,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1972,32 +1751,32 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D16:Z63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="31.125" customWidth="1"/>
-    <col min="10" max="13" width="16.625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" customWidth="1"/>
+    <col min="10" max="13" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="4:4">
+    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D16" s="3"/>
     </row>
-    <row r="31" spans="8:26">
-      <c r="H31" s="2" t="s">
+    <row r="31" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H31" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
       <c r="S31" t="s">
         <v>1</v>
       </c>
@@ -2023,7 +1802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="8:26">
+    <row r="32" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H32" s="4" t="s">
         <v>9</v>
       </c>
@@ -2036,7 +1815,7 @@
       <c r="K32" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L32" s="5"/>
+      <c r="L32" s="4"/>
       <c r="S32" t="s">
         <v>13</v>
       </c>
@@ -2062,7 +1841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="8:26">
+    <row r="33" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
         <v>16</v>
       </c>
@@ -2100,7 +1879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="8:26">
+    <row r="34" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
         <v>22</v>
       </c>
@@ -2138,7 +1917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="8:26">
+    <row r="35" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H35" t="s">
         <v>26</v>
       </c>
@@ -2176,7 +1955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="8:26">
+    <row r="36" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H36" t="s">
         <v>31</v>
       </c>
@@ -2214,7 +1993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="8:26">
+    <row r="37" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H37" t="s">
         <v>36</v>
       </c>
@@ -2252,17 +2031,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="8:26">
-      <c r="H39" s="2" t="s">
+    <row r="39" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="8:26">
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+    </row>
+    <row r="40" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H40" s="4" t="s">
         <v>9</v>
       </c>
@@ -2275,9 +2054,9 @@
       <c r="K40" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="5"/>
-    </row>
-    <row r="41" spans="8:26">
+      <c r="L40" s="4"/>
+    </row>
+    <row r="41" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H41" t="s">
         <v>41</v>
       </c>
@@ -2291,7 +2070,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="8:26">
+    <row r="42" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H42" t="s">
         <v>45</v>
       </c>
@@ -2305,7 +2084,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="8:26">
+    <row r="43" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H43" t="s">
         <v>47</v>
       </c>
@@ -2319,7 +2098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="8:26">
+    <row r="44" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H44" t="s">
         <v>51</v>
       </c>
@@ -2333,7 +2112,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="8:26">
+    <row r="45" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H45" t="s">
         <v>54</v>
       </c>
@@ -2347,17 +2126,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="8:26">
-      <c r="H47" s="2" t="s">
+    <row r="47" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H47" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="8:26">
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+    </row>
+    <row r="48" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H48" s="4" t="s">
         <v>9</v>
       </c>
@@ -2370,9 +2149,9 @@
       <c r="K48" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="8:13">
+      <c r="L48" s="4"/>
+    </row>
+    <row r="49" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H49" t="s">
         <v>59</v>
       </c>
@@ -2386,7 +2165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="8:13">
+    <row r="50" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H50" t="s">
         <v>62</v>
       </c>
@@ -2400,7 +2179,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="8:13">
+    <row r="51" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H51" t="s">
         <v>66</v>
       </c>
@@ -2414,7 +2193,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="8:13">
+    <row r="52" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H52" t="s">
         <v>67</v>
       </c>
@@ -2428,17 +2207,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="8:13">
-      <c r="H54" s="2" t="s">
+    <row r="54" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H54" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-    </row>
-    <row r="55" spans="8:13">
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+    </row>
+    <row r="55" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H55" s="4" t="s">
         <v>9</v>
       </c>
@@ -2451,9 +2230,9 @@
       <c r="K55" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="8:13">
+      <c r="L55" s="4"/>
+    </row>
+    <row r="56" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H56" t="s">
         <v>69</v>
       </c>
@@ -2467,7 +2246,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="8:13">
+    <row r="57" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H57" t="s">
         <v>72</v>
       </c>
@@ -2481,17 +2260,17 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="8:13">
-      <c r="H59" s="2" t="s">
+    <row r="59" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H59" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="8:13">
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+    </row>
+    <row r="60" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H60" s="4" t="s">
         <v>9</v>
       </c>
@@ -2505,7 +2284,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="8:13">
+    <row r="61" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H61" t="s">
         <v>77</v>
       </c>
@@ -2519,7 +2298,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="8:13">
+    <row r="62" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H62" t="s">
         <v>79</v>
       </c>
@@ -2533,7 +2312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="8:13">
+    <row r="63" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H63" t="s">
         <v>82</v>
       </c>
@@ -2555,262 +2334,765 @@
     <mergeCell ref="H54:M54"/>
     <mergeCell ref="H59:M59"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="O20:O25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7D3264-5272-4993-B0B0-C05DC6415756}">
+  <dimension ref="A1:J53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" style="2" customWidth="1"/>
+    <col min="3" max="10" width="13.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="20" spans="15:15">
-      <c r="O20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="15:15">
-      <c r="O21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="15:15">
-      <c r="O22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="15:15">
-      <c r="O23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="15:15">
-      <c r="O24" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="15:15">
-      <c r="O25" t="s">
-        <v>89</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1"/>
+      <c r="D1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2"/>
+      <c r="D2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3"/>
+      <c r="D3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4"/>
+      <c r="D4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5"/>
+      <c r="D5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8"/>
+      <c r="C8" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9"/>
+      <c r="C9" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11"/>
+      <c r="C11" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22"/>
+      <c r="C22" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23"/>
+      <c r="C23" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B26"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B27"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B29"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B30"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31"/>
+      <c r="C31" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C33" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C34" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C36" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C37" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <mergeCells count="1">
+    <mergeCell ref="A28:H28"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="K19:N46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="11" max="16" width="20.625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="O20:O25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="19" spans="11:14">
-      <c r="K19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="11:14">
-      <c r="K21" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" t="s">
-        <v>92</v>
-      </c>
-      <c r="M21" t="s">
-        <v>93</v>
-      </c>
-      <c r="N21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="11:14">
-      <c r="K22" t="s">
-        <v>95</v>
-      </c>
-      <c r="L22" t="s">
-        <v>96</v>
-      </c>
-      <c r="M22" t="s">
-        <v>97</v>
-      </c>
-      <c r="N22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="11:14">
-      <c r="K23" t="s">
-        <v>99</v>
-      </c>
-      <c r="L23" t="s">
-        <v>100</v>
-      </c>
-      <c r="M23" t="s">
-        <v>101</v>
-      </c>
-      <c r="N23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="11:14">
-      <c r="K24" t="s">
-        <v>103</v>
-      </c>
-      <c r="L24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M24" t="s">
-        <v>105</v>
-      </c>
-      <c r="N24" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="11:14">
-      <c r="K25" t="s">
-        <v>107</v>
-      </c>
-      <c r="L25" t="s">
-        <v>108</v>
-      </c>
-      <c r="M25" t="s">
-        <v>109</v>
-      </c>
-      <c r="N25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="11:14">
-      <c r="K26" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" t="s">
-        <v>112</v>
-      </c>
-      <c r="M26" t="s">
-        <v>113</v>
-      </c>
-      <c r="N26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="11:12">
-      <c r="K33" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="11:12">
-      <c r="K35" t="s">
-        <v>116</v>
-      </c>
-      <c r="L35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="11:12">
-      <c r="K36" t="s">
-        <v>118</v>
-      </c>
-      <c r="L36" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="11:12">
-      <c r="K37" t="s">
-        <v>120</v>
-      </c>
-      <c r="L37" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="11:12">
-      <c r="K38" t="s">
-        <v>122</v>
-      </c>
-      <c r="L38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="11:12">
-      <c r="K39" t="s">
-        <v>124</v>
-      </c>
-      <c r="L39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="11:12">
-      <c r="K40" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" spans="11:12">
-      <c r="K41" t="s">
-        <v>91</v>
-      </c>
-      <c r="L41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="11:12">
-      <c r="K42" t="s">
-        <v>95</v>
-      </c>
-      <c r="L42" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="11:12">
-      <c r="K43" t="s">
-        <v>99</v>
-      </c>
-      <c r="L43" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="11:12">
-      <c r="K44" t="s">
-        <v>103</v>
-      </c>
-      <c r="L44" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="11:12">
-      <c r="K45" t="s">
-        <v>107</v>
-      </c>
-      <c r="L45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="11:12">
-      <c r="K46" t="s">
-        <v>111</v>
-      </c>
-      <c r="L46" t="s">
-        <v>132</v>
+    <row r="20" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O25" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="K19:N46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="16" width="20.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="19" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
+        <v>91</v>
+      </c>
+      <c r="L21" t="s">
+        <v>92</v>
+      </c>
+      <c r="M21" t="s">
+        <v>93</v>
+      </c>
+      <c r="N21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22" t="s">
+        <v>96</v>
+      </c>
+      <c r="M22" t="s">
+        <v>97</v>
+      </c>
+      <c r="N22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K23" t="s">
+        <v>99</v>
+      </c>
+      <c r="L23" t="s">
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>101</v>
+      </c>
+      <c r="N23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K24" t="s">
+        <v>103</v>
+      </c>
+      <c r="L24" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" t="s">
+        <v>105</v>
+      </c>
+      <c r="N24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K25" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25" t="s">
+        <v>108</v>
+      </c>
+      <c r="M25" t="s">
+        <v>109</v>
+      </c>
+      <c r="N25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>111</v>
+      </c>
+      <c r="L26" t="s">
+        <v>112</v>
+      </c>
+      <c r="M26" t="s">
+        <v>113</v>
+      </c>
+      <c r="N26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K35" t="s">
+        <v>116</v>
+      </c>
+      <c r="L35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>118</v>
+      </c>
+      <c r="L36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>120</v>
+      </c>
+      <c r="L37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>122</v>
+      </c>
+      <c r="L38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>124</v>
+      </c>
+      <c r="L39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>91</v>
+      </c>
+      <c r="L41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K42" t="s">
+        <v>95</v>
+      </c>
+      <c r="L42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K43" t="s">
+        <v>99</v>
+      </c>
+      <c r="L43" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>103</v>
+      </c>
+      <c r="L44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
+        <v>107</v>
+      </c>
+      <c r="L45" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="11:12" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
+        <v>111</v>
+      </c>
+      <c r="L46" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="I11:S40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="11" spans="9:19">
+    <row r="11" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I11" t="s">
         <v>133</v>
       </c>
@@ -2820,12 +3102,11 @@
       <c r="Q11" t="s">
         <v>135</v>
       </c>
-      <c r="R11"/>
       <c r="S11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="9:19">
+    <row r="13" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>137</v>
       </c>
@@ -2845,7 +3126,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="9:19">
+    <row r="14" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>141</v>
       </c>
@@ -2865,7 +3146,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="9:19">
+    <row r="15" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>69</v>
       </c>
@@ -2885,7 +3166,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="9:19">
+    <row r="16" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
         <v>82</v>
       </c>
@@ -2905,7 +3186,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="9:19">
+    <row r="17" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I17" t="s">
         <v>150</v>
       </c>
@@ -2925,7 +3206,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="9:19">
+    <row r="18" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>153</v>
       </c>
@@ -2945,7 +3226,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="9:19">
+    <row r="19" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>26</v>
       </c>
@@ -2965,7 +3246,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="9:19">
+    <row r="20" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>158</v>
       </c>
@@ -2985,7 +3266,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="9:19">
+    <row r="21" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>161</v>
       </c>
@@ -3005,7 +3286,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="9:19">
+    <row r="22" spans="9:19" x14ac:dyDescent="0.25">
       <c r="Q22" t="s">
         <v>26</v>
       </c>
@@ -3016,7 +3297,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="9:19">
+    <row r="23" spans="9:19" x14ac:dyDescent="0.25">
       <c r="Q23" t="s">
         <v>69</v>
       </c>
@@ -3027,7 +3308,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="9:19">
+    <row r="25" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I25" t="s">
         <v>30</v>
       </c>
@@ -3041,7 +3322,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="9:19">
+    <row r="26" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
         <v>169</v>
       </c>
@@ -3055,7 +3336,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27" spans="9:19">
+    <row r="27" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>173</v>
       </c>
@@ -3069,7 +3350,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="28" spans="9:19">
+    <row r="28" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I28" t="s">
         <v>177</v>
       </c>
@@ -3083,7 +3364,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="9:19">
+    <row r="29" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I29" t="s">
         <v>181</v>
       </c>
@@ -3097,7 +3378,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="9:19">
+    <row r="30" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I30" t="s">
         <v>185</v>
       </c>
@@ -3105,25 +3386,25 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="9:13">
+    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I35" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="9:13">
+    <row r="36" spans="9:13" ht="15.6" x14ac:dyDescent="0.25">
       <c r="I36" s="1" t="s">
         <v>188</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="9:13">
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+    </row>
+    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I37" t="s">
         <v>190</v>
       </c>
@@ -3131,7 +3412,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="9:13">
+    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I38" t="s">
         <v>191</v>
       </c>
@@ -3139,7 +3420,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="9:13">
+    <row r="39" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I39" t="s">
         <v>192</v>
       </c>
@@ -3147,7 +3428,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="9:13">
+    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I40" t="s">
         <v>193</v>
       </c>
@@ -3159,156 +3440,151 @@
   <mergeCells count="1">
     <mergeCell ref="K36:M36"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="H8:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="8" spans="8:16">
-      <c r="O8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" spans="8:16">
-      <c r="H10" t="s">
-        <v>195</v>
-      </c>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="O10" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" spans="8:16">
-      <c r="O11" t="s">
-        <v>197</v>
-      </c>
-      <c r="P11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="8:16">
-      <c r="H12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J12" t="s">
-        <v>199</v>
-      </c>
-      <c r="K12" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" t="s">
-        <v>200</v>
-      </c>
-      <c r="P12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="8:16">
-      <c r="H13" t="s">
-        <v>200</v>
-      </c>
-      <c r="I13" t="s">
-        <v>202</v>
-      </c>
-      <c r="J13" t="s">
-        <v>203</v>
-      </c>
-      <c r="K13" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" t="s">
-        <v>205</v>
-      </c>
-      <c r="P13" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" spans="8:16">
-      <c r="H14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I14" t="s">
-        <v>207</v>
-      </c>
-      <c r="J14" t="s">
-        <v>208</v>
-      </c>
-      <c r="K14" t="s">
-        <v>209</v>
-      </c>
-      <c r="O14" t="s">
-        <v>210</v>
-      </c>
-      <c r="P14" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="15" spans="8:16">
-      <c r="H15" t="s">
-        <v>210</v>
-      </c>
-      <c r="I15" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" t="s">
-        <v>213</v>
-      </c>
-      <c r="O15" t="s">
-        <v>214</v>
-      </c>
-      <c r="P15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" spans="8:16">
-      <c r="H16" t="s">
-        <v>214</v>
-      </c>
-      <c r="I16" t="s">
-        <v>216</v>
-      </c>
-      <c r="J16" t="s">
-        <v>217</v>
-      </c>
-      <c r="K16" t="s">
-        <v>218</v>
-      </c>
-      <c r="O16" t="s">
-        <v>219</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="H8:P16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="8" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="O8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>195</v>
+      </c>
+      <c r="O10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="O11" t="s">
+        <v>197</v>
+      </c>
+      <c r="P11" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>197</v>
+      </c>
+      <c r="I12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" t="s">
+        <v>199</v>
+      </c>
+      <c r="K12" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" t="s">
+        <v>200</v>
+      </c>
+      <c r="P12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" t="s">
+        <v>202</v>
+      </c>
+      <c r="J13" t="s">
+        <v>203</v>
+      </c>
+      <c r="K13" t="s">
+        <v>204</v>
+      </c>
+      <c r="O13" t="s">
+        <v>205</v>
+      </c>
+      <c r="P13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>205</v>
+      </c>
+      <c r="I14" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" t="s">
+        <v>208</v>
+      </c>
+      <c r="K14" t="s">
+        <v>209</v>
+      </c>
+      <c r="O14" t="s">
+        <v>210</v>
+      </c>
+      <c r="P14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>210</v>
+      </c>
+      <c r="I15" t="s">
+        <v>212</v>
+      </c>
+      <c r="J15" t="s">
+        <v>111</v>
+      </c>
+      <c r="K15" t="s">
+        <v>213</v>
+      </c>
+      <c r="O15" t="s">
+        <v>214</v>
+      </c>
+      <c r="P15" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="8:16" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>214</v>
+      </c>
+      <c r="I16" t="s">
+        <v>216</v>
+      </c>
+      <c r="J16" t="s">
+        <v>217</v>
+      </c>
+      <c r="K16" t="s">
+        <v>218</v>
+      </c>
+      <c r="O16" t="s">
+        <v>219</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="J5:L53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="10:11">
+    <row r="5" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="10:11">
+    <row r="6" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>221</v>
       </c>
@@ -3316,7 +3592,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="7" spans="10:11">
+    <row r="7" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>10</v>
       </c>
@@ -3324,7 +3600,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="10:11">
+    <row r="8" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J8" t="s">
         <v>11</v>
       </c>
@@ -3332,7 +3608,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="10:11">
+    <row r="9" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
         <v>225</v>
       </c>
@@ -3340,17 +3616,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="10:12">
+    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J17" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="10:12">
+    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="10:12">
+    <row r="20" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>228</v>
       </c>
@@ -3361,7 +3637,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="10:12">
+    <row r="21" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J21" t="s">
         <v>84</v>
       </c>
@@ -3372,7 +3648,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="22" spans="10:12">
+    <row r="22" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
         <v>231</v>
       </c>
@@ -3383,7 +3659,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="23" spans="10:12">
+    <row r="23" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
         <v>232</v>
       </c>
@@ -3394,7 +3670,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="10:12">
+    <row r="24" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
         <v>233</v>
       </c>
@@ -3405,7 +3681,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="25" spans="10:12">
+    <row r="25" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J25" t="s">
         <v>234</v>
       </c>
@@ -3416,22 +3692,22 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="26" spans="10:12">
+    <row r="26" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J26" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="10:12">
+    <row r="29" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J29" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="10:12">
+    <row r="31" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="10:12">
+    <row r="32" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
         <v>228</v>
       </c>
@@ -3442,7 +3718,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="33" spans="10:12">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J33" t="s">
         <v>238</v>
       </c>
@@ -3453,7 +3729,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="10:12">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J34" t="s">
         <v>56</v>
       </c>
@@ -3464,7 +3740,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="10:12">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J35" t="s">
         <v>52</v>
       </c>
@@ -3475,7 +3751,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="10:12">
+    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J36" t="s">
         <v>239</v>
       </c>
@@ -3486,7 +3762,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="37" spans="10:12">
+    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J37" t="s">
         <v>234</v>
       </c>
@@ -3497,27 +3773,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="10:12">
+    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J38" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="10:12">
+    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J41" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="43" spans="10:12">
+    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J43" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="44" spans="10:12">
+    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J44" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="46" spans="10:12">
+    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J46" t="s">
         <v>228</v>
       </c>
@@ -3528,7 +3804,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="47" spans="10:12">
+    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J47" t="s">
         <v>244</v>
       </c>
@@ -3539,7 +3815,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="48" spans="10:12">
+    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J48" t="s">
         <v>246</v>
       </c>
@@ -3550,7 +3826,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="49" spans="10:12">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J49" t="s">
         <v>248</v>
       </c>
@@ -3561,7 +3837,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="50" spans="10:12">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J50" t="s">
         <v>35</v>
       </c>
@@ -3572,7 +3848,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="10:12">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J51" t="s">
         <v>25</v>
       </c>
@@ -3583,7 +3859,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="52" spans="10:12">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J52" t="s">
         <v>39</v>
       </c>
@@ -3594,13 +3870,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="53" spans="10:12">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J53" t="s">
         <v>253</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/documents/新需求/数值管理.xlsx
+++ b/documents/新需求/数值管理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4-softworkspace\java\CombatDebugStudio\documents\新需求\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED608F39-A368-451C-B82A-C0F3DCE5378D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EC3FC2-7F0F-42A1-8C32-01459B46D108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4176" yWindow="2160" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="386">
   <si>
     <t>B类属性</t>
   </si>
@@ -790,10 +790,6 @@
     <t>天赋不建议大量给速度，否则终极天赋会变成速度竞赛。</t>
   </si>
   <si>
-    <t>基础属性</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -814,10 +810,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>输出属性</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>暴击率</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -830,14 +822,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">真实伤害率 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对抗属性</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>A</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -866,26 +850,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>生存属性</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>D</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>五行属性</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>E</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>机制属性</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>F</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -898,10 +870,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">控制成功率 </t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>五行攻击%</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1060,9 +1028,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>气血  攻击  防御  命中  闪避  速度</t>
-  </si>
-  <si>
     <t>防御系数</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1092,9 +1057,6 @@
   </si>
   <si>
     <t>伤害加成</t>
-  </si>
-  <si>
-    <t>伤害加成</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1145,10 +1107,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>真伤</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>普攻加成</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1162,10 +1120,187 @@
     <t>吸血效果加成</t>
   </si>
   <si>
+    <t>投放</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10%-25%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>将一部分伤害转化为真实伤害。不允许超过100%，普通伤害基数 = 伤害基数 × (1 - 真实伤害率%)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>来源: 武器、戒指、护符</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>同一装备最多出现1条真实伤害率词条。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>流派投放15%</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>天赋投放10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件型真伤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真伤率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真伤系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真伤附加值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真伤追加值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>真伤抗性</t>
+  </si>
+  <si>
+    <t>真伤抗性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻抵抗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始能量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量获取效率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能抵抗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击伤害加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击伤害系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>气血</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终攻击</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终防御</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>L4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输出</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击伤害系数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终伤害提升</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>生存</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终伤害减免</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对抗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗削减</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>五行</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>机制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘲讽</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>溅射</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>治疗强度加成</t>
-  </si>
-  <si>
-    <t>真伤加成</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1243,7 +1378,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1259,14 +1394,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,6 +1405,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1769,14 +1913,14 @@
       <c r="D16" s="3"/>
     </row>
     <row r="31" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
       <c r="S31" t="s">
         <v>1</v>
       </c>
@@ -2032,14 +2176,14 @@
       </c>
     </row>
     <row r="39" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
     </row>
     <row r="40" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H40" s="4" t="s">
@@ -2127,14 +2271,14 @@
       </c>
     </row>
     <row r="47" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
     </row>
     <row r="48" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H48" s="4" t="s">
@@ -2208,14 +2352,14 @@
       </c>
     </row>
     <row r="54" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H54" s="5" t="s">
+      <c r="H54" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
     </row>
     <row r="55" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H55" s="4" t="s">
@@ -2261,14 +2405,14 @@
       </c>
     </row>
     <row r="59" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H59" s="5" t="s">
+      <c r="H59" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="5"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
     </row>
     <row r="60" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H60" s="4" t="s">
@@ -2341,503 +2485,763 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7D3264-5272-4993-B0B0-C05DC6415756}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" style="2" customWidth="1"/>
-    <col min="3" max="10" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="3" width="8.77734375" style="2" customWidth="1"/>
+    <col min="4" max="11" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B1"/>
-      <c r="D1" t="s">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H2" s="8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H3" s="8" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H4" s="8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E8" t="s">
+        <v>254</v>
+      </c>
+      <c r="F8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" t="s">
+        <v>256</v>
+      </c>
+      <c r="H8" t="s">
+        <v>257</v>
+      </c>
+      <c r="I8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="10"/>
+      <c r="C9" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="10"/>
+      <c r="C10" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2"/>
-      <c r="D2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="I10" s="5" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3"/>
-      <c r="D3" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4"/>
-      <c r="D4" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5"/>
-      <c r="D5" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="G5" s="10" t="s">
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="10"/>
+      <c r="C11" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="10"/>
+      <c r="C15" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="10"/>
+      <c r="C16" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="10"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="10"/>
+      <c r="C21" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="10"/>
+      <c r="C22" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="I25" t="s">
+        <v>354</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="M25" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" t="s">
-        <v>255</v>
-      </c>
-      <c r="E7" t="s">
-        <v>256</v>
-      </c>
-      <c r="F7" t="s">
-        <v>257</v>
-      </c>
-      <c r="G7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8"/>
-      <c r="C8" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9"/>
-      <c r="C9" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E9" s="6" t="s">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11"/>
-      <c r="C11" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B14" t="s">
-        <v>267</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>265</v>
-      </c>
-      <c r="B15" t="s">
-        <v>268</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" t="s">
-        <v>274</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" t="s">
-        <v>274</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>275</v>
-      </c>
-      <c r="B18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>277</v>
-      </c>
-      <c r="B19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B21"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B22"/>
-      <c r="C22" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23"/>
-      <c r="C23" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31"/>
-      <c r="C31" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C32" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C34" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C35" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C36" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C37" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>336</v>
+      <c r="D30" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C35" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D40" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60"/>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61"/>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="5"/>
+      <c r="D62" s="2"/>
+      <c r="E62" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="5"/>
+      <c r="C63" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64"/>
+      <c r="C64" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B65"/>
+      <c r="C65" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="E65" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B66"/>
+      <c r="C66" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="E66" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B67"/>
+      <c r="C67" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B68"/>
+      <c r="C68" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K69" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="P69" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q69" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="R69" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D72" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C76" s="6"/>
+      <c r="D76" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C77" s="6"/>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C78" s="6"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A28:H28"/>
+  <mergeCells count="5">
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="E76:J76"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B20:B22"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3398,11 +3802,11 @@
       <c r="J36">
         <v>10</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
     </row>
     <row r="37" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I37" t="s">

--- a/documents/新需求/数值管理.xlsx
+++ b/documents/新需求/数值管理.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5-workspace\code\CombatDebugStudio\documents\新需求\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4-softworkspace\java\CombatDebugStudio\documents\新需求\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA599F-D522-4571-854F-A712F71E374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,24 +24,11 @@
     <sheet name="神器与法宝" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="538">
   <si>
     <t>B类属性</t>
   </si>
@@ -1659,15 +1647,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1685,13 +1669,13 @@
       <sz val="10"/>
       <color rgb="FFF2858C"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1702,345 +1686,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2048,255 +1708,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2309,15 +1727,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2325,18 +1734,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2345,93 +1748,165 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2442,7 +1917,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2470,154 +1945,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2867,32 +2228,32 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D16:Z63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="16.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="31.1083333333333" customWidth="1"/>
-    <col min="10" max="13" width="16.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" customWidth="1"/>
+    <col min="10" max="13" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="4:4">
-      <c r="D16" s="14"/>
-    </row>
-    <row r="31" spans="8:26">
-      <c r="H31" s="2" t="s">
+    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="9"/>
+    </row>
+    <row r="31" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H31" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
       <c r="S31" t="s">
         <v>1</v>
       </c>
@@ -2918,20 +2279,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="8:26">
-      <c r="H32" s="15" t="s">
+    <row r="32" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L32" s="15"/>
+      <c r="L32" s="10"/>
       <c r="S32" t="s">
         <v>13</v>
       </c>
@@ -2957,7 +2318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="8:26">
+    <row r="33" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
         <v>16</v>
       </c>
@@ -2995,7 +2356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="8:26">
+    <row r="34" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
         <v>22</v>
       </c>
@@ -3033,7 +2394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="8:26">
+    <row r="35" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H35" t="s">
         <v>26</v>
       </c>
@@ -3071,7 +2432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="8:26">
+    <row r="36" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H36" t="s">
         <v>31</v>
       </c>
@@ -3109,7 +2470,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="8:26">
+    <row r="37" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H37" t="s">
         <v>36</v>
       </c>
@@ -3147,32 +2508,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="8:26">
-      <c r="H39" s="2" t="s">
+    <row r="39" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H39" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="8:26">
-      <c r="H40" s="15" t="s">
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+    </row>
+    <row r="40" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H40" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J40" s="15" t="s">
+      <c r="J40" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K40" s="15" t="s">
+      <c r="K40" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="15"/>
-    </row>
-    <row r="41" spans="8:26">
+      <c r="L40" s="10"/>
+    </row>
+    <row r="41" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H41" t="s">
         <v>41</v>
       </c>
@@ -3186,7 +2547,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="8:26">
+    <row r="42" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H42" t="s">
         <v>45</v>
       </c>
@@ -3200,7 +2561,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="8:26">
+    <row r="43" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H43" t="s">
         <v>47</v>
       </c>
@@ -3214,7 +2575,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="8:26">
+    <row r="44" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H44" t="s">
         <v>51</v>
       </c>
@@ -3228,7 +2589,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="8:26">
+    <row r="45" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H45" t="s">
         <v>54</v>
       </c>
@@ -3242,32 +2603,32 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="8:26">
-      <c r="H47" s="2" t="s">
+    <row r="47" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H47" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="8:26">
-      <c r="H48" s="15" t="s">
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+    </row>
+    <row r="48" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H48" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J48" s="15" t="s">
+      <c r="J48" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K48" s="15" t="s">
+      <c r="K48" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L48" s="15"/>
-    </row>
-    <row r="49" spans="8:13">
+      <c r="L48" s="10"/>
+    </row>
+    <row r="49" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H49" t="s">
         <v>59</v>
       </c>
@@ -3281,7 +2642,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="8:13">
+    <row r="50" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H50" t="s">
         <v>62</v>
       </c>
@@ -3295,7 +2656,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="8:13">
+    <row r="51" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H51" t="s">
         <v>66</v>
       </c>
@@ -3309,7 +2670,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="8:13">
+    <row r="52" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H52" t="s">
         <v>67</v>
       </c>
@@ -3323,32 +2684,32 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="8:13">
-      <c r="H54" s="2" t="s">
+    <row r="54" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H54" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-    </row>
-    <row r="55" spans="8:13">
-      <c r="H55" s="15" t="s">
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+    </row>
+    <row r="55" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H55" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I55" s="15" t="s">
+      <c r="I55" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J55" s="15" t="s">
+      <c r="J55" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K55" s="15" t="s">
+      <c r="K55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="15"/>
-    </row>
-    <row r="56" spans="8:13">
+      <c r="L55" s="10"/>
+    </row>
+    <row r="56" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H56" t="s">
         <v>69</v>
       </c>
@@ -3362,7 +2723,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="8:13">
+    <row r="57" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H57" t="s">
         <v>72</v>
       </c>
@@ -3376,31 +2737,31 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="8:13">
-      <c r="H59" s="2" t="s">
+    <row r="59" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H59" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="8:13">
-      <c r="H60" s="15" t="s">
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+    </row>
+    <row r="60" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H60" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I60" s="15" t="s">
+      <c r="I60" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J60" s="15" t="s">
+      <c r="J60" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K60" s="15" t="s">
+      <c r="K60" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="8:13">
+    <row r="61" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H61" t="s">
         <v>77</v>
       </c>
@@ -3414,7 +2775,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="8:13">
+    <row r="62" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H62" t="s">
         <v>79</v>
       </c>
@@ -3428,7 +2789,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="8:13">
+    <row r="63" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H63" t="s">
         <v>82</v>
       </c>
@@ -3450,1467 +2811,1934 @@
     <mergeCell ref="H54:M54"/>
     <mergeCell ref="H59:M59"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:O108"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.75" customWidth="1"/>
-    <col min="3" max="3" width="40.875" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="10.625" customWidth="1"/>
-    <col min="9" max="9" width="12.625"/>
-    <col min="10" max="16" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="40.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625"/>
+    <col min="10" max="16" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="12"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="J13" s="8"/>
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="J14" s="8"/>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="J15" s="8"/>
+      <c r="O15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>161</v>
+      </c>
+      <c r="G16" t="s">
+        <v>163</v>
+      </c>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s">
+        <v>193</v>
+      </c>
+      <c r="D22" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" t="s">
+        <v>202</v>
+      </c>
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="2"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F28" t="s">
+        <v>299</v>
+      </c>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29" t="s">
+        <v>300</v>
+      </c>
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" t="s">
+        <v>303</v>
+      </c>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="2"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" t="s">
+        <v>308</v>
+      </c>
+      <c r="F35" t="s">
+        <v>309</v>
+      </c>
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" t="s">
+        <v>310</v>
+      </c>
+      <c r="D36" t="s">
+        <v>311</v>
+      </c>
+      <c r="E36" t="s">
+        <v>312</v>
+      </c>
+      <c r="F36" t="s">
+        <v>313</v>
+      </c>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" t="s">
+        <v>314</v>
+      </c>
+      <c r="D37" t="s">
+        <v>315</v>
+      </c>
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
         <v>84</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C40" t="s">
         <v>85</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D40" t="s">
         <v>86</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E40" t="s">
         <v>87</v>
       </c>
-      <c r="F7"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>88</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B41" t="s">
         <v>89</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C41" t="s">
         <v>90</v>
       </c>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>91</v>
-      </c>
-      <c r="B9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="J9" s="13"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="13"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="J14" s="13"/>
-      <c r="O14" s="8"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="O15" s="8"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="J16" s="13"/>
-      <c r="O16" s="8"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="J17" s="13"/>
-      <c r="O17" s="8"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="O18" s="8"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="J19" s="13"/>
-      <c r="O19" s="8"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J21" s="13"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J22" s="13"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J23" s="13"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J24" s="13"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J25" s="13"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J26" s="13"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J27" s="13"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>131</v>
-      </c>
-      <c r="F28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" t="s">
-        <v>132</v>
-      </c>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" s="3">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" t="s">
-        <v>39</v>
-      </c>
-      <c r="J29" s="13"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>131</v>
-      </c>
-      <c r="J30" s="13"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" t="s">
-        <v>135</v>
-      </c>
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="J31" s="13"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" t="s">
-        <v>137</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32">
-        <v>1000</v>
-      </c>
-      <c r="J32" s="13"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D33" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J33" s="13"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>141</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="J34" s="13"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>143</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J35" s="13"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J36" s="13"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" t="s">
-        <v>148</v>
-      </c>
-      <c r="D37" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" t="s">
-        <v>149</v>
-      </c>
-      <c r="B38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>151</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J39" s="13"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" t="s">
-        <v>154</v>
-      </c>
-      <c r="D40" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B41" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" t="s">
-        <v>156</v>
-      </c>
-      <c r="D41" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="J41" s="13"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" t="s">
-        <v>157</v>
       </c>
       <c r="B42" t="s">
         <v>89</v>
       </c>
       <c r="C42" t="s">
-        <v>158</v>
-      </c>
-      <c r="J42" s="13"/>
-    </row>
-    <row r="43" spans="1:10">
+        <v>92</v>
+      </c>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
-      </c>
-      <c r="D43" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="J43" s="13"/>
-    </row>
-    <row r="44" spans="1:10">
+        <v>94</v>
+      </c>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
-      </c>
-      <c r="D44" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="J44" s="13"/>
-    </row>
-    <row r="45" spans="1:10">
+        <v>96</v>
+      </c>
+      <c r="I44" t="s">
+        <v>173</v>
+      </c>
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
-      </c>
-      <c r="D45" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="J45" s="13"/>
-    </row>
-    <row r="46" spans="1:10">
+        <v>98</v>
+      </c>
+      <c r="I45" t="s">
+        <v>179</v>
+      </c>
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
         <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46">
-        <v>500</v>
-      </c>
-      <c r="J46" s="13"/>
-    </row>
-    <row r="47" spans="1:10">
+        <v>100</v>
+      </c>
+      <c r="I46" t="s">
+        <v>185</v>
+      </c>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
         <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="D47" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J47" s="13"/>
-    </row>
-    <row r="48" spans="1:10">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>187</v>
+      </c>
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
         <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="D48" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E48" t="s">
-        <v>169</v>
-      </c>
-      <c r="F48" t="s">
-        <v>170</v>
-      </c>
-      <c r="G48" t="s">
-        <v>171</v>
-      </c>
-      <c r="H48" t="s">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>173</v>
-      </c>
-      <c r="J48" s="13"/>
-    </row>
-    <row r="49" spans="1:10">
+        <v>192</v>
+      </c>
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
         <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="D49" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E49" t="s">
-        <v>175</v>
-      </c>
-      <c r="F49" t="s">
-        <v>176</v>
-      </c>
-      <c r="G49" t="s">
-        <v>177</v>
-      </c>
-      <c r="H49" t="s">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>179</v>
-      </c>
-      <c r="J49" s="13"/>
-    </row>
-    <row r="50" spans="1:10">
+        <v>187</v>
+      </c>
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
         <v>102</v>
       </c>
       <c r="C50" t="s">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="D50" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E50" t="s">
-        <v>181</v>
-      </c>
-      <c r="F50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G50" t="s">
-        <v>183</v>
-      </c>
-      <c r="H50" t="s">
-        <v>184</v>
+        <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>185</v>
-      </c>
-      <c r="J50" s="13"/>
-    </row>
-    <row r="51" spans="1:10">
+        <v>187</v>
+      </c>
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
         <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="D51" s="3">
-        <v>0.55</v>
-      </c>
-      <c r="E51" t="s">
-        <v>169</v>
-      </c>
-      <c r="F51" t="s">
-        <v>170</v>
-      </c>
-      <c r="G51" t="s">
-        <v>171</v>
-      </c>
-      <c r="H51" t="s">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="I51" t="s">
         <v>187</v>
       </c>
-      <c r="J51" s="13"/>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="B52" t="s">
         <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="D52" s="3">
-        <v>0.92</v>
-      </c>
-      <c r="E52" t="s">
-        <v>189</v>
-      </c>
-      <c r="F52" t="s">
-        <v>190</v>
-      </c>
-      <c r="G52" t="s">
-        <v>191</v>
-      </c>
-      <c r="H52" t="s">
-        <v>184</v>
+        <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>192</v>
-      </c>
-      <c r="J52" s="13"/>
-    </row>
-    <row r="53" spans="1:10">
+        <v>187</v>
+      </c>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>193</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
         <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>115</v>
       </c>
       <c r="D53" s="3">
-        <v>0.62</v>
-      </c>
-      <c r="E53" t="s">
-        <v>195</v>
-      </c>
-      <c r="F53" t="s">
-        <v>182</v>
-      </c>
-      <c r="G53" t="s">
-        <v>196</v>
-      </c>
-      <c r="H53" t="s">
-        <v>172</v>
-      </c>
-      <c r="I53" t="s">
-        <v>187</v>
-      </c>
-      <c r="J53" s="13"/>
-    </row>
-    <row r="54" spans="1:10">
+        <v>0.6</v>
+      </c>
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
         <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="D54" s="3">
-        <v>0.62</v>
-      </c>
-      <c r="E54" t="s">
-        <v>195</v>
-      </c>
-      <c r="F54" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54" t="s">
-        <v>196</v>
-      </c>
-      <c r="H54" t="s">
-        <v>172</v>
-      </c>
-      <c r="I54" t="s">
-        <v>187</v>
-      </c>
-      <c r="J54" s="13"/>
-    </row>
-    <row r="55" spans="1:10">
+        <v>0.6</v>
+      </c>
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
         <v>102</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="D55" s="3">
-        <v>0.62</v>
-      </c>
-      <c r="E55" t="s">
-        <v>195</v>
-      </c>
-      <c r="F55" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55" t="s">
-        <v>196</v>
-      </c>
-      <c r="H55" t="s">
-        <v>172</v>
-      </c>
-      <c r="I55" t="s">
-        <v>187</v>
-      </c>
-      <c r="J55" s="13"/>
-    </row>
-    <row r="56" spans="1:10">
+        <v>0.6</v>
+      </c>
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
         <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="D56" s="3">
-        <v>0.62</v>
-      </c>
-      <c r="E56" t="s">
-        <v>195</v>
-      </c>
-      <c r="F56" t="s">
-        <v>182</v>
-      </c>
-      <c r="G56" t="s">
-        <v>196</v>
-      </c>
-      <c r="H56" t="s">
-        <v>172</v>
+        <v>0.6</v>
       </c>
       <c r="I56" t="s">
-        <v>187</v>
-      </c>
-      <c r="J56" s="13"/>
-    </row>
-    <row r="57" spans="1:10">
+        <v>179</v>
+      </c>
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
         <v>102</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="D57" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="J57" s="13"/>
-    </row>
-    <row r="58" spans="1:10">
+        <v>0.6</v>
+      </c>
+      <c r="I57" t="s">
+        <v>179</v>
+      </c>
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
         <v>102</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
-      </c>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="1:10">
+        <v>125</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="I58" t="s">
+        <v>179</v>
+      </c>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
         <v>102</v>
       </c>
       <c r="C59" t="s">
-        <v>205</v>
-      </c>
-      <c r="J59" s="13"/>
-    </row>
-    <row r="60" spans="1:10">
+        <v>127</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
         <v>102</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="D60" s="3">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>175</v>
-      </c>
-      <c r="F60" t="s">
-        <v>176</v>
-      </c>
-      <c r="G60" t="s">
-        <v>177</v>
-      </c>
-      <c r="H60" t="s">
-        <v>178</v>
-      </c>
-      <c r="I60" t="s">
-        <v>179</v>
-      </c>
-      <c r="J60" s="13"/>
-    </row>
-    <row r="61" spans="1:10">
+        <v>0.6</v>
+      </c>
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
         <v>102</v>
       </c>
       <c r="C61" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="F61" t="s">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
       <c r="H61" t="s">
-        <v>178</v>
-      </c>
-      <c r="I61" t="s">
-        <v>179</v>
-      </c>
-      <c r="J61" s="13"/>
-    </row>
-    <row r="62" spans="1:10">
+        <v>132</v>
+      </c>
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
         <v>102</v>
       </c>
       <c r="C62" t="s">
-        <v>211</v>
+        <v>133</v>
       </c>
       <c r="D62" s="3">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="F62" t="s">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>177</v>
-      </c>
-      <c r="H62" t="s">
-        <v>178</v>
+        <v>39</v>
       </c>
       <c r="I62" t="s">
         <v>179</v>
       </c>
-      <c r="J62" s="13"/>
-    </row>
-    <row r="63" spans="1:10">
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>214</v>
-      </c>
-      <c r="D63">
-        <v>50</v>
-      </c>
-      <c r="J63" s="13"/>
-    </row>
-    <row r="64" spans="1:10">
+        <v>134</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>131</v>
+      </c>
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="B64" t="s">
         <v>102</v>
       </c>
       <c r="C64" t="s">
-        <v>216</v>
+        <v>136</v>
       </c>
       <c r="D64" s="3">
-        <v>1</v>
-      </c>
-      <c r="J64" s="13"/>
-    </row>
-    <row r="65" spans="1:10">
+        <v>0.8</v>
+      </c>
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
         <v>102</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
-      </c>
-      <c r="D65" s="3">
-        <v>2</v>
-      </c>
-      <c r="J65" s="13"/>
-    </row>
-    <row r="66" spans="1:10">
+        <v>138</v>
+      </c>
+      <c r="D65">
+        <v>1000</v>
+      </c>
+      <c r="I65" t="s">
+        <v>179</v>
+      </c>
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
         <v>102</v>
       </c>
       <c r="C66" t="s">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="D66" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E66" t="s">
-        <v>212</v>
-      </c>
-      <c r="F66" t="s">
-        <v>176</v>
-      </c>
-      <c r="G66" t="s">
-        <v>177</v>
-      </c>
-      <c r="H66" t="s">
-        <v>178</v>
-      </c>
-      <c r="I66" t="s">
-        <v>179</v>
-      </c>
-      <c r="J66" s="13"/>
-    </row>
-    <row r="67" spans="1:10">
+        <v>1.5</v>
+      </c>
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s">
         <v>102</v>
       </c>
       <c r="C67" t="s">
-        <v>222</v>
+        <v>142</v>
       </c>
       <c r="D67" s="3">
         <v>1</v>
       </c>
-      <c r="J67" s="13"/>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="I67" t="s">
+        <v>238</v>
+      </c>
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="B68" t="s">
         <v>102</v>
       </c>
       <c r="C68" t="s">
-        <v>224</v>
+        <v>144</v>
       </c>
       <c r="D68" s="3">
-        <v>1</v>
-      </c>
-      <c r="E68" t="s">
-        <v>225</v>
-      </c>
-      <c r="F68" t="s">
-        <v>226</v>
-      </c>
-      <c r="G68" t="s">
-        <v>184</v>
-      </c>
-      <c r="H68" t="s">
-        <v>227</v>
-      </c>
-      <c r="J68" s="13"/>
-    </row>
-    <row r="69" spans="1:10">
+        <v>0.5</v>
+      </c>
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>228</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s">
         <v>102</v>
       </c>
       <c r="C69" t="s">
-        <v>229</v>
+        <v>146</v>
       </c>
       <c r="D69" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E69" t="s">
-        <v>212</v>
-      </c>
-      <c r="F69" t="s">
-        <v>176</v>
-      </c>
-      <c r="G69" t="s">
-        <v>177</v>
-      </c>
-      <c r="H69" t="s">
-        <v>178</v>
+        <v>1.5</v>
       </c>
       <c r="I69" t="s">
         <v>179</v>
       </c>
-      <c r="J69" s="13"/>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="J69" s="8"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
         <v>102</v>
       </c>
       <c r="C70" t="s">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="D70" s="3">
-        <v>3</v>
-      </c>
-      <c r="J70" s="13"/>
-    </row>
-    <row r="71" spans="1:10">
+        <v>1.5</v>
+      </c>
+      <c r="J70" s="8"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>232</v>
+        <v>149</v>
       </c>
       <c r="B71" t="s">
         <v>102</v>
       </c>
       <c r="C71" t="s">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="D71" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E71" t="s">
-        <v>234</v>
-      </c>
-      <c r="F71" t="s">
-        <v>235</v>
-      </c>
-      <c r="G71" t="s">
-        <v>236</v>
-      </c>
-      <c r="H71" t="s">
-        <v>237</v>
+        <v>1.5</v>
       </c>
       <c r="I71" t="s">
-        <v>238</v>
-      </c>
-      <c r="J71" s="13"/>
-    </row>
-    <row r="72" spans="1:10">
+        <v>179</v>
+      </c>
+      <c r="J71" s="8"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="B72" t="s">
         <v>102</v>
       </c>
       <c r="C72" t="s">
-        <v>240</v>
+        <v>152</v>
       </c>
       <c r="D72" s="3">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
-        <v>225</v>
-      </c>
-      <c r="F72" t="s">
-        <v>226</v>
-      </c>
-      <c r="G72" t="s">
-        <v>184</v>
-      </c>
-      <c r="H72" t="s">
-        <v>227</v>
-      </c>
-      <c r="J72" s="13"/>
-    </row>
-    <row r="73" spans="1:10">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="B73" t="s">
         <v>102</v>
       </c>
       <c r="C73" t="s">
-        <v>242</v>
+        <v>154</v>
       </c>
       <c r="D73" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E73" t="s">
-        <v>212</v>
-      </c>
-      <c r="F73" t="s">
-        <v>176</v>
-      </c>
-      <c r="G73" t="s">
-        <v>177</v>
-      </c>
-      <c r="H73" t="s">
-        <v>178</v>
-      </c>
-      <c r="I73" t="s">
-        <v>179</v>
-      </c>
-      <c r="J73" s="13"/>
-    </row>
-    <row r="74" spans="1:10">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="B74" t="s">
         <v>102</v>
       </c>
       <c r="C74" t="s">
+        <v>156</v>
+      </c>
+      <c r="D74" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" t="s">
+        <v>102</v>
+      </c>
+      <c r="C76" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B77" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B78" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" t="s">
+        <v>164</v>
+      </c>
+      <c r="D79">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" t="s">
+        <v>168</v>
+      </c>
+      <c r="D81" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E81" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" t="s">
+        <v>171</v>
+      </c>
+      <c r="H81" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82" t="s">
+        <v>174</v>
+      </c>
+      <c r="D82" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E82" t="s">
+        <v>175</v>
+      </c>
+      <c r="F82" t="s">
+        <v>176</v>
+      </c>
+      <c r="G82" t="s">
+        <v>177</v>
+      </c>
+      <c r="H82" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" t="s">
+        <v>180</v>
+      </c>
+      <c r="D83" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E83" t="s">
+        <v>181</v>
+      </c>
+      <c r="F83" t="s">
+        <v>182</v>
+      </c>
+      <c r="G83" t="s">
+        <v>183</v>
+      </c>
+      <c r="H83" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" t="s">
+        <v>186</v>
+      </c>
+      <c r="D84" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E84" t="s">
+        <v>169</v>
+      </c>
+      <c r="F84" t="s">
+        <v>170</v>
+      </c>
+      <c r="G84" t="s">
+        <v>171</v>
+      </c>
+      <c r="H84" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" t="s">
+        <v>102</v>
+      </c>
+      <c r="C85" t="s">
+        <v>188</v>
+      </c>
+      <c r="D85" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="E85" t="s">
+        <v>189</v>
+      </c>
+      <c r="F85" t="s">
+        <v>190</v>
+      </c>
+      <c r="G85" t="s">
+        <v>191</v>
+      </c>
+      <c r="H85" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>193</v>
+      </c>
+      <c r="B86" t="s">
+        <v>102</v>
+      </c>
+      <c r="C86" t="s">
+        <v>194</v>
+      </c>
+      <c r="D86" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="E86" t="s">
+        <v>195</v>
+      </c>
+      <c r="F86" t="s">
+        <v>182</v>
+      </c>
+      <c r="G86" t="s">
+        <v>196</v>
+      </c>
+      <c r="H86" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s">
+        <v>102</v>
+      </c>
+      <c r="C87" t="s">
+        <v>198</v>
+      </c>
+      <c r="D87" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="E87" t="s">
+        <v>195</v>
+      </c>
+      <c r="F87" t="s">
+        <v>182</v>
+      </c>
+      <c r="G87" t="s">
+        <v>196</v>
+      </c>
+      <c r="H87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>199</v>
+      </c>
+      <c r="B88" t="s">
+        <v>102</v>
+      </c>
+      <c r="C88" t="s">
+        <v>200</v>
+      </c>
+      <c r="D88" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="E88" t="s">
+        <v>195</v>
+      </c>
+      <c r="F88" t="s">
+        <v>182</v>
+      </c>
+      <c r="G88" t="s">
+        <v>196</v>
+      </c>
+      <c r="H88" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>54</v>
+      </c>
+      <c r="B89" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" t="s">
+        <v>201</v>
+      </c>
+      <c r="D89" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="E89" t="s">
+        <v>195</v>
+      </c>
+      <c r="F89" t="s">
+        <v>182</v>
+      </c>
+      <c r="G89" t="s">
+        <v>196</v>
+      </c>
+      <c r="H89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" t="s">
+        <v>203</v>
+      </c>
+      <c r="D90" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>69</v>
+      </c>
+      <c r="B91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>72</v>
+      </c>
+      <c r="B92" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" t="s">
+        <v>207</v>
+      </c>
+      <c r="D93" s="3">
+        <v>1</v>
+      </c>
+      <c r="E93" t="s">
+        <v>175</v>
+      </c>
+      <c r="F93" t="s">
+        <v>176</v>
+      </c>
+      <c r="G93" t="s">
+        <v>177</v>
+      </c>
+      <c r="H93" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" t="s">
+        <v>102</v>
+      </c>
+      <c r="C94" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" s="3">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>175</v>
+      </c>
+      <c r="F94" t="s">
+        <v>176</v>
+      </c>
+      <c r="G94" t="s">
+        <v>177</v>
+      </c>
+      <c r="H94" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95" t="s">
+        <v>211</v>
+      </c>
+      <c r="D95" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E95" t="s">
+        <v>212</v>
+      </c>
+      <c r="F95" t="s">
+        <v>176</v>
+      </c>
+      <c r="G95" t="s">
+        <v>177</v>
+      </c>
+      <c r="H95" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96" t="s">
+        <v>89</v>
+      </c>
+      <c r="C96" t="s">
+        <v>214</v>
+      </c>
+      <c r="D96">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" t="s">
+        <v>216</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" t="s">
+        <v>218</v>
+      </c>
+      <c r="D98" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" t="s">
+        <v>102</v>
+      </c>
+      <c r="C99" t="s">
+        <v>220</v>
+      </c>
+      <c r="D99" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E99" t="s">
+        <v>212</v>
+      </c>
+      <c r="F99" t="s">
+        <v>176</v>
+      </c>
+      <c r="G99" t="s">
+        <v>177</v>
+      </c>
+      <c r="H99" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" t="s">
+        <v>222</v>
+      </c>
+      <c r="D100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" t="s">
+        <v>102</v>
+      </c>
+      <c r="C101" t="s">
+        <v>224</v>
+      </c>
+      <c r="D101" s="3">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" t="s">
+        <v>226</v>
+      </c>
+      <c r="G101" t="s">
+        <v>184</v>
+      </c>
+      <c r="H101" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" t="s">
+        <v>102</v>
+      </c>
+      <c r="C102" t="s">
+        <v>229</v>
+      </c>
+      <c r="D102" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E102" t="s">
+        <v>212</v>
+      </c>
+      <c r="F102" t="s">
+        <v>176</v>
+      </c>
+      <c r="G102" t="s">
+        <v>177</v>
+      </c>
+      <c r="H102" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>230</v>
+      </c>
+      <c r="B103" t="s">
+        <v>102</v>
+      </c>
+      <c r="C103" t="s">
+        <v>231</v>
+      </c>
+      <c r="D103" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" t="s">
+        <v>102</v>
+      </c>
+      <c r="C104" t="s">
+        <v>233</v>
+      </c>
+      <c r="D104" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F104" t="s">
+        <v>235</v>
+      </c>
+      <c r="G104" t="s">
+        <v>236</v>
+      </c>
+      <c r="H104" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>239</v>
+      </c>
+      <c r="B105" t="s">
+        <v>102</v>
+      </c>
+      <c r="C105" t="s">
+        <v>240</v>
+      </c>
+      <c r="D105" s="3">
+        <v>1</v>
+      </c>
+      <c r="E105" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" t="s">
+        <v>226</v>
+      </c>
+      <c r="G105" t="s">
+        <v>184</v>
+      </c>
+      <c r="H105" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>241</v>
+      </c>
+      <c r="B106" t="s">
+        <v>102</v>
+      </c>
+      <c r="C106" t="s">
+        <v>242</v>
+      </c>
+      <c r="D106" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E106" t="s">
+        <v>212</v>
+      </c>
+      <c r="F106" t="s">
+        <v>176</v>
+      </c>
+      <c r="G106" t="s">
+        <v>177</v>
+      </c>
+      <c r="H106" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>243</v>
+      </c>
+      <c r="B107" t="s">
+        <v>102</v>
+      </c>
+      <c r="C107" t="s">
         <v>244</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D107" s="3">
         <v>1</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E107" t="s">
         <v>225</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F107" t="s">
         <v>226</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G107" t="s">
         <v>184</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H107" t="s">
         <v>227</v>
       </c>
-      <c r="J74" s="13"/>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" t="s">
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>245</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B108" t="s">
         <v>102</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C108" t="s">
         <v>246</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D108" s="3">
         <v>0.5</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E108" t="s">
         <v>212</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F108" t="s">
         <v>176</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G108" t="s">
         <v>177</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H108" t="s">
         <v>178</v>
       </c>
-      <c r="I75" t="s">
-        <v>179</v>
-      </c>
-      <c r="J75" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="L21:M21"/>
+  <mergeCells count="8">
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A21:A22"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB207"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="12.625" customWidth="1"/>
+    <col min="1" max="7" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
       <c r="B1">
         <v>50</v>
       </c>
-      <c r="I1" t="s">
+      <c r="O1" t="s">
         <v>247</v>
       </c>
-      <c r="J1" t="s">
+      <c r="P1" t="s">
         <v>248</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>85</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>249</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="S1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="12"/>
       <c r="D2" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="12"/>
       <c r="G2" t="s">
         <v>253</v>
       </c>
-      <c r="I2" t="s">
+      <c r="O2" t="s">
         <v>255</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="P2" t="s">
         <v>256</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="Q2" t="s">
         <v>257</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="S2" s="11" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>12</v>
       </c>
@@ -4932,23 +4760,34 @@
       <c r="G3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="H3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3">
+        <f>C3+F3*($B$1-1)</f>
+        <v>1236</v>
+      </c>
+      <c r="J3">
+        <f>I3/A3</f>
+        <v>103</v>
+      </c>
+      <c r="O3" t="s">
         <v>259</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="P3" t="s">
         <v>260</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="Q3" t="s">
         <v>261</v>
       </c>
-      <c r="L3" t="s">
+      <c r="R3" t="s">
         <v>262</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="S3" s="11" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4970,23 +4809,34 @@
       <c r="G4">
         <v>4</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I8" si="0">C4+F4*($B$1-1)</f>
+        <v>408</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J8" si="1">I4/A4</f>
+        <v>204</v>
+      </c>
+      <c r="O4" t="s">
         <v>264</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="P4" t="s">
         <v>265</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="Q4" t="s">
         <v>266</v>
       </c>
-      <c r="L4" t="s">
+      <c r="R4" t="s">
         <v>267</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="S4" s="11" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5008,20 +4858,31 @@
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>206</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="O5" t="s">
         <v>269</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="P5" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="Q5" t="s">
         <v>270</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="S5" s="11" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -5043,10 +4904,21 @@
       <c r="G6">
         <v>1</v>
       </c>
+      <c r="H6" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5068,10 +4940,21 @@
       <c r="G7">
         <v>1</v>
       </c>
+      <c r="H7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -5093,10 +4976,21 @@
       <c r="G8">
         <v>1</v>
       </c>
+      <c r="H8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>108</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D9">
         <f>SUM(D3:D8)</f>
         <v>33</v>
@@ -5105,115 +4999,16 @@
         <f>SUM(G3:G8)</f>
         <v>11</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="I10" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" t="s">
-        <v>91</v>
-      </c>
-      <c r="M10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N10" t="s">
-        <v>95</v>
-      </c>
-      <c r="O10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="I11" s="2"/>
-      <c r="J11" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="I12" s="2"/>
-      <c r="J12" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="I13" s="2"/>
-      <c r="J13" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="7"/>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="J9">
+        <f>SUM(J3:J8)</f>
+        <v>572</v>
+      </c>
+      <c r="Q9" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5229,16 +5024,9 @@
       <c r="E14" t="s">
         <v>281</v>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="7"/>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -5249,608 +5037,191 @@
       <c r="C15">
         <v>120</v>
       </c>
-      <c r="D15" s="8">
-        <f>ROUND(C15/$C$21,2)</f>
+      <c r="D15" s="5">
+        <f t="shared" ref="D15:D20" si="2">ROUND(C15/$C$21,2)</f>
         <v>0.31</v>
       </c>
       <c r="E15" t="s">
         <v>282</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="C16">
         <v>120</v>
       </c>
-      <c r="D16" s="8">
-        <f>ROUND(C16/$C$21,2)</f>
+      <c r="D16" s="5">
+        <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
       <c r="E16" t="s">
         <v>284</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q16" s="7"/>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="C17">
         <v>60</v>
       </c>
-      <c r="D17" s="8">
-        <f>ROUND(C17/$C$21,2)</f>
+      <c r="D17" s="5">
+        <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="E17" t="s">
         <v>286</v>
       </c>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="7"/>
-    </row>
-    <row r="18" spans="1:18">
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="C18">
         <v>30</v>
       </c>
-      <c r="D18" s="8">
-        <f>ROUND(C18/$C$21,2)</f>
+      <c r="D18" s="5">
+        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E18" t="s">
         <v>287</v>
       </c>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-    </row>
-    <row r="19" spans="1:18">
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="C19">
         <v>30</v>
       </c>
-      <c r="D19" s="8">
-        <f>ROUND(C19/$C$21,2)</f>
+      <c r="D19" s="5">
+        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E19" t="s">
         <v>287</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-    </row>
-    <row r="20" spans="1:18">
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
       <c r="C20">
         <v>30</v>
       </c>
-      <c r="D20" s="8">
-        <f>ROUND(C20/$C$21,2)</f>
+      <c r="D20" s="5">
+        <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E20" t="s">
         <v>288</v>
       </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="7"/>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C21">
         <f>SUM(C15:C20)</f>
         <v>390</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="M21" s="5"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9" t="s">
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>289</v>
       </c>
       <c r="C22">
         <f>B15/D15</f>
-        <v>1845.16129032258</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="I23" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="I24" s="2"/>
-      <c r="J24" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="I25" s="2"/>
-      <c r="J25" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="I27" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="I28" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O28" s="5"/>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" t="s">
-        <v>193</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="R29" s="5"/>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="R30" s="5"/>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="I31" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="5"/>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="I32" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="R32" s="5"/>
-    </row>
-    <row r="33" spans="9:17">
-      <c r="I33" s="6"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="P33" s="5"/>
-    </row>
-    <row r="34" spans="9:17">
-      <c r="I34" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="9:17">
-      <c r="I35" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-    </row>
-    <row r="36" spans="9:17">
-      <c r="I36" s="6"/>
-      <c r="J36" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-    </row>
-    <row r="37" spans="9:17">
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="9:17">
-      <c r="I38" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-    </row>
-    <row r="39" spans="9:17">
-      <c r="I39" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="40" spans="9:17">
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="9:17">
-      <c r="I41" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-    </row>
-    <row r="42" spans="9:17">
-      <c r="I42" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-    </row>
-    <row r="43" spans="9:17">
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-    </row>
-    <row r="44" spans="9:17">
-      <c r="I44" s="6"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-    </row>
-    <row r="45" spans="9:17">
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="5"/>
-      <c r="O45" s="5"/>
-    </row>
-    <row r="49" spans="12:20">
+        <v>1845.1612903225807</v>
+      </c>
+      <c r="Q22" s="2"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q27" s="2"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="38" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="41" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q41" s="2"/>
+    </row>
+    <row r="49" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
-      <c r="N49" s="5"/>
-    </row>
-    <row r="50" spans="12:20">
-      <c r="L50" s="6"/>
+    </row>
+    <row r="50" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L50" s="2"/>
       <c r="M50" s="2"/>
-      <c r="T50" s="5"/>
-    </row>
-    <row r="51" spans="12:20">
+    </row>
+    <row r="51" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5"/>
-    </row>
-    <row r="52" spans="12:20">
+    </row>
+    <row r="52" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="12:20">
+    <row r="53" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="12:20">
+    <row r="54" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="12:20">
+    <row r="55" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="12:20">
+    <row r="56" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="12:20">
+    <row r="57" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="12:20">
+    <row r="58" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="12:20">
+    <row r="59" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="12:20">
+    <row r="60" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="12:20">
+    <row r="61" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="12:20">
+    <row r="62" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="12:20">
+    <row r="63" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="12:20">
+    <row r="64" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="11:28">
+    <row r="65" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="11:28">
-      <c r="L66" s="6" t="s">
+    <row r="66" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="L66" s="2" t="s">
         <v>316</v>
       </c>
       <c r="M66" s="2"/>
@@ -5862,247 +5233,235 @@
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
     </row>
-    <row r="67" spans="11:28">
+    <row r="67" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="11:28">
+    <row r="68" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="11:28">
-      <c r="L69" s="5"/>
+    <row r="69" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="70" spans="11:28">
-      <c r="L70" s="5"/>
-      <c r="M70" s="6" t="s">
+    <row r="70" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="M70" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="N70" s="6"/>
+      <c r="N70" s="2"/>
       <c r="O70" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="71" spans="11:28">
-      <c r="M71" s="6" t="s">
+    <row r="71" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="M71" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="N71" s="6"/>
+      <c r="N71" s="2"/>
       <c r="O71" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="72" spans="11:28">
-      <c r="M72" s="6" t="s">
+    <row r="72" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="M72" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="N72" s="6"/>
+      <c r="N72" s="2"/>
       <c r="O72" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="11:28">
-      <c r="M73" s="6" t="s">
+    <row r="73" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="M73" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="N73" s="6"/>
+      <c r="N73" s="2"/>
       <c r="O73" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="74" spans="11:28">
-      <c r="M74" s="6" t="s">
+    <row r="74" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="M74" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="N74" s="6"/>
+      <c r="N74" s="2"/>
       <c r="O74" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="75" spans="11:28">
-      <c r="M75" s="6" t="s">
+    <row r="75" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="M75" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="N75" s="6"/>
+      <c r="N75" s="2"/>
       <c r="O75" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="76" spans="11:28">
+    <row r="76" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
-      <c r="U76" s="5" t="s">
+      <c r="U76" t="s">
         <v>325</v>
       </c>
-      <c r="V76" s="5" t="s">
+      <c r="V76" t="s">
         <v>326</v>
       </c>
-      <c r="Z76" s="5" t="s">
+      <c r="Z76" t="s">
         <v>327</v>
       </c>
-      <c r="AA76" s="5" t="s">
+      <c r="AA76" t="s">
         <v>328</v>
       </c>
-      <c r="AB76" s="5" t="s">
+      <c r="AB76" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="77" spans="11:28">
+    <row r="77" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
-    <row r="78" spans="11:28">
+    <row r="78" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
-    <row r="79" spans="11:28">
+    <row r="79" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
-      <c r="N79" s="5" t="s">
+      <c r="N79" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="80" spans="11:28">
-      <c r="K80" s="5" t="s">
+    <row r="80" spans="11:28" x14ac:dyDescent="0.25">
+      <c r="K80" t="s">
         <v>331</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="11:20">
-      <c r="K81" s="5" t="s">
+    <row r="81" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="K81" t="s">
         <v>332</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="11:20">
+    <row r="82" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="11:20">
-      <c r="K83" s="5" t="s">
+    <row r="83" spans="11:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K83" t="s">
         <v>135</v>
       </c>
-      <c r="L83" s="6" t="s">
+      <c r="L83" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M83" s="6"/>
+      <c r="M83" s="2"/>
       <c r="N83" s="3">
         <v>0.5</v>
       </c>
-      <c r="O83" s="10" t="s">
+      <c r="O83" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="P83" s="11"/>
-      <c r="Q83" s="11"/>
-      <c r="R83" s="11"/>
-      <c r="S83" s="11"/>
-      <c r="T83" s="11"/>
-    </row>
-    <row r="84" spans="11:20">
-      <c r="K84" s="5" t="s">
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7"/>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
+    </row>
+    <row r="84" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="K84" t="s">
         <v>153</v>
       </c>
-      <c r="L84" s="6" t="s">
+      <c r="L84" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M84" s="6"/>
-    </row>
-    <row r="85" spans="11:20">
-      <c r="K85" s="5" t="s">
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="K85" t="s">
         <v>334</v>
       </c>
-      <c r="L85" s="6" t="s">
+      <c r="L85" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M85" s="6"/>
-    </row>
-    <row r="86" spans="11:20">
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="11:20">
+    <row r="87" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="11:20">
-      <c r="K88" s="5" t="s">
+    <row r="88" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="K88" t="s">
         <v>193</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
-      <c r="N88" s="5" t="s">
+      <c r="N88" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="89" spans="11:20">
+    <row r="89" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="201" spans="12:13">
+    <row r="201" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
     </row>
-    <row r="202" spans="12:13">
+    <row r="202" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
     </row>
-    <row r="203" spans="12:13">
+    <row r="203" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
     </row>
-    <row r="204" spans="12:13">
+    <row r="204" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
     </row>
-    <row r="205" spans="12:13">
+    <row r="205" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
     </row>
-    <row r="206" spans="12:13">
+    <row r="206" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
     </row>
-    <row r="207" spans="12:13">
+    <row r="207" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="2">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="L66:T66"/>
-    <mergeCell ref="O83:T83"/>
-    <mergeCell ref="I10:I13"/>
-    <mergeCell ref="I16:I19"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="I39:I40"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A16:X40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="12" width="8.625" customWidth="1"/>
+    <col min="7" max="12" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="7:8">
+    <row r="16" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G16" t="s">
         <v>336</v>
       </c>
@@ -6110,7 +5469,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>131</v>
       </c>
@@ -6124,7 +5483,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G18" t="s">
         <v>341</v>
       </c>
@@ -6138,7 +5497,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>345</v>
       </c>
@@ -6152,7 +5511,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
         <v>348</v>
       </c>
@@ -6166,17 +5525,17 @@
         <v>351</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G22" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>353</v>
       </c>
@@ -6193,7 +5552,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>358</v>
       </c>
@@ -6209,12 +5568,11 @@
       <c r="H26" t="s">
         <v>360</v>
       </c>
-      <c r="I26"/>
       <c r="K26" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>362</v>
       </c>
@@ -6246,7 +5604,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>365</v>
       </c>
@@ -6278,7 +5636,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>367</v>
       </c>
@@ -6298,7 +5656,7 @@
         <v>91</v>
       </c>
       <c r="I29" s="3">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J29" t="s">
         <v>124</v>
@@ -6313,7 +5671,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>371</v>
       </c>
@@ -6339,7 +5697,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G31" t="s">
         <v>343</v>
       </c>
@@ -6353,7 +5711,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G32" t="s">
         <v>344</v>
       </c>
@@ -6367,20 +5725,19 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
       <c r="G33" t="s">
         <v>346</v>
       </c>
       <c r="H33" t="s">
         <v>88</v>
       </c>
-      <c r="I33"/>
       <c r="M33" t="s">
         <v>373</v>
       </c>
@@ -6388,7 +5745,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
@@ -6408,7 +5765,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2</v>
       </c>
@@ -6425,7 +5782,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6436,7 +5793,7 @@
         <v>99</v>
       </c>
       <c r="I36" s="3">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J36" t="s">
         <v>62</v>
@@ -6451,7 +5808,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4</v>
       </c>
@@ -6471,11 +5828,10 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5</v>
       </c>
-      <c r="B38"/>
       <c r="G38" t="s">
         <v>351</v>
       </c>
@@ -6492,12 +5848,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G39" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G40" t="s">
         <v>352</v>
       </c>
@@ -6530,26 +5886,25 @@
   <mergeCells count="1">
     <mergeCell ref="A33:D33"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="K19:N46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="16" width="20.6666666666667" customWidth="1"/>
+    <col min="11" max="16" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="11:14">
+    <row r="19" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K19" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="21" spans="11:14">
+    <row r="21" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K21" t="s">
         <v>132</v>
       </c>
@@ -6563,7 +5918,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="22" spans="11:14">
+    <row r="22" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K22" t="s">
         <v>379</v>
       </c>
@@ -6577,7 +5932,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="23" spans="11:14">
+    <row r="23" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K23" t="s">
         <v>383</v>
       </c>
@@ -6591,7 +5946,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="24" spans="11:14">
+    <row r="24" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K24" t="s">
         <v>387</v>
       </c>
@@ -6605,7 +5960,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="25" spans="11:14">
+    <row r="25" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K25" t="s">
         <v>391</v>
       </c>
@@ -6619,7 +5974,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="26" spans="11:14">
+    <row r="26" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K26" t="s">
         <v>395</v>
       </c>
@@ -6633,12 +5988,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="33" spans="11:12">
+    <row r="33" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K33" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="35" spans="11:12">
+    <row r="35" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K35" t="s">
         <v>400</v>
       </c>
@@ -6646,7 +6001,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="36" spans="11:12">
+    <row r="36" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K36" t="s">
         <v>402</v>
       </c>
@@ -6654,7 +6009,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="37" spans="11:12">
+    <row r="37" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K37" t="s">
         <v>404</v>
       </c>
@@ -6662,7 +6017,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="38" spans="11:12">
+    <row r="38" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K38" t="s">
         <v>406</v>
       </c>
@@ -6670,7 +6025,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="39" spans="11:12">
+    <row r="39" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K39" t="s">
         <v>408</v>
       </c>
@@ -6678,12 +6033,12 @@
         <v>409</v>
       </c>
     </row>
-    <row r="40" spans="11:12">
+    <row r="40" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K40" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="41" spans="11:12">
+    <row r="41" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K41" t="s">
         <v>132</v>
       </c>
@@ -6691,7 +6046,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="42" spans="11:12">
+    <row r="42" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K42" t="s">
         <v>379</v>
       </c>
@@ -6699,7 +6054,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="43" spans="11:12">
+    <row r="43" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K43" t="s">
         <v>383</v>
       </c>
@@ -6707,7 +6062,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="44" spans="11:12">
+    <row r="44" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K44" t="s">
         <v>387</v>
       </c>
@@ -6715,7 +6070,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="45" spans="11:12">
+    <row r="45" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K45" t="s">
         <v>391</v>
       </c>
@@ -6723,7 +6078,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="46" spans="11:12">
+    <row r="46" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K46" t="s">
         <v>395</v>
       </c>
@@ -6732,18 +6087,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="I11:S40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="11" spans="9:19">
+    <row r="11" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I11" t="s">
         <v>417</v>
       </c>
@@ -6757,7 +6111,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="9:19">
+    <row r="13" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>421</v>
       </c>
@@ -6777,7 +6131,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="9:19">
+    <row r="14" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>424</v>
       </c>
@@ -6797,7 +6151,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="15" spans="9:19">
+    <row r="15" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>69</v>
       </c>
@@ -6817,7 +6171,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="16" spans="9:19">
+    <row r="16" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
         <v>82</v>
       </c>
@@ -6837,7 +6191,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="17" spans="9:19">
+    <row r="17" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I17" t="s">
         <v>432</v>
       </c>
@@ -6857,7 +6211,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="18" spans="9:19">
+    <row r="18" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>435</v>
       </c>
@@ -6877,7 +6231,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="19" spans="9:19">
+    <row r="19" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>26</v>
       </c>
@@ -6897,7 +6251,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="20" spans="9:19">
+    <row r="20" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>440</v>
       </c>
@@ -6917,7 +6271,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="21" spans="9:19">
+    <row r="21" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>443</v>
       </c>
@@ -6937,7 +6291,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="22" spans="9:19">
+    <row r="22" spans="9:19" x14ac:dyDescent="0.25">
       <c r="Q22" t="s">
         <v>26</v>
       </c>
@@ -6948,7 +6302,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="23" spans="9:19">
+    <row r="23" spans="9:19" x14ac:dyDescent="0.25">
       <c r="Q23" t="s">
         <v>69</v>
       </c>
@@ -6959,7 +6313,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="25" spans="9:19">
+    <row r="25" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I25" t="s">
         <v>30</v>
       </c>
@@ -6973,7 +6327,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="26" spans="9:19">
+    <row r="26" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
         <v>451</v>
       </c>
@@ -6987,7 +6341,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="27" spans="9:19">
+    <row r="27" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>455</v>
       </c>
@@ -7001,7 +6355,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="9:19">
+    <row r="28" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I28" t="s">
         <v>459</v>
       </c>
@@ -7015,7 +6369,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="9:19">
+    <row r="29" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I29" t="s">
         <v>463</v>
       </c>
@@ -7029,7 +6383,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="30" spans="9:19">
+    <row r="30" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I30" t="s">
         <v>467</v>
       </c>
@@ -7037,25 +6391,25 @@
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="9:13">
+    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I35" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="9:13">
+    <row r="36" spans="9:13" ht="15.6" x14ac:dyDescent="0.25">
       <c r="I36" s="1" t="s">
         <v>470</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="9:13">
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+    </row>
+    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I37" t="s">
         <v>472</v>
       </c>
@@ -7063,7 +6417,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="9:13">
+    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I38" t="s">
         <v>473</v>
       </c>
@@ -7071,7 +6425,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="9:13">
+    <row r="39" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I39" t="s">
         <v>474</v>
       </c>
@@ -7079,7 +6433,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="9:13">
+    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I40" t="s">
         <v>475</v>
       </c>
@@ -7091,23 +6445,22 @@
   <mergeCells count="1">
     <mergeCell ref="K36:M36"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="H8:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="8" spans="8:16">
+    <row r="8" spans="8:16" x14ac:dyDescent="0.25">
       <c r="O8" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="10" spans="8:16">
+    <row r="10" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>477</v>
       </c>
@@ -7115,7 +6468,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="11" spans="8:16">
+    <row r="11" spans="8:16" x14ac:dyDescent="0.25">
       <c r="O11" t="s">
         <v>479</v>
       </c>
@@ -7123,7 +6476,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="12" spans="8:16">
+    <row r="12" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>479</v>
       </c>
@@ -7143,7 +6496,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="13" spans="8:16">
+    <row r="13" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>482</v>
       </c>
@@ -7163,7 +6516,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="14" spans="8:16">
+    <row r="14" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>487</v>
       </c>
@@ -7183,7 +6536,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="15" spans="8:16">
+    <row r="15" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H15" t="s">
         <v>492</v>
       </c>
@@ -7203,7 +6556,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="16" spans="8:16">
+    <row r="16" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H16" t="s">
         <v>496</v>
       </c>
@@ -7221,23 +6574,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="J4:R53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="10:18">
+    <row r="4" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R4" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="5" spans="10:18">
+    <row r="5" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>503</v>
       </c>
@@ -7245,7 +6597,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="6" spans="10:18">
+    <row r="6" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>505</v>
       </c>
@@ -7256,7 +6608,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="7" spans="10:18">
+    <row r="7" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>10</v>
       </c>
@@ -7264,7 +6616,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="8" spans="10:18">
+    <row r="8" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J8" t="s">
         <v>11</v>
       </c>
@@ -7272,7 +6624,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="9" spans="10:18">
+    <row r="9" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
         <v>510</v>
       </c>
@@ -7280,17 +6632,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="10:12">
+    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J17" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="19" spans="10:12">
+    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="20" spans="10:12">
+    <row r="20" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>87</v>
       </c>
@@ -7301,7 +6653,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="21" spans="10:12">
+    <row r="21" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J21" t="s">
         <v>131</v>
       </c>
@@ -7312,7 +6664,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="22" spans="10:12">
+    <row r="22" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
         <v>514</v>
       </c>
@@ -7323,7 +6675,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="23" spans="10:12">
+    <row r="23" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
         <v>515</v>
       </c>
@@ -7334,7 +6686,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="10:12">
+    <row r="24" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
         <v>516</v>
       </c>
@@ -7345,7 +6697,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="25" spans="10:12">
+    <row r="25" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J25" t="s">
         <v>517</v>
       </c>
@@ -7356,22 +6708,22 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="26" spans="10:12">
+    <row r="26" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J26" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="29" spans="10:12">
+    <row r="29" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J29" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="31" spans="10:12">
+    <row r="31" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="32" spans="10:12">
+    <row r="32" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
         <v>87</v>
       </c>
@@ -7382,7 +6734,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="33" spans="10:12">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J33" t="s">
         <v>521</v>
       </c>
@@ -7393,7 +6745,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="10:12">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J34" t="s">
         <v>56</v>
       </c>
@@ -7404,7 +6756,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="10:12">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J35" t="s">
         <v>52</v>
       </c>
@@ -7415,7 +6767,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="10:12">
+    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J36" t="s">
         <v>522</v>
       </c>
@@ -7426,7 +6778,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="37" spans="10:12">
+    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J37" t="s">
         <v>517</v>
       </c>
@@ -7437,27 +6789,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="10:12">
+    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J38" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="41" spans="10:12">
+    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J41" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="43" spans="10:12">
+    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J43" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="44" spans="10:12">
+    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J44" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="46" spans="10:12">
+    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J46" t="s">
         <v>87</v>
       </c>
@@ -7468,7 +6820,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="10:12">
+    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J47" t="s">
         <v>527</v>
       </c>
@@ -7479,7 +6831,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="48" spans="10:12">
+    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J48" t="s">
         <v>529</v>
       </c>
@@ -7490,7 +6842,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="49" spans="10:12">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J49" t="s">
         <v>531</v>
       </c>
@@ -7501,7 +6853,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="50" spans="10:12">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J50" t="s">
         <v>35</v>
       </c>
@@ -7512,7 +6864,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="51" spans="10:12">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J51" t="s">
         <v>25</v>
       </c>
@@ -7523,7 +6875,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="52" spans="10:12">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J52" t="s">
         <v>39</v>
       </c>
@@ -7534,30 +6886,29 @@
         <v>535</v>
       </c>
     </row>
-    <row r="53" spans="10:12">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J53" t="s">
         <v>536</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>537</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/documents/新需求/数值管理.xlsx
+++ b/documents/新需求/数值管理.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4-softworkspace\java\CombatDebugStudio\documents\新需求\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5-workspace\code\CombatDebugStudio\documents\新需求\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA599F-D522-4571-854F-A712F71E374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,11 +23,24 @@
     <sheet name="神器与法宝" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="636">
   <si>
     <t>B类属性</t>
   </si>
@@ -282,6 +294,231 @@
     <t>护腕、五行流派、机巧天赋</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>层级</t>
+  </si>
+  <si>
+    <t>基础-20</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>气血</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>气血加成</t>
+  </si>
+  <si>
+    <t>攻击加成</t>
+  </si>
+  <si>
+    <t>防御加成</t>
+  </si>
+  <si>
+    <t>命中加成</t>
+  </si>
+  <si>
+    <t>闪避加成</t>
+  </si>
+  <si>
+    <t>速度加成</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>气血系数</t>
+  </si>
+  <si>
+    <t>攻击系数</t>
+  </si>
+  <si>
+    <t>防御系数</t>
+  </si>
+  <si>
+    <t>命中系数</t>
+  </si>
+  <si>
+    <t>闪避系数</t>
+  </si>
+  <si>
+    <t>速度系数</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>最终攻击</t>
+  </si>
+  <si>
+    <t>最终防御</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>输出-14</t>
+  </si>
+  <si>
+    <t>真伤率</t>
+  </si>
+  <si>
+    <t>真伤附加值</t>
+  </si>
+  <si>
+    <t>伤害加成</t>
+  </si>
+  <si>
+    <t>普攻加成</t>
+  </si>
+  <si>
+    <t>技能加成</t>
+  </si>
+  <si>
+    <t>反击伤害加成</t>
+  </si>
+  <si>
+    <t>伤害系数</t>
+  </si>
+  <si>
+    <t>反击伤害系数</t>
+  </si>
+  <si>
+    <t>连击伤害系数</t>
+  </si>
+  <si>
+    <t>真伤系数</t>
+  </si>
+  <si>
+    <t>最终伤害提升</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>生存-7</t>
+  </si>
+  <si>
+    <t>护盾</t>
+  </si>
+  <si>
+    <t>气血回复(%)</t>
+  </si>
+  <si>
+    <t>气血回复(固定)</t>
+  </si>
+  <si>
+    <t>免伤系数</t>
+  </si>
+  <si>
+    <t>最终伤害减免</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>对抗-10</t>
+  </si>
+  <si>
+    <t>真伤抗性</t>
+  </si>
+  <si>
+    <t>普攻抵抗</t>
+  </si>
+  <si>
+    <t>技能抵抗</t>
+  </si>
+  <si>
+    <t>效果抵抗</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>五行-2</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>机制-5</t>
+  </si>
+  <si>
+    <t>效果命中</t>
+  </si>
+  <si>
+    <t>初始能量</t>
+  </si>
+  <si>
+    <t>能量获取效率</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>占位-1</t>
+  </si>
+  <si>
+    <t>溅射</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>机制-10</t>
+  </si>
+  <si>
+    <t>破甲</t>
+  </si>
+  <si>
+    <t>易伤</t>
+  </si>
+  <si>
+    <t>吸血效果加成</t>
+  </si>
+  <si>
+    <t>吸血效果削减</t>
+  </si>
+  <si>
+    <t>护盾加成</t>
+  </si>
+  <si>
+    <t>护盾削减</t>
+  </si>
+  <si>
+    <t>治疗强度加成</t>
+  </si>
+  <si>
+    <t>治疗强度削减</t>
+  </si>
+  <si>
+    <t>伤害反弹加成</t>
+  </si>
+  <si>
+    <t>伤害反弹削减</t>
+  </si>
+  <si>
     <t>数值类型</t>
   </si>
   <si>
@@ -294,46 +531,34 @@
     <t>来源</t>
   </si>
   <si>
-    <t>气血</t>
-  </si>
-  <si>
     <t>数值</t>
   </si>
   <si>
     <t>角色生命值，归零即退场。</t>
   </si>
   <si>
-    <t>攻击</t>
-  </si>
-  <si>
     <t>伤害计算基数，越高伤害越高。</t>
   </si>
   <si>
-    <t>防御</t>
-  </si>
-  <si>
     <t>抵扣受到的伤害，越高受伤越低。</t>
   </si>
   <si>
-    <t>命中</t>
-  </si>
-  <si>
     <t>攻击命中判定的基础值，对抗目标闪避值。</t>
   </si>
   <si>
-    <t>闪避</t>
+    <t>流派+15%</t>
   </si>
   <si>
     <t>闪避判定的基础值，对抗目标命中值。</t>
   </si>
   <si>
-    <t>速度</t>
+    <t>流派16</t>
   </si>
   <si>
     <t>决定每回合行动顺序，高者先动。</t>
   </si>
   <si>
-    <t>气血加成</t>
+    <t>流派+16%</t>
   </si>
   <si>
     <t>百分比</t>
@@ -342,81 +567,48 @@
     <t>按百分比提高气血。</t>
   </si>
   <si>
-    <t>攻击加成</t>
+    <t>流派+10%</t>
   </si>
   <si>
     <t>按百分比提高攻击。</t>
   </si>
   <si>
-    <t>防御加成</t>
+    <t>流派+12%</t>
   </si>
   <si>
     <t>按百分比提高防御。</t>
   </si>
   <si>
-    <t>命中加成</t>
-  </si>
-  <si>
     <t>按百分比提高命中。</t>
   </si>
   <si>
-    <t>闪避加成</t>
-  </si>
-  <si>
     <t>按百分比提高闪避。</t>
   </si>
   <si>
-    <t>速度加成</t>
-  </si>
-  <si>
     <t>按百分比提高速度。</t>
   </si>
   <si>
-    <t>气血系数</t>
-  </si>
-  <si>
     <t>对气血进行独立乘区放大。</t>
   </si>
   <si>
-    <t>攻击系数</t>
-  </si>
-  <si>
     <t>对攻击进行独立乘区放大。</t>
   </si>
   <si>
-    <t>防御系数</t>
-  </si>
-  <si>
     <t>对防御进行独立乘区放大。</t>
   </si>
   <si>
-    <t>命中系数</t>
-  </si>
-  <si>
     <t>对命中进行独立乘区放大。</t>
   </si>
   <si>
-    <t>闪避系数</t>
-  </si>
-  <si>
     <t>对闪避进行独立乘区放大。</t>
   </si>
   <si>
-    <t>速度系数</t>
-  </si>
-  <si>
     <t>对速度进行独立乘区放大。</t>
   </si>
   <si>
-    <t>最终攻击</t>
-  </si>
-  <si>
     <t>最终层提高攻击，不被任何乘区稀释。</t>
   </si>
   <si>
-    <t>最终防御</t>
-  </si>
-  <si>
     <t>最终层提高防御，不被任何乘区稀释</t>
   </si>
   <si>
@@ -435,75 +627,42 @@
     <t>攻击后追加额外攻击段的概率。</t>
   </si>
   <si>
-    <t>真伤率</t>
-  </si>
-  <si>
     <t>将伤害基数的一定比例转化为无视防御的真实伤害。</t>
   </si>
   <si>
-    <t>真伤附加值</t>
-  </si>
-  <si>
     <t>额外附加的固定真实伤害，不随倍率放大。</t>
   </si>
   <si>
-    <t>伤害加成</t>
-  </si>
-  <si>
     <t>按百分比提高造成的所有伤害。</t>
   </si>
   <si>
-    <t>普攻加成</t>
-  </si>
-  <si>
     <t>仅按百分比提高普攻伤害。</t>
   </si>
   <si>
-    <t>技能加成</t>
+    <t>流派12%</t>
   </si>
   <si>
     <t>仅按百分比提高技能伤害。</t>
   </si>
   <si>
-    <t>反击伤害加成</t>
-  </si>
-  <si>
     <t>仅按百分比提高反击的伤害。</t>
   </si>
   <si>
-    <t>伤害系数</t>
-  </si>
-  <si>
     <t>对造成的伤害进行独立乘区放大。</t>
   </si>
   <si>
-    <t>反击伤害系数</t>
-  </si>
-  <si>
     <t>独立放大反击段的伤害。</t>
   </si>
   <si>
-    <t>连击伤害系数</t>
-  </si>
-  <si>
     <t>独立放大连击段的伤害。</t>
   </si>
   <si>
-    <t>真伤系数</t>
-  </si>
-  <si>
     <t>独立放大真实伤害。</t>
   </si>
   <si>
-    <t>最终伤害提升</t>
-  </si>
-  <si>
     <t>最终层提高造成的伤害。</t>
   </si>
   <si>
-    <t>护盾</t>
-  </si>
-  <si>
     <t>独立于气血的白字血量，优先吸收伤害。</t>
   </si>
   <si>
@@ -513,27 +672,15 @@
     <t>将受到伤害的一定比例反弹给攻击者。</t>
   </si>
   <si>
-    <t>气血回复(%)</t>
-  </si>
-  <si>
     <t>每回合按最大气血百分比回复。</t>
   </si>
   <si>
-    <t>气血回复(固定)</t>
-  </si>
-  <si>
     <t>每回合回复固定气血值。</t>
   </si>
   <si>
-    <t>免伤系数</t>
-  </si>
-  <si>
     <t>独立放大免伤效果。</t>
   </si>
   <si>
-    <t>最终伤害减免</t>
-  </si>
-  <si>
     <t>最终层减少受到的伤害。</t>
   </si>
   <si>
@@ -549,9 +696,6 @@
     <t>坐骑+10%</t>
   </si>
   <si>
-    <t>流派+15%</t>
-  </si>
-  <si>
     <t>直接提高最终命中概率，对抗目标闪避率。</t>
   </si>
   <si>
@@ -567,9 +711,6 @@
     <t>宠物8%</t>
   </si>
   <si>
-    <t>流派16</t>
-  </si>
-  <si>
     <t>直接降低敌方对自己的最终命中概率。</t>
   </si>
   <si>
@@ -585,15 +726,9 @@
     <t>坐骑+12%</t>
   </si>
   <si>
-    <t>流派+16%</t>
-  </si>
-  <si>
     <t>降低敌方对自己的暴击率。</t>
   </si>
   <si>
-    <t>流派+10%</t>
-  </si>
-  <si>
     <t>降低敌方对自己的暴击伤害。</t>
   </si>
   <si>
@@ -606,12 +741,6 @@
     <t>鞋+8%+8%</t>
   </si>
   <si>
-    <t>流派+12%</t>
-  </si>
-  <si>
-    <t>真伤抗性</t>
-  </si>
-  <si>
     <t>减少受到的真实伤害。</t>
   </si>
   <si>
@@ -621,24 +750,15 @@
     <t>鞋+6%+6%</t>
   </si>
   <si>
-    <t>普攻抵抗</t>
-  </si>
-  <si>
     <t>减少受到的普攻伤害。</t>
   </si>
   <si>
-    <t>技能抵抗</t>
-  </si>
-  <si>
     <t>减少受到的技能伤害。</t>
   </si>
   <si>
     <t>降低被敌方控制的概率。</t>
   </si>
   <si>
-    <t>效果抵抗</t>
-  </si>
-  <si>
     <t>降低被敌方减益/异常状态命中的概率。</t>
   </si>
   <si>
@@ -744,9 +864,6 @@
     <t>宠物6%</t>
   </si>
   <si>
-    <t>流派12%</t>
-  </si>
-  <si>
     <t>吸血效果加成%</t>
   </si>
   <si>
@@ -771,9 +888,6 @@
     <t>降低目标受到的治疗效果。</t>
   </si>
   <si>
-    <t>层级</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
@@ -846,24 +960,6 @@
     <t>+10%最终攻击</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>基础-20</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>L4</t>
-  </si>
-  <si>
     <t>总属性点</t>
   </si>
   <si>
@@ -879,15 +975,9 @@
     <t>属性A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>属性A B C D E F + 属性增幅</t>
   </si>
   <si>
-    <t>输出-14</t>
-  </si>
-  <si>
     <t>技能 + 特性 + 属性增幅</t>
   </si>
   <si>
@@ -900,84 +990,6 @@
     <t>总属性点:</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>生存-7</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>对抗-10</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>五行-2</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>机制-5</t>
-  </si>
-  <si>
-    <t>效果命中</t>
-  </si>
-  <si>
-    <t>初始能量</t>
-  </si>
-  <si>
-    <t>能量获取效率</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>占位-1</t>
-  </si>
-  <si>
-    <t>溅射</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>机制-10</t>
-  </si>
-  <si>
-    <t>破甲</t>
-  </si>
-  <si>
-    <t>易伤</t>
-  </si>
-  <si>
-    <t>吸血效果加成</t>
-  </si>
-  <si>
-    <t>吸血效果削减</t>
-  </si>
-  <si>
-    <t>护盾加成</t>
-  </si>
-  <si>
-    <t>护盾削减</t>
-  </si>
-  <si>
-    <t>治疗强度加成</t>
-  </si>
-  <si>
-    <t>治疗强度削减</t>
-  </si>
-  <si>
-    <t>伤害反弹加成</t>
-  </si>
-  <si>
-    <t>伤害反弹削减</t>
-  </si>
-  <si>
     <t>统一属性价值模型 = 基础价值 + 期望收益 + 条件覆盖率 + 乘区位置 + 边际衰减</t>
   </si>
   <si>
@@ -1158,6 +1170,81 @@
     <t>护符</t>
   </si>
   <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>被动</t>
+  </si>
+  <si>
+    <t>连击气势</t>
+  </si>
+  <si>
+    <t>被动 2 普攻叠风势,每层+5%连击，最高8层</t>
+  </si>
+  <si>
+    <t>被动 2 触发连击时，降敌敌人5%防御，最高6层</t>
+  </si>
+  <si>
+    <t>本回合每触发1段连击，普攻倍率+5%(最高+25%)，下回合重置</t>
+  </si>
+  <si>
+    <t>连击段对随机另一名敌人造成50%溅射伤害</t>
+  </si>
+  <si>
+    <t>风势满层后，每次普攻消耗1层风势，该次普攻倍率+30%</t>
+  </si>
+  <si>
+    <t>小技能</t>
+  </si>
+  <si>
+    <t>迅风击</t>
+  </si>
+  <si>
+    <t>以130%倍率进行一次普攻，命中+1层风势</t>
+  </si>
+  <si>
+    <t>聚风</t>
+  </si>
+  <si>
+    <t>下次普攻倍率+50%(封顶200%)，且首段连击必定触发</t>
+  </si>
+  <si>
+    <t>破甲斩</t>
+  </si>
+  <si>
+    <t>以140%倍率进行一次普攻，命中额外+1层裂甲</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>本次普攻变为列攻击(同列前后排)，倍率100%，连击段仍只打主目标</t>
+  </si>
+  <si>
+    <t>斗战·千连击</t>
+  </si>
+  <si>
+    <t>以150%倍率进行一次普攻，本次连击伤害不衰减，段数上限+1</t>
+  </si>
+  <si>
+    <t>斗战·连环击</t>
+  </si>
+  <si>
+    <t>连续进行3次普攻(每次120%倍率，各自独立判定连击)，每层风势+2%连击率(本技能)</t>
+  </si>
+  <si>
+    <t>以130%倍率进行普攻，命中+1层风势</t>
+  </si>
+  <si>
+    <t>风势滔天</t>
+  </si>
+  <si>
+    <t>进入风势状态2回合：普攻倍率+30%、连击率+10%、连击段带50%溅射；发动时立即追加1次基础普攻</t>
+  </si>
+  <si>
     <t>流派树属性归属</t>
   </si>
   <si>
@@ -1227,27 +1314,122 @@
     <t>物理暴击主属性、反伤主属性</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>弱点洞察</t>
+  </si>
+  <si>
+    <t>基础</t>
+  </si>
+  <si>
+    <t>战斗开始暴击率+10%</t>
+  </si>
+  <si>
+    <t>凶残</t>
+  </si>
+  <si>
+    <t>暴击伤害+20%</t>
+  </si>
+  <si>
+    <t>破绽洞察</t>
+  </si>
+  <si>
+    <t>暴击施加1层破绽(上限3)，每层-5%目标免伤</t>
+  </si>
+  <si>
+    <t>暴击之势</t>
+  </si>
+  <si>
+    <t>进阶</t>
+  </si>
+  <si>
+    <r>
+      <t>暴击后下次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>普攻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害+30%且必定触发1次连击(连击仅普攻可触发)</t>
+    </r>
+  </si>
+  <si>
+    <t>破盾</t>
+  </si>
+  <si>
+    <t>对护盾目标暴击率+20%，护盾伤害+20%</t>
+  </si>
+  <si>
     <t>流派树节点收窄</t>
   </si>
   <si>
+    <t>斩杀</t>
+  </si>
+  <si>
+    <t>目标气血&lt;30%时暴击伤害+50%</t>
+  </si>
+  <si>
+    <t>无情</t>
+  </si>
+  <si>
+    <t>暴击无视10%防御</t>
+  </si>
+  <si>
     <t>节点类型</t>
   </si>
   <si>
     <t>作用</t>
   </si>
   <si>
+    <t>会心</t>
+  </si>
+  <si>
+    <t>暴击溢出转化提升至每1%转0.8%暴伤</t>
+  </si>
+  <si>
     <t>小节点</t>
   </si>
   <si>
     <t>只给本流派相关属性</t>
   </si>
   <si>
+    <t>破军</t>
+  </si>
+  <si>
+    <t>终极</t>
+  </si>
+  <si>
+    <t>攻击破绽目标附加目标10%最大气血真伤(单次上限自身攻击150%，Boss减半)</t>
+  </si>
+  <si>
     <t>中节点</t>
   </si>
   <si>
     <t>强化本流派机制</t>
   </si>
   <si>
+    <t>天崩</t>
+  </si>
+  <si>
+    <t>每回合首次攻击必定暴击；溢出伤害(超出目标剩余气血部分)30%溅射其他敌人真伤</t>
+  </si>
+  <si>
     <t>大节点</t>
   </si>
   <si>
@@ -1260,25 +1442,169 @@
     <t>提供流派质变，但不给最终乘区</t>
   </si>
   <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
     <t>例如：</t>
   </si>
   <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>单体</t>
+  </si>
+  <si>
+    <t>130%伤害，本次暴击率+20%</t>
+  </si>
+  <si>
     <t>终极节点示例</t>
   </si>
   <si>
+    <t>破绽斩</t>
+  </si>
+  <si>
+    <t>150%伤害，暴击时额外+1层破绽</t>
+  </si>
+  <si>
     <t>连击第3段后附加破甲，独立伤害+10%</t>
   </si>
   <si>
+    <t>弱点刺</t>
+  </si>
+  <si>
+    <t>100%伤害，命中必定施加1层破绽(无需暴击)</t>
+  </si>
+  <si>
     <t>暴击后目标获得破绽，暴伤独立+15%</t>
   </si>
   <si>
+    <t>碎盾斩</t>
+  </si>
+  <si>
+    <t>140%伤害，护盾伤害+50%，暴击时击破目标护盾</t>
+  </si>
+  <si>
     <t>护盾破碎后获得怒目，反伤独立+30%</t>
   </si>
   <si>
+    <t>灭魂一击</t>
+  </si>
+  <si>
+    <t>气血最低</t>
+  </si>
+  <si>
+    <t>160%伤害，暴击率+15%(收割)</t>
+  </si>
+  <si>
     <t>闪避成功后下次反击必中并致盲</t>
   </si>
   <si>
+    <t>怒斩</t>
+  </si>
+  <si>
+    <t>120%伤害，消耗目标破绽，每层+20%伤害</t>
+  </si>
+  <si>
     <t>五行异常触发率+10%，异常目标受五行伤害独立+12%</t>
+  </si>
+  <si>
+    <t>破阵斩</t>
+  </si>
+  <si>
+    <t>列攻击</t>
+  </si>
+  <si>
+    <t>同列前后排110%伤害，本技能暴击率+15%</t>
+  </si>
+  <si>
+    <t>袭后斩</t>
+  </si>
+  <si>
+    <t>切后</t>
+  </si>
+  <si>
+    <t>无视前排保护130%伤害，目标暴露时暴伤+25%</t>
+  </si>
+  <si>
+    <t>穿甲刺</t>
+  </si>
+  <si>
+    <t>110%伤害，施加1层裂甲(-5%防御)</t>
+  </si>
+  <si>
+    <t>嗜血斩</t>
+  </si>
+  <si>
+    <t>130%伤害，暴击时吸血本次伤害50%</t>
+  </si>
+  <si>
+    <t>破军·天崩</t>
+  </si>
+  <si>
+    <t>250%伤害，必定暴击，暴击+2层破绽</t>
+  </si>
+  <si>
+    <t>破军·屠戮</t>
+  </si>
+  <si>
+    <t>全体</t>
+  </si>
+  <si>
+    <t>150%伤害，本次暴击率+40%；暴击且目标&lt;30%血直接斩杀(Boss免疫)</t>
+  </si>
+  <si>
+    <t>破军·破绽爆</t>
+  </si>
+  <si>
+    <t>200%伤害，消耗全部破绽每层+40%伤害；消耗≥3层时目标眩晕1回合(Boss抗性生效)</t>
+  </si>
+  <si>
+    <t>破军·碎盾军</t>
+  </si>
+  <si>
+    <t>140%伤害，护盾伤害+100%，暴击时击破目标护盾</t>
+  </si>
+  <si>
+    <t>破军·处刑闪</t>
+  </si>
+  <si>
+    <t>280%伤害，击杀目标时立即获得1次额外行动(每场1次)</t>
+  </si>
+  <si>
+    <t>破军·弱点灭</t>
+  </si>
+  <si>
+    <t>300%伤害，无视30%防御，目标每1%免伤转1%本次暴伤</t>
+  </si>
+  <si>
+    <t>破军·杀意域</t>
+  </si>
+  <si>
+    <t>领域</t>
+  </si>
+  <si>
+    <t>2回合：敌方全体受暴伤+15%，斩杀线提升至40%</t>
+  </si>
+  <si>
+    <t>破军·崩天击</t>
+  </si>
+  <si>
+    <t>320%伤害，溢出伤害50%溅射其他敌人真伤</t>
+  </si>
+  <si>
+    <t>破军·必杀</t>
+  </si>
+  <si>
+    <t>220%伤害，本次暴击伤害+100%</t>
+  </si>
+  <si>
+    <t>破军·灭绝</t>
+  </si>
+  <si>
+    <t>160%伤害，消耗全体目标破绽，每层追加1段60%攻击(上限+3段)</t>
   </si>
   <si>
     <t>宠物属性收窄</t>
@@ -1647,11 +1973,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1669,13 +1999,13 @@
       <sz val="10"/>
       <color rgb="FFF2858C"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1686,21 +2016,351 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1708,13 +2368,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1723,6 +2625,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -1739,7 +2644,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1751,162 +2656,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1917,7 +2750,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1945,40 +2778,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2228,32 +3175,32 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="D16:Z63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="31.109375" customWidth="1"/>
-    <col min="10" max="13" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="31.1083333333333" customWidth="1"/>
+    <col min="10" max="13" width="16.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D16" s="9"/>
-    </row>
-    <row r="31" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H31" s="12" t="s">
+    <row r="16" spans="4:4">
+      <c r="D16" s="10"/>
+    </row>
+    <row r="31" spans="8:26">
+      <c r="H31" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
       <c r="S31" t="s">
         <v>1</v>
       </c>
@@ -2279,20 +3226,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H32" s="10" t="s">
+    <row r="32" spans="8:26">
+      <c r="H32" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J32" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L32" s="10"/>
+      <c r="L32" s="11"/>
       <c r="S32" t="s">
         <v>13</v>
       </c>
@@ -2318,7 +3265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:26">
       <c r="H33" t="s">
         <v>16</v>
       </c>
@@ -2356,7 +3303,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:26">
       <c r="H34" t="s">
         <v>22</v>
       </c>
@@ -2394,7 +3341,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:26">
       <c r="H35" t="s">
         <v>26</v>
       </c>
@@ -2432,7 +3379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="8:26">
       <c r="H36" t="s">
         <v>31</v>
       </c>
@@ -2470,7 +3417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:26">
       <c r="H37" t="s">
         <v>36</v>
       </c>
@@ -2508,32 +3455,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H39" s="12" t="s">
+    <row r="39" spans="8:26">
+      <c r="H39" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-    </row>
-    <row r="40" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H40" s="10" t="s">
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="8:26">
+      <c r="H40" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="K40" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="10"/>
-    </row>
-    <row r="41" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" spans="8:26">
       <c r="H41" t="s">
         <v>41</v>
       </c>
@@ -2547,7 +3494,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="8:26">
       <c r="H42" t="s">
         <v>45</v>
       </c>
@@ -2561,7 +3508,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="8:26">
       <c r="H43" t="s">
         <v>47</v>
       </c>
@@ -2575,7 +3522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:26">
       <c r="H44" t="s">
         <v>51</v>
       </c>
@@ -2589,7 +3536,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="8:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:26">
       <c r="H45" t="s">
         <v>54</v>
       </c>
@@ -2603,32 +3550,32 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H47" s="12" t="s">
+    <row r="47" spans="8:26">
+      <c r="H47" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-    </row>
-    <row r="48" spans="8:26" x14ac:dyDescent="0.25">
-      <c r="H48" s="10" t="s">
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="8:26">
+      <c r="H48" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="I48" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J48" s="10" t="s">
+      <c r="J48" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" spans="8:13">
       <c r="H49" t="s">
         <v>59</v>
       </c>
@@ -2642,7 +3589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="8:13">
       <c r="H50" t="s">
         <v>62</v>
       </c>
@@ -2656,7 +3603,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="8:13">
       <c r="H51" t="s">
         <v>66</v>
       </c>
@@ -2670,7 +3617,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="8:13">
       <c r="H52" t="s">
         <v>67</v>
       </c>
@@ -2684,32 +3631,32 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H54" s="12" t="s">
+    <row r="54" spans="8:13">
+      <c r="H54" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-    </row>
-    <row r="55" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H55" s="10" t="s">
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+    </row>
+    <row r="55" spans="8:13">
+      <c r="H55" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J55" s="10" t="s">
+      <c r="J55" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="10"/>
-    </row>
-    <row r="56" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="L55" s="11"/>
+    </row>
+    <row r="56" spans="8:13">
       <c r="H56" t="s">
         <v>69</v>
       </c>
@@ -2723,7 +3670,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="8:13">
       <c r="H57" t="s">
         <v>72</v>
       </c>
@@ -2737,31 +3684,31 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H59" s="12" t="s">
+    <row r="59" spans="8:13">
+      <c r="H59" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="12"/>
-      <c r="M59" s="12"/>
-    </row>
-    <row r="60" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H60" s="10" t="s">
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="8:13">
+      <c r="H60" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J60" s="10" t="s">
+      <c r="J60" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="K60" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="8:13">
       <c r="H61" t="s">
         <v>77</v>
       </c>
@@ -2775,7 +3722,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="8:13">
       <c r="H62" t="s">
         <v>79</v>
       </c>
@@ -2789,7 +3736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="8:13">
       <c r="H63" t="s">
         <v>82</v>
       </c>
@@ -2811,31 +3758,32 @@
     <mergeCell ref="H54:M54"/>
     <mergeCell ref="H59:M59"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A2:O108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
-    <col min="3" max="3" width="40.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625"/>
-    <col min="10" max="16" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.775" customWidth="1"/>
+    <col min="3" max="3" width="40.8833333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.8833333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="12.6666666666667"/>
+    <col min="10" max="16" width="10.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -2846,107 +3794,107 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>273</v>
+    <row r="3" spans="1:15">
+      <c r="A3" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
         <v>88</v>
       </c>
       <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" t="s">
         <v>91</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s">
         <v>93</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" t="s">
         <v>97</v>
       </c>
-      <c r="H3" t="s">
+      <c r="F4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" t="s">
         <v>99</v>
       </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
         <v>104</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" t="s">
         <v>106</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G4" t="s">
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="s">
         <v>110</v>
       </c>
-      <c r="H4" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" t="s">
-        <v>124</v>
-      </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>283</v>
+        <v>111</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
@@ -2956,14 +3904,14 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>285</v>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
@@ -2975,82 +3923,82 @@
         <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
-      </c>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
+        <v>114</v>
+      </c>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>275</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+        <v>118</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="O10" s="6"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="F11" t="s">
-        <v>153</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
+        <v>122</v>
+      </c>
+      <c r="J11" s="9"/>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>277</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="J13" s="8"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J13" s="9"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
-      <c r="J14" s="8"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J14" s="9"/>
+      <c r="O14" s="6"/>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
@@ -3060,18 +4008,18 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="J15" s="8"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>291</v>
+      <c r="J15" s="9"/>
+      <c r="O15" s="6"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -3080,46 +4028,46 @@
         <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="G16" t="s">
-        <v>163</v>
-      </c>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+        <v>128</v>
+      </c>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>165</v>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+        <v>129</v>
+      </c>
+      <c r="J17" s="9"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>277</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
-      </c>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2" t="s">
-        <v>292</v>
+        <v>131</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
@@ -3129,14 +4077,14 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>293</v>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
         <v>59</v>
@@ -3150,39 +4098,39 @@
       <c r="F21" t="s">
         <v>67</v>
       </c>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
       </c>
       <c r="G22" t="s">
-        <v>202</v>
-      </c>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>294</v>
+        <v>137</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
@@ -3192,14 +4140,14 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="J24" s="8"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>295</v>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
         <v>69</v>
@@ -3207,31 +4155,31 @@
       <c r="D25" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="8"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="J26" s="8"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2" t="s">
-        <v>296</v>
+        <v>139</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>297</v>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
         <v>77</v>
@@ -3240,34 +4188,34 @@
         <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>298</v>
+        <v>141</v>
       </c>
       <c r="F28" t="s">
-        <v>299</v>
-      </c>
-      <c r="J28" s="8"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
+        <v>142</v>
+      </c>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>275</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>300</v>
-      </c>
-      <c r="J29" s="8"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="J30" s="8"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2" t="s">
-        <v>301</v>
+        <v>144</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>9</v>
@@ -3277,31 +4225,31 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="J31" s="8"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>302</v>
+      <c r="J31" s="9"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>275</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>303</v>
-      </c>
-      <c r="J32" s="8"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
+        <v>146</v>
+      </c>
+      <c r="J32" s="9"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J33" s="9"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>304</v>
+        <v>147</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>9</v>
@@ -3311,416 +4259,416 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J34" s="9"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>305</v>
+        <v>148</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>306</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>307</v>
+        <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>308</v>
+        <v>151</v>
       </c>
       <c r="F35" t="s">
-        <v>309</v>
-      </c>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" t="s">
-        <v>310</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>311</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>312</v>
+        <v>155</v>
       </c>
       <c r="F36" t="s">
-        <v>313</v>
-      </c>
-      <c r="J36" s="8"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="J36" s="9"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" t="s">
-        <v>314</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>315</v>
-      </c>
-      <c r="J37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="J38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J39" s="8"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J38" s="9"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="J39" s="9"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="E40" t="s">
-        <v>87</v>
-      </c>
-      <c r="J40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="J40" s="9"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>88</v>
       </c>
       <c r="B41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" t="s">
+        <v>164</v>
+      </c>
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
         <v>89</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B42" t="s">
+        <v>163</v>
+      </c>
+      <c r="C42" t="s">
+        <v>165</v>
+      </c>
+      <c r="J42" s="9"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
         <v>90</v>
       </c>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" t="s">
+        <v>166</v>
+      </c>
+      <c r="J43" s="9"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
         <v>91</v>
       </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B44" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" t="s">
+        <v>167</v>
+      </c>
+      <c r="I44" t="s">
+        <v>168</v>
+      </c>
+      <c r="J44" s="9"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
         <v>92</v>
       </c>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B45" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" t="s">
+        <v>169</v>
+      </c>
+      <c r="I45" t="s">
+        <v>170</v>
+      </c>
+      <c r="J45" s="9"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
         <v>93</v>
       </c>
-      <c r="B43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>94</v>
-      </c>
-      <c r="J43" s="8"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46" t="s">
+        <v>171</v>
+      </c>
+      <c r="I46" t="s">
+        <v>172</v>
+      </c>
+      <c r="J46" s="9"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
         <v>95</v>
       </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B47" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>175</v>
+      </c>
+      <c r="J47" s="9"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
         <v>96</v>
       </c>
-      <c r="I44" t="s">
+      <c r="B48" t="s">
         <v>173</v>
       </c>
-      <c r="J44" s="8"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="C48" t="s">
+        <v>176</v>
+      </c>
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>177</v>
+      </c>
+      <c r="J48" s="9"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
         <v>97</v>
       </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B49" t="s">
+        <v>173</v>
+      </c>
+      <c r="C49" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>175</v>
+      </c>
+      <c r="J49" s="9"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
         <v>98</v>
       </c>
-      <c r="I45" t="s">
+      <c r="B50" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" t="s">
         <v>179</v>
       </c>
-      <c r="J45" s="8"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>175</v>
+      </c>
+      <c r="J50" s="9"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
         <v>99</v>
       </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B51" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>175</v>
+      </c>
+      <c r="J51" s="9"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
         <v>100</v>
       </c>
-      <c r="I46" t="s">
+      <c r="B52" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>175</v>
+      </c>
+      <c r="J52" s="9"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J53" s="9"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>183</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J54" s="9"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J55" s="9"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" t="s">
         <v>185</v>
       </c>
-      <c r="J46" s="8"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="3">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="D56" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I56" t="s">
+        <v>170</v>
+      </c>
+      <c r="J56" s="9"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I57" t="s">
+        <v>170</v>
+      </c>
+      <c r="J57" s="9"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
         <v>187</v>
       </c>
-      <c r="J47" s="8"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>104</v>
-      </c>
-      <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="3">
-        <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>192</v>
-      </c>
-      <c r="J48" s="8"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" s="3">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>187</v>
-      </c>
-      <c r="J49" s="8"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D58" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I58" t="s">
+        <v>170</v>
+      </c>
+      <c r="J58" s="9"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="3">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>187</v>
-      </c>
-      <c r="J50" s="8"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B59" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J59" s="9"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
         <v>110</v>
       </c>
-      <c r="B51" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" s="3">
-        <v>1</v>
-      </c>
-      <c r="I51" t="s">
-        <v>187</v>
-      </c>
-      <c r="J51" s="8"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52" s="3">
-        <v>1</v>
-      </c>
-      <c r="I52" t="s">
-        <v>187</v>
-      </c>
-      <c r="J52" s="8"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>114</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" s="3">
+      <c r="B60" t="s">
+        <v>173</v>
+      </c>
+      <c r="C60" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" s="4">
         <v>0.6</v>
       </c>
-      <c r="J53" s="8"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>116</v>
-      </c>
-      <c r="B54" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J54" s="8"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>118</v>
-      </c>
-      <c r="B55" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J55" s="8"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>120</v>
-      </c>
-      <c r="B56" t="s">
-        <v>102</v>
-      </c>
-      <c r="C56" t="s">
-        <v>121</v>
-      </c>
-      <c r="D56" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="I56" t="s">
-        <v>179</v>
-      </c>
-      <c r="J56" s="8"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>122</v>
-      </c>
-      <c r="B57" t="s">
-        <v>102</v>
-      </c>
-      <c r="C57" t="s">
-        <v>123</v>
-      </c>
-      <c r="D57" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="I57" t="s">
-        <v>179</v>
-      </c>
-      <c r="J57" s="8"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>124</v>
-      </c>
-      <c r="B58" t="s">
-        <v>102</v>
-      </c>
-      <c r="C58" t="s">
-        <v>125</v>
-      </c>
-      <c r="D58" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="I58" t="s">
-        <v>179</v>
-      </c>
-      <c r="J58" s="8"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" t="s">
-        <v>127</v>
-      </c>
-      <c r="D59" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J59" s="8"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C60" t="s">
-        <v>129</v>
-      </c>
-      <c r="D60" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="J60" s="8"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J60" s="9"/>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>130</v>
-      </c>
-      <c r="D61" s="3">
+        <v>190</v>
+      </c>
+      <c r="D61" s="4">
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
@@ -3729,25 +4677,25 @@
         <v>39</v>
       </c>
       <c r="H61" t="s">
-        <v>132</v>
-      </c>
-      <c r="J61" s="8"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="J61" s="9"/>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>133</v>
-      </c>
-      <c r="D62" s="3">
+        <v>193</v>
+      </c>
+      <c r="D62" s="4">
         <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -3756,935 +4704,936 @@
         <v>39</v>
       </c>
       <c r="I62" t="s">
-        <v>179</v>
-      </c>
-      <c r="J62" s="8"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="J62" s="9"/>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
-      </c>
-      <c r="D63" s="3">
+        <v>194</v>
+      </c>
+      <c r="D63" s="4">
         <v>1.2</v>
       </c>
       <c r="E63" t="s">
-        <v>131</v>
-      </c>
-      <c r="J63" s="8"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="J63" s="9"/>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C64" t="s">
-        <v>136</v>
-      </c>
-      <c r="D64" s="3">
+        <v>195</v>
+      </c>
+      <c r="D64" s="4">
         <v>0.8</v>
       </c>
-      <c r="J64" s="8"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J64" s="9"/>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C65" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="D65">
         <v>1000</v>
       </c>
       <c r="I65" t="s">
-        <v>179</v>
-      </c>
-      <c r="J65" s="8"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="J65" s="9"/>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C66" t="s">
-        <v>140</v>
-      </c>
-      <c r="D66" s="3">
+        <v>197</v>
+      </c>
+      <c r="D66" s="4">
         <v>1.5</v>
       </c>
-      <c r="J66" s="8"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J66" s="9"/>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="B67" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>142</v>
-      </c>
-      <c r="D67" s="3">
+        <v>198</v>
+      </c>
+      <c r="D67" s="4">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>238</v>
-      </c>
-      <c r="J67" s="8"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+      <c r="J67" s="9"/>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
-      </c>
-      <c r="D68" s="3">
+        <v>200</v>
+      </c>
+      <c r="D68" s="4">
         <v>0.5</v>
       </c>
-      <c r="J68" s="8"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J68" s="9"/>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="B69" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C69" t="s">
-        <v>146</v>
-      </c>
-      <c r="D69" s="3">
+        <v>201</v>
+      </c>
+      <c r="D69" s="4">
         <v>1.5</v>
       </c>
       <c r="I69" t="s">
-        <v>179</v>
-      </c>
-      <c r="J69" s="8"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="J69" s="9"/>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
-      </c>
-      <c r="D70" s="3">
+        <v>202</v>
+      </c>
+      <c r="D70" s="4">
         <v>1.5</v>
       </c>
-      <c r="J70" s="8"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J70" s="9"/>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="B71" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C71" t="s">
-        <v>150</v>
-      </c>
-      <c r="D71" s="3">
+        <v>203</v>
+      </c>
+      <c r="D71" s="4">
         <v>1.5</v>
       </c>
       <c r="I71" t="s">
-        <v>179</v>
-      </c>
-      <c r="J71" s="8"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="J71" s="9"/>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
-      </c>
-      <c r="D72" s="3">
+        <v>204</v>
+      </c>
+      <c r="D72" s="4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="B73" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>154</v>
-      </c>
-      <c r="D73" s="3">
+        <v>205</v>
+      </c>
+      <c r="D73" s="4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="B74" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C74" t="s">
-        <v>156</v>
-      </c>
-      <c r="D74" s="3">
+        <v>206</v>
+      </c>
+      <c r="D74" s="4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="C75" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C76" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="3">
+        <v>208</v>
+      </c>
+      <c r="D76" s="4">
         <v>0.6</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C77" t="s">
-        <v>160</v>
-      </c>
-      <c r="D77" s="3">
+        <v>209</v>
+      </c>
+      <c r="D77" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="B78" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
-      </c>
-      <c r="D78" s="3">
+        <v>210</v>
+      </c>
+      <c r="D78" s="4">
         <v>0.2</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
+        <v>128</v>
+      </c>
+      <c r="B79" t="s">
         <v>163</v>
       </c>
-      <c r="B79" t="s">
-        <v>89</v>
-      </c>
       <c r="C79" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="D79">
         <v>500</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
-      </c>
-      <c r="D80" s="3">
+        <v>212</v>
+      </c>
+      <c r="D80" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C81" t="s">
-        <v>168</v>
-      </c>
-      <c r="D81" s="3">
+        <v>213</v>
+      </c>
+      <c r="D81" s="4">
         <v>0.4</v>
       </c>
       <c r="E81" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="F81" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="G81" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="H81" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
-      </c>
-      <c r="D82" s="3">
+        <v>218</v>
+      </c>
+      <c r="D82" s="4">
         <v>0.5</v>
       </c>
       <c r="E82" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F82" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G82" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="H82" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>180</v>
-      </c>
-      <c r="D83" s="3">
+        <v>223</v>
+      </c>
+      <c r="D83" s="4">
         <v>0.5</v>
       </c>
       <c r="E83" t="s">
-        <v>181</v>
+        <v>224</v>
       </c>
       <c r="F83" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="G83" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="H83" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
-        <v>186</v>
-      </c>
-      <c r="D84" s="3">
-        <v>0.55000000000000004</v>
+        <v>228</v>
+      </c>
+      <c r="D84" s="4">
+        <v>0.55</v>
       </c>
       <c r="E84" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="F84" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="H84" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C85" t="s">
-        <v>188</v>
-      </c>
-      <c r="D85" s="3">
+        <v>229</v>
+      </c>
+      <c r="D85" s="4">
         <v>0.92</v>
       </c>
       <c r="E85" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="F85" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="G85" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="H85" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="B86" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>194</v>
-      </c>
-      <c r="D86" s="3">
+        <v>233</v>
+      </c>
+      <c r="D86" s="4">
         <v>0.62</v>
       </c>
       <c r="E86" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F86" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="G86" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="H86" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C87" t="s">
-        <v>198</v>
-      </c>
-      <c r="D87" s="3">
+        <v>236</v>
+      </c>
+      <c r="D87" s="4">
         <v>0.62</v>
       </c>
       <c r="E87" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F87" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="G87" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="H87" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
-      </c>
-      <c r="D88" s="3">
+        <v>237</v>
+      </c>
+      <c r="D88" s="4">
         <v>0.62</v>
       </c>
       <c r="E88" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F88" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="G88" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="H88" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>54</v>
       </c>
       <c r="B89" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C89" t="s">
-        <v>201</v>
-      </c>
-      <c r="D89" s="3">
+        <v>238</v>
+      </c>
+      <c r="D89" s="4">
         <v>0.62</v>
       </c>
       <c r="E89" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F89" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="G89" t="s">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="H89" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C90" t="s">
-        <v>203</v>
-      </c>
-      <c r="D90" s="3">
+        <v>239</v>
+      </c>
+      <c r="D90" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C91" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>72</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C92" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="B93" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C93" t="s">
-        <v>207</v>
-      </c>
-      <c r="D93" s="3">
+        <v>243</v>
+      </c>
+      <c r="D93" s="4">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F93" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G93" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="H93" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="B94" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C94" t="s">
-        <v>209</v>
-      </c>
-      <c r="D94" s="3">
+        <v>245</v>
+      </c>
+      <c r="D94" s="4">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F94" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G94" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="H94" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="B95" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
-      </c>
-      <c r="D95" s="3">
+        <v>247</v>
+      </c>
+      <c r="D95" s="4">
         <v>0.5</v>
       </c>
       <c r="E95" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="F95" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G95" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="H95" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="B96" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="C96" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="D96">
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C97" t="s">
-        <v>216</v>
-      </c>
-      <c r="D97" s="3">
+        <v>252</v>
+      </c>
+      <c r="D97" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C98" t="s">
-        <v>218</v>
-      </c>
-      <c r="D98" s="3">
+        <v>254</v>
+      </c>
+      <c r="D98" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="C99" t="s">
+        <v>256</v>
+      </c>
+      <c r="D99" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E99" t="s">
+        <v>248</v>
+      </c>
+      <c r="F99" t="s">
         <v>220</v>
       </c>
-      <c r="D99" s="3">
+      <c r="G99" t="s">
+        <v>221</v>
+      </c>
+      <c r="H99" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>257</v>
+      </c>
+      <c r="B100" t="s">
+        <v>173</v>
+      </c>
+      <c r="C100" t="s">
+        <v>258</v>
+      </c>
+      <c r="D100" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>259</v>
+      </c>
+      <c r="B101" t="s">
+        <v>173</v>
+      </c>
+      <c r="C101" t="s">
+        <v>260</v>
+      </c>
+      <c r="D101" s="4">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>261</v>
+      </c>
+      <c r="F101" t="s">
+        <v>262</v>
+      </c>
+      <c r="G101" t="s">
+        <v>227</v>
+      </c>
+      <c r="H101" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>264</v>
+      </c>
+      <c r="B102" t="s">
+        <v>173</v>
+      </c>
+      <c r="C102" t="s">
+        <v>265</v>
+      </c>
+      <c r="D102" s="4">
         <v>0.5</v>
       </c>
-      <c r="E99" t="s">
-        <v>212</v>
-      </c>
-      <c r="F99" t="s">
-        <v>176</v>
-      </c>
-      <c r="G99" t="s">
-        <v>177</v>
-      </c>
-      <c r="H99" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="E102" t="s">
+        <v>248</v>
+      </c>
+      <c r="F102" t="s">
+        <v>220</v>
+      </c>
+      <c r="G102" t="s">
         <v>221</v>
       </c>
-      <c r="B100" t="s">
-        <v>102</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="H102" t="s">
         <v>222</v>
       </c>
-      <c r="D100" s="3">
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>266</v>
+      </c>
+      <c r="B103" t="s">
+        <v>173</v>
+      </c>
+      <c r="C103" t="s">
+        <v>267</v>
+      </c>
+      <c r="D103" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B104" t="s">
+        <v>173</v>
+      </c>
+      <c r="C104" t="s">
+        <v>269</v>
+      </c>
+      <c r="D104" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E104" t="s">
+        <v>270</v>
+      </c>
+      <c r="F104" t="s">
+        <v>271</v>
+      </c>
+      <c r="G104" t="s">
+        <v>272</v>
+      </c>
+      <c r="H104" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>274</v>
+      </c>
+      <c r="B105" t="s">
+        <v>173</v>
+      </c>
+      <c r="C105" t="s">
+        <v>275</v>
+      </c>
+      <c r="D105" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>223</v>
-      </c>
-      <c r="B101" t="s">
-        <v>102</v>
-      </c>
-      <c r="C101" t="s">
-        <v>224</v>
-      </c>
-      <c r="D101" s="3">
+      <c r="E105" t="s">
+        <v>261</v>
+      </c>
+      <c r="F105" t="s">
+        <v>262</v>
+      </c>
+      <c r="G105" t="s">
+        <v>227</v>
+      </c>
+      <c r="H105" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>276</v>
+      </c>
+      <c r="B106" t="s">
+        <v>173</v>
+      </c>
+      <c r="C106" t="s">
+        <v>277</v>
+      </c>
+      <c r="D106" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E106" t="s">
+        <v>248</v>
+      </c>
+      <c r="F106" t="s">
+        <v>220</v>
+      </c>
+      <c r="G106" t="s">
+        <v>221</v>
+      </c>
+      <c r="H106" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>278</v>
+      </c>
+      <c r="B107" t="s">
+        <v>173</v>
+      </c>
+      <c r="C107" t="s">
+        <v>279</v>
+      </c>
+      <c r="D107" s="4">
         <v>1</v>
       </c>
-      <c r="E101" t="s">
-        <v>225</v>
-      </c>
-      <c r="F101" t="s">
-        <v>226</v>
-      </c>
-      <c r="G101" t="s">
-        <v>184</v>
-      </c>
-      <c r="H101" t="s">
+      <c r="E107" t="s">
+        <v>261</v>
+      </c>
+      <c r="F107" t="s">
+        <v>262</v>
+      </c>
+      <c r="G107" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>228</v>
-      </c>
-      <c r="B102" t="s">
-        <v>102</v>
-      </c>
-      <c r="C102" t="s">
-        <v>229</v>
-      </c>
-      <c r="D102" s="3">
+      <c r="H107" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>280</v>
+      </c>
+      <c r="B108" t="s">
+        <v>173</v>
+      </c>
+      <c r="C108" t="s">
+        <v>281</v>
+      </c>
+      <c r="D108" s="4">
         <v>0.5</v>
       </c>
-      <c r="E102" t="s">
-        <v>212</v>
-      </c>
-      <c r="F102" t="s">
-        <v>176</v>
-      </c>
-      <c r="G102" t="s">
-        <v>177</v>
-      </c>
-      <c r="H102" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>230</v>
-      </c>
-      <c r="B103" t="s">
-        <v>102</v>
-      </c>
-      <c r="C103" t="s">
-        <v>231</v>
-      </c>
-      <c r="D103" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>232</v>
-      </c>
-      <c r="B104" t="s">
-        <v>102</v>
-      </c>
-      <c r="C104" t="s">
-        <v>233</v>
-      </c>
-      <c r="D104" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E104" t="s">
-        <v>234</v>
-      </c>
-      <c r="F104" t="s">
-        <v>235</v>
-      </c>
-      <c r="G104" t="s">
-        <v>236</v>
-      </c>
-      <c r="H104" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>239</v>
-      </c>
-      <c r="B105" t="s">
-        <v>102</v>
-      </c>
-      <c r="C105" t="s">
-        <v>240</v>
-      </c>
-      <c r="D105" s="3">
-        <v>1</v>
-      </c>
-      <c r="E105" t="s">
-        <v>225</v>
-      </c>
-      <c r="F105" t="s">
-        <v>226</v>
-      </c>
-      <c r="G105" t="s">
-        <v>184</v>
-      </c>
-      <c r="H105" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>241</v>
-      </c>
-      <c r="B106" t="s">
-        <v>102</v>
-      </c>
-      <c r="C106" t="s">
-        <v>242</v>
-      </c>
-      <c r="D106" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E106" t="s">
-        <v>212</v>
-      </c>
-      <c r="F106" t="s">
-        <v>176</v>
-      </c>
-      <c r="G106" t="s">
-        <v>177</v>
-      </c>
-      <c r="H106" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>243</v>
-      </c>
-      <c r="B107" t="s">
-        <v>102</v>
-      </c>
-      <c r="C107" t="s">
-        <v>244</v>
-      </c>
-      <c r="D107" s="3">
-        <v>1</v>
-      </c>
-      <c r="E107" t="s">
-        <v>225</v>
-      </c>
-      <c r="F107" t="s">
-        <v>226</v>
-      </c>
-      <c r="G107" t="s">
-        <v>184</v>
-      </c>
-      <c r="H107" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>245</v>
-      </c>
-      <c r="B108" t="s">
-        <v>102</v>
-      </c>
-      <c r="C108" t="s">
-        <v>246</v>
-      </c>
-      <c r="D108" s="3">
-        <v>0.5</v>
-      </c>
       <c r="E108" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="F108" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G108" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="H108" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A32:A33"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A33"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AB207"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="7" width="12.6640625" customWidth="1"/>
+    <col min="1" max="7" width="12.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -4692,53 +5641,53 @@
         <v>50</v>
       </c>
       <c r="O1" t="s">
-        <v>247</v>
+        <v>85</v>
       </c>
       <c r="P1" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="Q1" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="R1" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="S1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="12"/>
+        <v>285</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="2"/>
       <c r="D2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F2" s="12"/>
+        <v>287</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F2" s="2"/>
       <c r="G2" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="O2" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="P2" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="Q2" t="s">
-        <v>257</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>12</v>
       </c>
@@ -4772,27 +5721,27 @@
         <v>103</v>
       </c>
       <c r="O3" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="P3" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="Q3" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="R3" t="s">
-        <v>262</v>
-      </c>
-      <c r="S3" s="11" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C4">
         <v>16</v>
@@ -4801,7 +5750,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F4">
         <v>8</v>
@@ -4810,7 +5759,7 @@
         <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I8" si="0">C4+F4*($B$1-1)</f>
@@ -4821,27 +5770,27 @@
         <v>204</v>
       </c>
       <c r="O4" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="P4" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="Q4" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="R4" t="s">
-        <v>267</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -4850,7 +5799,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4859,7 +5808,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
@@ -4870,24 +5819,24 @@
         <v>103</v>
       </c>
       <c r="O5" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
       </c>
       <c r="Q5" t="s">
-        <v>270</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -4896,7 +5845,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -4905,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
@@ -4918,12 +5867,12 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -4932,7 +5881,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -4941,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
@@ -4954,12 +5903,12 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -4968,7 +5917,7 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -4977,7 +5926,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
@@ -4990,7 +5939,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19">
       <c r="D9">
         <f>SUM(D3:D8)</f>
         <v>33</v>
@@ -5005,28 +5954,28 @@
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="Q13" s="4"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19">
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="D14" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="E14" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q14" s="4"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -5037,190 +5986,190 @@
       <c r="C15">
         <v>120</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="6">
         <f t="shared" ref="D15:D20" si="2">ROUND(C15/$C$21,2)</f>
         <v>0.31</v>
       </c>
       <c r="E15" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="C16">
         <v>120</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="6">
         <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
       <c r="E16" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q16" s="4"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="C17">
         <v>60</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="6">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="E17" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q17" s="4"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="C18">
         <v>30</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="6">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
         <v>35</v>
       </c>
       <c r="C19">
         <v>30</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="6">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
         <v>39</v>
       </c>
       <c r="C20">
         <v>30</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="6">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
       <c r="E20" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q20" s="4"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17">
       <c r="C21">
         <f>SUM(C15:C20)</f>
         <v>390</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17">
       <c r="B22" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C22">
         <f>B15/D15</f>
-        <v>1845.1612903225807</v>
+        <v>1845.16129032258</v>
       </c>
       <c r="Q22" s="2"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17">
       <c r="Q27" s="2"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17">
       <c r="Q31" s="2"/>
     </row>
-    <row r="38" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="17:17">
       <c r="Q38" s="2"/>
     </row>
-    <row r="41" spans="17:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="17:17">
       <c r="Q41" s="2"/>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="12:13">
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="12:13">
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:13">
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:13">
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="12:13">
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:13">
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="12:13">
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="12:13">
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="12:13">
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="12:13">
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="12:13">
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="12:13">
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="12:13">
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="12:13">
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="12:13">
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="12:13">
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="11:28">
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="11:28">
       <c r="L66" s="2" t="s">
         <v>316</v>
       </c>
@@ -5233,22 +6182,22 @@
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
     </row>
-    <row r="67" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="11:28">
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="11:28">
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="11:28">
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="70" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="11:28">
       <c r="M70" s="2" t="s">
         <v>318</v>
       </c>
@@ -5257,7 +6206,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="71" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="11:28">
       <c r="M71" s="2" t="s">
         <v>318</v>
       </c>
@@ -5266,7 +6215,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="72" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="11:28">
       <c r="M72" s="2" t="s">
         <v>318</v>
       </c>
@@ -5275,7 +6224,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="11:28">
       <c r="M73" s="2" t="s">
         <v>318</v>
       </c>
@@ -5284,7 +6233,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="74" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="11:28">
       <c r="M74" s="2" t="s">
         <v>318</v>
       </c>
@@ -5293,7 +6242,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="75" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="11:28">
       <c r="M75" s="2" t="s">
         <v>318</v>
       </c>
@@ -5302,7 +6251,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="76" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="11:28">
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="U76" t="s">
@@ -5321,88 +6270,88 @@
         <v>329</v>
       </c>
     </row>
-    <row r="77" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="11:28">
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
-    <row r="78" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="11:28">
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
-    <row r="79" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="11:28">
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="80" spans="11:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="11:28">
       <c r="K80" t="s">
         <v>331</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="11:20">
       <c r="K81" t="s">
         <v>332</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="11:20">
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="11:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="14.4" customHeight="1" spans="11:20">
       <c r="K83" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="M83" s="2"/>
-      <c r="N83" s="3">
+      <c r="N83" s="4">
         <v>0.5</v>
       </c>
-      <c r="O83" s="6" t="s">
+      <c r="O83" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="P83" s="7"/>
-      <c r="Q83" s="7"/>
-      <c r="R83" s="7"/>
-      <c r="S83" s="7"/>
-      <c r="T83" s="7"/>
-    </row>
-    <row r="84" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="P83" s="8"/>
+      <c r="Q83" s="8"/>
+      <c r="R83" s="8"/>
+      <c r="S83" s="8"/>
+      <c r="T83" s="8"/>
+    </row>
+    <row r="84" spans="11:20">
       <c r="K84" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="11:20">
       <c r="K85" t="s">
         <v>334</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="11:20">
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="11:20">
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="11:20">
       <c r="K88" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -5410,35 +6359,35 @@
         <v>335</v>
       </c>
     </row>
-    <row r="89" spans="11:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="11:20">
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="201" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="12:13">
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
     </row>
-    <row r="202" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="12:13">
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
     </row>
-    <row r="203" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="12:13">
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
     </row>
-    <row r="204" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="12:13">
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
     </row>
-    <row r="205" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="12:13">
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
     </row>
-    <row r="206" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="12:13">
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
     </row>
-    <row r="207" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="12:13">
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
     </row>
@@ -5447,21 +6396,22 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A16:X40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="7" max="12" width="8.6640625" customWidth="1"/>
+    <col min="7" max="12" width="8.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="7:8">
       <c r="G16" t="s">
         <v>336</v>
       </c>
@@ -5469,9 +6419,9 @@
         <v>337</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14">
       <c r="G17" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="H17" t="s">
         <v>338</v>
@@ -5483,7 +6433,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14">
       <c r="G18" t="s">
         <v>341</v>
       </c>
@@ -5497,7 +6447,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14">
       <c r="G19" t="s">
         <v>345</v>
       </c>
@@ -5511,7 +6461,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14">
       <c r="G20" t="s">
         <v>348</v>
       </c>
@@ -5525,17 +6475,17 @@
         <v>351</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14">
       <c r="G21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14">
       <c r="G22" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>353</v>
       </c>
@@ -5552,7 +6502,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>358</v>
       </c>
@@ -5572,7 +6522,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>362</v>
       </c>
@@ -5589,22 +6539,22 @@
         <v>338</v>
       </c>
       <c r="H27" t="s">
-        <v>91</v>
-      </c>
-      <c r="I27" s="3">
+        <v>89</v>
+      </c>
+      <c r="I27" s="4">
         <v>0.85</v>
       </c>
       <c r="J27" t="s">
-        <v>124</v>
-      </c>
-      <c r="K27" s="3">
+        <v>107</v>
+      </c>
+      <c r="K27" s="4">
         <v>0.1</v>
       </c>
       <c r="L27" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>365</v>
       </c>
@@ -5621,22 +6571,22 @@
         <v>339</v>
       </c>
       <c r="H28" t="s">
-        <v>91</v>
-      </c>
-      <c r="I28" s="3">
+        <v>89</v>
+      </c>
+      <c r="I28" s="4">
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
-      </c>
-      <c r="K28" s="3">
+        <v>107</v>
+      </c>
+      <c r="K28" s="4">
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>367</v>
       </c>
@@ -5653,15 +6603,15 @@
         <v>340</v>
       </c>
       <c r="H29" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="3">
-        <v>1.1499999999999999</v>
+        <v>89</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1.15</v>
       </c>
       <c r="J29" t="s">
-        <v>124</v>
-      </c>
-      <c r="K29" s="3">
+        <v>107</v>
+      </c>
+      <c r="K29" s="4">
         <v>-0.1</v>
       </c>
       <c r="L29" t="s">
@@ -5671,7 +6621,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>371</v>
       </c>
@@ -5688,50 +6638,50 @@
         <v>342</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M30" t="s">
         <v>373</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="4">
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14">
       <c r="G31" t="s">
         <v>343</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M31" t="s">
         <v>373</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31" s="4">
         <v>0.13</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14">
       <c r="G32" t="s">
         <v>344</v>
       </c>
       <c r="H32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M32" t="s">
         <v>373</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="4">
         <v>0.16</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+    <row r="33" spans="1:24">
+      <c r="A33" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
       <c r="G33" t="s">
         <v>346</v>
       </c>
@@ -5741,11 +6691,11 @@
       <c r="M33" t="s">
         <v>373</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="4">
         <v>0.06</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24">
       <c r="A34">
         <v>1</v>
       </c>
@@ -5761,11 +6711,11 @@
       <c r="M34" t="s">
         <v>373</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="4">
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24">
       <c r="A35">
         <v>2</v>
       </c>
@@ -5778,11 +6728,11 @@
       <c r="M35" t="s">
         <v>373</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="4">
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5790,10 +6740,10 @@
         <v>349</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
-      </c>
-      <c r="I36" s="3">
-        <v>1.1499999999999999</v>
+        <v>93</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1.15</v>
       </c>
       <c r="J36" t="s">
         <v>62</v>
@@ -5804,11 +6754,11 @@
       <c r="M36" t="s">
         <v>373</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36" s="4">
         <v>0.06</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24">
       <c r="A37">
         <v>4</v>
       </c>
@@ -5816,19 +6766,19 @@
         <v>350</v>
       </c>
       <c r="H37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I37" s="3">
+        <v>93</v>
+      </c>
+      <c r="I37" s="4">
         <v>1</v>
       </c>
       <c r="M37" t="s">
         <v>373</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N37" s="4">
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24">
       <c r="A38">
         <v>5</v>
       </c>
@@ -5836,24 +6786,24 @@
         <v>351</v>
       </c>
       <c r="H38" t="s">
-        <v>99</v>
-      </c>
-      <c r="I38" s="3">
+        <v>93</v>
+      </c>
+      <c r="I38" s="4">
         <v>0.85</v>
       </c>
       <c r="M38" t="s">
         <v>373</v>
       </c>
-      <c r="N38" s="3">
+      <c r="N38" s="4">
         <v>0.1</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24">
       <c r="G39" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24">
       <c r="G40" t="s">
         <v>352</v>
       </c>
@@ -5861,7 +6811,7 @@
         <v>31</v>
       </c>
       <c r="J40" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="N40" t="s">
         <v>16</v>
@@ -5870,376 +6820,988 @@
         <v>22</v>
       </c>
       <c r="R40" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="T40" t="s">
-        <v>306</v>
+        <v>149</v>
       </c>
       <c r="V40" t="s">
-        <v>308</v>
+        <v>151</v>
       </c>
       <c r="X40" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A33:D33"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="K19:N46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:Q63"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="11" max="16" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="63.125" customWidth="1"/>
+    <col min="14" max="19" width="20.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K19" t="s">
+    <row r="1" spans="2:5">
+      <c r="B1" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="21" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K21" t="s">
-        <v>132</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="C1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5">
+      <c r="B2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="E3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="E4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="E6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="E7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" t="s">
+        <v>388</v>
+      </c>
+      <c r="E11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="C12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E12" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="C13" t="s">
+        <v>392</v>
+      </c>
+      <c r="E13" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" t="s">
+        <v>394</v>
+      </c>
+      <c r="E15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E16" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" t="s">
+        <v>386</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="B19" t="s">
+        <v>399</v>
+      </c>
+      <c r="E19" t="s">
+        <v>400</v>
+      </c>
+      <c r="N19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="N21" t="s">
+        <v>192</v>
+      </c>
+      <c r="O21" t="s">
         <v>360</v>
       </c>
-      <c r="M21" t="s">
+      <c r="P21" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="N22" t="s">
+        <v>404</v>
+      </c>
+      <c r="O22" t="s">
+        <v>405</v>
+      </c>
+      <c r="P22" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="N23" t="s">
+        <v>408</v>
+      </c>
+      <c r="O23" t="s">
+        <v>409</v>
+      </c>
+      <c r="P23" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17">
+      <c r="N24" t="s">
+        <v>412</v>
+      </c>
+      <c r="O24" t="s">
+        <v>413</v>
+      </c>
+      <c r="P24" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17">
+      <c r="N25" t="s">
+        <v>416</v>
+      </c>
+      <c r="O25" t="s">
+        <v>417</v>
+      </c>
+      <c r="P25" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="N26" t="s">
+        <v>420</v>
+      </c>
+      <c r="O26" t="s">
+        <v>421</v>
+      </c>
+      <c r="P26" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="B28" t="s">
+        <v>424</v>
+      </c>
+      <c r="C28" t="s">
         <v>377</v>
       </c>
-      <c r="N21" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="22" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K22" t="s">
-        <v>379</v>
-      </c>
-      <c r="L22" t="s">
-        <v>380</v>
-      </c>
-      <c r="M22" t="s">
-        <v>381</v>
-      </c>
-      <c r="N22" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="23" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K23" t="s">
-        <v>383</v>
-      </c>
-      <c r="L23" t="s">
-        <v>384</v>
-      </c>
-      <c r="M23" t="s">
-        <v>385</v>
-      </c>
-      <c r="N23" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="24" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K24" t="s">
-        <v>387</v>
-      </c>
-      <c r="L24" t="s">
-        <v>388</v>
-      </c>
-      <c r="M24" t="s">
-        <v>389</v>
-      </c>
-      <c r="N24" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="25" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K25" t="s">
-        <v>391</v>
-      </c>
-      <c r="L25" t="s">
-        <v>392</v>
-      </c>
-      <c r="M25" t="s">
-        <v>393</v>
-      </c>
-      <c r="N25" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="26" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K26" t="s">
-        <v>395</v>
-      </c>
-      <c r="L26" t="s">
-        <v>396</v>
-      </c>
-      <c r="M26" t="s">
-        <v>397</v>
-      </c>
-      <c r="N26" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="33" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K33" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="35" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K35" t="s">
-        <v>400</v>
-      </c>
-      <c r="L35" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="36" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K36" t="s">
-        <v>402</v>
-      </c>
-      <c r="L36" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="37" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K37" t="s">
+      <c r="D28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>426</v>
+      </c>
+      <c r="D29" t="s">
+        <v>427</v>
+      </c>
+      <c r="E29" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>429</v>
+      </c>
+      <c r="D30" t="s">
+        <v>427</v>
+      </c>
+      <c r="E30" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>431</v>
+      </c>
+      <c r="D31" t="s">
+        <v>427</v>
+      </c>
+      <c r="E31" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="2:17">
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" t="s">
+        <v>434</v>
+      </c>
+      <c r="E32" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>436</v>
+      </c>
+      <c r="D33" t="s">
+        <v>434</v>
+      </c>
+      <c r="E33" t="s">
+        <v>437</v>
+      </c>
+      <c r="N33" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15">
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>439</v>
+      </c>
+      <c r="D34" t="s">
+        <v>434</v>
+      </c>
+      <c r="E34" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>441</v>
+      </c>
+      <c r="D35" t="s">
+        <v>434</v>
+      </c>
+      <c r="E35" t="s">
+        <v>442</v>
+      </c>
+      <c r="N35" t="s">
+        <v>443</v>
+      </c>
+      <c r="O35" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>445</v>
+      </c>
+      <c r="D36" t="s">
+        <v>434</v>
+      </c>
+      <c r="E36" t="s">
+        <v>446</v>
+      </c>
+      <c r="N36" t="s">
+        <v>447</v>
+      </c>
+      <c r="O36" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="B37">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>449</v>
+      </c>
+      <c r="D37" t="s">
+        <v>450</v>
+      </c>
+      <c r="E37" t="s">
+        <v>451</v>
+      </c>
+      <c r="N37" t="s">
+        <v>452</v>
+      </c>
+      <c r="O37" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>454</v>
+      </c>
+      <c r="D38" t="s">
+        <v>450</v>
+      </c>
+      <c r="E38" t="s">
+        <v>455</v>
+      </c>
+      <c r="N38" t="s">
+        <v>456</v>
+      </c>
+      <c r="O38" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="N39" t="s">
+        <v>458</v>
+      </c>
+      <c r="O39" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="B40" t="s">
+        <v>424</v>
+      </c>
+      <c r="C40" t="s">
+        <v>377</v>
+      </c>
+      <c r="D40" t="s">
+        <v>460</v>
+      </c>
+      <c r="E40" t="s">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>425</v>
+      </c>
+      <c r="N40" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>463</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>464</v>
+      </c>
+      <c r="F41" t="s">
+        <v>465</v>
+      </c>
+      <c r="N41" t="s">
+        <v>192</v>
+      </c>
+      <c r="O41" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>467</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>464</v>
+      </c>
+      <c r="F42" t="s">
+        <v>468</v>
+      </c>
+      <c r="N42" t="s">
         <v>404</v>
       </c>
-      <c r="L37" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="38" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K38" t="s">
-        <v>406</v>
-      </c>
-      <c r="L38" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="39" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K39" t="s">
+      <c r="O42" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>470</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>464</v>
+      </c>
+      <c r="F43" t="s">
+        <v>471</v>
+      </c>
+      <c r="N43" t="s">
         <v>408</v>
       </c>
-      <c r="L39" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="40" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K40" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="41" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K41" t="s">
-        <v>132</v>
-      </c>
-      <c r="L41" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="42" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K42" t="s">
-        <v>379</v>
-      </c>
-      <c r="L42" t="s">
+      <c r="O43" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>473</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>464</v>
+      </c>
+      <c r="F44" t="s">
+        <v>474</v>
+      </c>
+      <c r="N44" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="43" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K43" t="s">
-        <v>383</v>
-      </c>
-      <c r="L43" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="44" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K44" t="s">
-        <v>387</v>
-      </c>
-      <c r="L44" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="45" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K45" t="s">
-        <v>391</v>
-      </c>
-      <c r="L45" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="46" spans="11:12" x14ac:dyDescent="0.25">
-      <c r="K46" t="s">
-        <v>395</v>
-      </c>
-      <c r="L46" t="s">
+      <c r="O44" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15">
+      <c r="B45">
+        <v>5</v>
+      </c>
+      <c r="C45" t="s">
+        <v>476</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>477</v>
+      </c>
+      <c r="F45" t="s">
+        <v>478</v>
+      </c>
+      <c r="N45" t="s">
         <v>416</v>
       </c>
+      <c r="O45" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
+      <c r="B46">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>480</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>464</v>
+      </c>
+      <c r="F46" t="s">
+        <v>481</v>
+      </c>
+      <c r="N46" t="s">
+        <v>420</v>
+      </c>
+      <c r="O46" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>483</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>484</v>
+      </c>
+      <c r="F47" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>486</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>487</v>
+      </c>
+      <c r="F48" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>489</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>464</v>
+      </c>
+      <c r="F49" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>491</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>464</v>
+      </c>
+      <c r="F50" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" t="s">
+        <v>424</v>
+      </c>
+      <c r="C53" t="s">
+        <v>377</v>
+      </c>
+      <c r="D53" t="s">
+        <v>460</v>
+      </c>
+      <c r="E53" t="s">
+        <v>461</v>
+      </c>
+      <c r="F53" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>493</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>464</v>
+      </c>
+      <c r="F54" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>495</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>496</v>
+      </c>
+      <c r="F55" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>498</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>464</v>
+      </c>
+      <c r="F56" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>500</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>496</v>
+      </c>
+      <c r="F57" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>502</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>477</v>
+      </c>
+      <c r="F58" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>504</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>464</v>
+      </c>
+      <c r="F59" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>506</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>507</v>
+      </c>
+      <c r="F60" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>509</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61" t="s">
+        <v>464</v>
+      </c>
+      <c r="F61" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>511</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>464</v>
+      </c>
+      <c r="F62" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>513</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>496</v>
+      </c>
+      <c r="F63" t="s">
+        <v>514</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="I11:S40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="11" spans="9:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="9:19">
       <c r="I11" t="s">
-        <v>417</v>
+        <v>515</v>
       </c>
       <c r="K11" t="s">
-        <v>418</v>
+        <v>516</v>
       </c>
       <c r="Q11" t="s">
-        <v>419</v>
+        <v>517</v>
       </c>
       <c r="S11" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="13" spans="9:19" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="9:19">
       <c r="I13" t="s">
-        <v>421</v>
+        <v>519</v>
       </c>
       <c r="J13" t="s">
-        <v>422</v>
+        <v>520</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="Q13" t="s">
-        <v>423</v>
+        <v>521</v>
       </c>
       <c r="R13" t="s">
-        <v>422</v>
+        <v>520</v>
       </c>
       <c r="S13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="9:19" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="9:19">
       <c r="I14" t="s">
-        <v>424</v>
+        <v>522</v>
       </c>
       <c r="J14" t="s">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="K14" t="s">
-        <v>426</v>
+        <v>524</v>
       </c>
       <c r="Q14" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="R14" t="s">
-        <v>427</v>
+        <v>525</v>
       </c>
       <c r="S14" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="15" spans="9:19" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="15" spans="9:19">
       <c r="I15" t="s">
         <v>69</v>
       </c>
       <c r="J15" t="s">
-        <v>427</v>
+        <v>525</v>
       </c>
       <c r="K15" t="s">
-        <v>429</v>
+        <v>527</v>
       </c>
       <c r="Q15" t="s">
         <v>54</v>
       </c>
       <c r="R15" t="s">
-        <v>427</v>
+        <v>525</v>
       </c>
       <c r="S15" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="16" spans="9:19" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="16" spans="9:19">
       <c r="I16" t="s">
         <v>82</v>
       </c>
       <c r="J16" t="s">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="K16" t="s">
-        <v>430</v>
+        <v>528</v>
       </c>
       <c r="Q16" t="s">
         <v>41</v>
       </c>
       <c r="R16" t="s">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="S16" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="17" spans="9:19" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17" spans="9:19">
       <c r="I17" t="s">
-        <v>432</v>
+        <v>530</v>
       </c>
       <c r="J17" t="s">
-        <v>427</v>
+        <v>525</v>
       </c>
       <c r="K17" t="s">
-        <v>433</v>
+        <v>531</v>
       </c>
       <c r="Q17" t="s">
         <v>66</v>
       </c>
       <c r="R17" t="s">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="S17" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="18" spans="9:19" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="18" spans="9:19">
       <c r="I18" t="s">
-        <v>435</v>
+        <v>533</v>
       </c>
       <c r="J18" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="K18" t="s">
-        <v>437</v>
+        <v>535</v>
       </c>
       <c r="Q18" t="s">
         <v>67</v>
       </c>
       <c r="R18" t="s">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="S18" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="19" spans="9:19" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="19" spans="9:19">
       <c r="I19" t="s">
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="K19" t="s">
-        <v>438</v>
+        <v>536</v>
       </c>
       <c r="Q19" t="s">
         <v>62</v>
@@ -6248,18 +7810,18 @@
         <v>21</v>
       </c>
       <c r="S19" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="20" spans="9:19" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="20" spans="9:19">
       <c r="I20" t="s">
-        <v>440</v>
+        <v>538</v>
       </c>
       <c r="J20" t="s">
         <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>441</v>
+        <v>539</v>
       </c>
       <c r="Q20" t="s">
         <v>77</v>
@@ -6268,174 +7830,174 @@
         <v>21</v>
       </c>
       <c r="S20" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="21" spans="9:19" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="21" spans="9:19">
       <c r="I21" t="s">
-        <v>443</v>
+        <v>541</v>
       </c>
       <c r="J21" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="K21" t="s">
-        <v>444</v>
+        <v>542</v>
       </c>
       <c r="Q21" t="s">
-        <v>435</v>
+        <v>533</v>
       </c>
       <c r="R21" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="S21" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="22" spans="9:19" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="22" spans="9:19">
       <c r="Q22" t="s">
         <v>26</v>
       </c>
       <c r="R22" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="S22" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="23" spans="9:19" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="23" spans="9:19">
       <c r="Q23" t="s">
         <v>69</v>
       </c>
       <c r="R23" t="s">
-        <v>436</v>
+        <v>534</v>
       </c>
       <c r="S23" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="25" spans="9:19" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="25" spans="9:19">
       <c r="I25" t="s">
         <v>30</v>
       </c>
       <c r="J25" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
       <c r="Q25" t="s">
-        <v>449</v>
+        <v>547</v>
       </c>
       <c r="R25" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="26" spans="9:19" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="26" spans="9:19">
       <c r="I26" t="s">
-        <v>451</v>
+        <v>549</v>
       </c>
       <c r="J26" t="s">
-        <v>452</v>
+        <v>550</v>
       </c>
       <c r="Q26" t="s">
-        <v>453</v>
+        <v>551</v>
       </c>
       <c r="R26" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="27" spans="9:19" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="27" spans="9:19">
       <c r="I27" t="s">
-        <v>455</v>
+        <v>553</v>
       </c>
       <c r="J27" t="s">
-        <v>456</v>
+        <v>554</v>
       </c>
       <c r="Q27" t="s">
-        <v>457</v>
+        <v>555</v>
       </c>
       <c r="R27" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="28" spans="9:19" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="28" spans="9:19">
       <c r="I28" t="s">
-        <v>459</v>
+        <v>557</v>
       </c>
       <c r="J28" t="s">
-        <v>460</v>
+        <v>558</v>
       </c>
       <c r="Q28" t="s">
-        <v>461</v>
+        <v>559</v>
       </c>
       <c r="R28" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="29" spans="9:19" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="29" spans="9:19">
       <c r="I29" t="s">
-        <v>463</v>
+        <v>561</v>
       </c>
       <c r="J29" t="s">
-        <v>464</v>
+        <v>562</v>
       </c>
       <c r="Q29" t="s">
-        <v>465</v>
+        <v>563</v>
       </c>
       <c r="R29" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="30" spans="9:19" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="30" spans="9:19">
       <c r="I30" t="s">
-        <v>467</v>
+        <v>565</v>
       </c>
       <c r="J30" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="35" spans="9:13">
       <c r="I35" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="36" spans="9:13" ht="15.6" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="9:13">
       <c r="I36" s="1" t="s">
-        <v>470</v>
+        <v>568</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
-      <c r="K36" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-    </row>
-    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K36" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="9:13">
       <c r="I37" t="s">
-        <v>472</v>
+        <v>570</v>
       </c>
       <c r="J37">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:13">
       <c r="I38" t="s">
-        <v>473</v>
+        <v>571</v>
       </c>
       <c r="J38">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:13">
       <c r="I39" t="s">
-        <v>474</v>
+        <v>572</v>
       </c>
       <c r="J39">
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:13">
       <c r="I40" t="s">
-        <v>475</v>
+        <v>573</v>
       </c>
       <c r="J40">
         <v>100</v>
@@ -6445,217 +8007,219 @@
   <mergeCells count="1">
     <mergeCell ref="K36:M36"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="H8:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="8" spans="8:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="8:16">
       <c r="O8" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="10" spans="8:16" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="8:16">
       <c r="H10" t="s">
-        <v>477</v>
+        <v>575</v>
       </c>
       <c r="O10" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="11" spans="8:16" x14ac:dyDescent="0.25">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="8:16">
       <c r="O11" t="s">
-        <v>479</v>
+        <v>577</v>
       </c>
       <c r="P11" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="12" spans="8:16" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="12" spans="8:16">
       <c r="H12" t="s">
-        <v>479</v>
+        <v>577</v>
       </c>
       <c r="I12" t="s">
         <v>360</v>
       </c>
       <c r="J12" t="s">
-        <v>481</v>
+        <v>579</v>
       </c>
       <c r="K12" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="O12" t="s">
-        <v>482</v>
+        <v>580</v>
       </c>
       <c r="P12" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="13" spans="8:16" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="13" spans="8:16">
       <c r="H13" t="s">
-        <v>482</v>
+        <v>580</v>
       </c>
       <c r="I13" t="s">
-        <v>484</v>
+        <v>582</v>
       </c>
       <c r="J13" t="s">
-        <v>485</v>
+        <v>583</v>
       </c>
       <c r="K13" t="s">
-        <v>486</v>
+        <v>584</v>
       </c>
       <c r="O13" t="s">
-        <v>487</v>
+        <v>585</v>
       </c>
       <c r="P13" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="14" spans="8:16" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="8:16">
       <c r="H14" t="s">
-        <v>487</v>
+        <v>585</v>
       </c>
       <c r="I14" t="s">
-        <v>489</v>
+        <v>587</v>
       </c>
       <c r="J14" t="s">
-        <v>490</v>
+        <v>588</v>
       </c>
       <c r="K14" t="s">
-        <v>491</v>
+        <v>589</v>
       </c>
       <c r="O14" t="s">
-        <v>492</v>
+        <v>590</v>
       </c>
       <c r="P14" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="15" spans="8:16" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="15" spans="8:16">
       <c r="H15" t="s">
-        <v>492</v>
+        <v>590</v>
       </c>
       <c r="I15" t="s">
-        <v>494</v>
+        <v>592</v>
       </c>
       <c r="J15" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="K15" t="s">
-        <v>495</v>
+        <v>593</v>
       </c>
       <c r="O15" t="s">
-        <v>496</v>
+        <v>594</v>
       </c>
       <c r="P15" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="16" spans="8:16" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="16" spans="8:16">
       <c r="H16" t="s">
-        <v>496</v>
+        <v>594</v>
       </c>
       <c r="I16" t="s">
-        <v>498</v>
+        <v>596</v>
       </c>
       <c r="J16" t="s">
-        <v>499</v>
+        <v>597</v>
       </c>
       <c r="K16" t="s">
-        <v>500</v>
+        <v>598</v>
       </c>
       <c r="O16" t="s">
-        <v>501</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="J4:R53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="4" spans="10:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="10:18">
       <c r="R4" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="5" spans="10:18" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="10:18">
       <c r="J5" t="s">
-        <v>503</v>
+        <v>601</v>
       </c>
       <c r="R5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="6" spans="10:18" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="6" spans="10:18">
       <c r="J6" t="s">
-        <v>505</v>
+        <v>603</v>
       </c>
       <c r="K6" t="s">
-        <v>506</v>
+        <v>604</v>
       </c>
       <c r="R6" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="7" spans="10:18" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="7" spans="10:18">
       <c r="J7" t="s">
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="8" spans="10:18" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="8" spans="10:18">
       <c r="J8" t="s">
         <v>11</v>
       </c>
       <c r="K8" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="9" spans="10:18" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="9" spans="10:18">
       <c r="J9" t="s">
-        <v>510</v>
+        <v>608</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="10:12">
       <c r="J17" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="19" spans="10:12">
       <c r="J19" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="20" spans="10:12" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="20" spans="10:12">
       <c r="J20" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="K20" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="L20" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="21" spans="10:12" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="21" spans="10:12">
       <c r="J21" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="K21">
         <v>0.4</v>
@@ -6664,9 +8228,9 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="22" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="10:12">
       <c r="J22" t="s">
-        <v>514</v>
+        <v>612</v>
       </c>
       <c r="K22">
         <v>0.3</v>
@@ -6675,9 +8239,9 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="23" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="10:12">
       <c r="J23" t="s">
-        <v>515</v>
+        <v>613</v>
       </c>
       <c r="K23">
         <v>0.2</v>
@@ -6686,9 +8250,9 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="10:12">
       <c r="J24" t="s">
-        <v>516</v>
+        <v>614</v>
       </c>
       <c r="K24">
         <v>0.1</v>
@@ -6697,9 +8261,9 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="25" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="10:12">
       <c r="J25" t="s">
-        <v>517</v>
+        <v>615</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -6708,35 +8272,35 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="26" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="10:12">
       <c r="J26" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="29" spans="10:12" x14ac:dyDescent="0.25">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="29" spans="10:12">
       <c r="J29" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="31" spans="10:12" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="31" spans="10:12">
       <c r="J31" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="32" spans="10:12" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="32" spans="10:12">
       <c r="J32" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="K32" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="33" spans="10:12">
       <c r="J33" t="s">
-        <v>521</v>
+        <v>619</v>
       </c>
       <c r="K33">
         <v>0.4</v>
@@ -6745,7 +8309,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:12">
       <c r="J34" t="s">
         <v>56</v>
       </c>
@@ -6756,7 +8320,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:12">
       <c r="J35" t="s">
         <v>52</v>
       </c>
@@ -6767,9 +8331,9 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:12">
       <c r="J36" t="s">
-        <v>522</v>
+        <v>620</v>
       </c>
       <c r="K36">
         <v>0.1</v>
@@ -6778,9 +8342,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="10:12">
       <c r="J37" t="s">
-        <v>517</v>
+        <v>615</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -6789,71 +8353,71 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="10:12">
       <c r="J38" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="41" spans="10:12">
       <c r="J41" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="43" spans="10:12">
       <c r="J43" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="44" spans="10:12">
       <c r="J44" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="46" spans="10:12">
       <c r="J46" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="K46" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="L46" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="10:12">
       <c r="J47" t="s">
-        <v>527</v>
+        <v>625</v>
       </c>
       <c r="K47">
         <v>0.3</v>
       </c>
       <c r="L47" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="48" spans="10:12">
       <c r="J48" t="s">
-        <v>529</v>
+        <v>627</v>
       </c>
       <c r="K48">
         <v>0.2</v>
       </c>
       <c r="L48" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="49" spans="10:12">
       <c r="J49" t="s">
-        <v>531</v>
+        <v>629</v>
       </c>
       <c r="K49">
         <v>0.25</v>
       </c>
       <c r="L49" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="50" spans="10:12">
       <c r="J50" t="s">
         <v>35</v>
       </c>
@@ -6861,10 +8425,10 @@
         <v>0.15</v>
       </c>
       <c r="L50" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="51" spans="10:12">
       <c r="J51" t="s">
         <v>25</v>
       </c>
@@ -6872,43 +8436,44 @@
         <v>0.1</v>
       </c>
       <c r="L51" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="52" spans="10:12">
       <c r="J52" t="s">
         <v>39</v>
       </c>
       <c r="K52" t="s">
-        <v>534</v>
+        <v>632</v>
       </c>
       <c r="L52" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="53" spans="10:12">
       <c r="J53" t="s">
-        <v>536</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>537</v>
+        <v>635</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/documents/新需求/数值管理.xlsx
+++ b/documents/新需求/数值管理.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5-workspace\code\CombatDebugStudio\documents\新需求\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4-softworkspace\java\CombatDebugStudio\documents\新需求\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D882FC-ADEC-41FF-9F37-B64A88B509E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,24 +24,11 @@
     <sheet name="神器与法宝" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="742">
   <si>
     <t>B类属性</t>
   </si>
@@ -1355,7 +1343,7 @@
         <sz val="12"/>
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>普攻</t>
     </r>
@@ -1364,7 +1352,7 @@
         <sz val="12"/>
         <color rgb="FF222222"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>伤害+30%且必定触发1次连击(连击仅普攻可触发)</t>
     </r>
@@ -1968,20 +1956,420 @@
   </si>
   <si>
     <t>法宝主攻伐，神器主防守</t>
+  </si>
+  <si>
+    <t>连击伤害+20%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击之势</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击后下次普攻命中+15%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风连</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风势满层时连击伤害+15%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风势涌</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击后速度+5(上限3层)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>追风</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无影</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单次普攻连击达4段时，第5段+50%伤害且无视20%防御</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风势爆发</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗全部风势，使下次普攻必触发连击(每层+1次，上限3)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>战意</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击后叠战意(上限3)，每层+10%普攻伤害</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>120%伤害，消耗全部风势：每层+10%伤害并施加1层裂甲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>4段×60%，结束后下次普攻必连击2次</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>260%伤害，消耗目标裂甲每层+40%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>斗战·裂甲爆裂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>斗战·无影连斩</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>斗战·风势滔天</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻连击触发后连击伤害+30%且不衰减</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风狂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击有50%概率无视护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>开局免伤+10%；回合开始获15%最大气血护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>磐石体</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有盾反伤+20%；盾碎嘲讽1回合且反伤+30%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>怒目</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单次受伤≤25%最大气血；反伤无视防御</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>荆棘</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有盾时反弹+10%(结算受60%上限约束)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>厚土</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾值+20%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击后攻击者速度-10(2回合，上限2层)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>山震</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>免伤+10%；气血&lt;50%时护盾获取+50%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩势</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>怒目余威</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾碎时攻击者获"岩蚀"(-10%伤害，2回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动山</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>反伤30%转化护盾(每回合上限20%最大气血)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地之怒</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾碎时对全体敌人100%伤害并施加1层裂甲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>磐石盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>获20%最大气血护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>自身</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>100%伤害，嘲讽1回合</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>全体</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>震地</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>140%伤害，自身反伤+20%(2回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单体</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>反震击</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>守护击</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>120%伤害，最低血队友获10%护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩壁垒</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>免伤+15%(1回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>碎地震</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>同列110%伤害，目标速度-10(2回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾击</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有盾时+30%伤害(130%基础)1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>踏陷斩</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>130%伤害，目标有裂甲时+20%</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗当前盾50%，对目标造成等量真伤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>斥盾</t>
+  </si>
+  <si>
+    <t>全体友军获8%最大气血护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地之骨</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>160%伤害，全体敌人速度-20(2回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动·灭世震</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2回合：免伤+30%、反伤+30%，免疫1次控制</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动·山体</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>220%伤害，目标无护盾时眩晕1回合</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动·巨石阵</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2回合：友军免伤+15%，攻击者受击挂岩蚀</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动·地脉</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>领域</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>净化debuff，免伤+25%(2回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动·不屈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>120%伤害，本回合受击反伤按1.5倍结算</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>反震风暴</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>友军获20%护盾(取最高)，有盾期间免伤+10%(2回合)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>240%伤害，有盾时消耗护盾则伤害翻倍</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>山岳压</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘲讽全体2回合，本回合反伤+40%(封顶60%)；攻击者立即受1次反伤判定</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>怒目地狱</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>130%伤害，反伤+50%(2回合)，自身获20%护盾</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不动·地裂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴伤流 → 克制 → 反击流   (低频高爆发+斩杀，少喂反击，真伤收尾)</t>
+  </si>
+  <si>
+    <t>反击流 → 克制 → 连击流   (多段高频攻击疯狂喂反击)</t>
+  </si>
+  <si>
+    <t>连击流 → 克制 → 闪避流   (多段判定+裂甲削防+命中堆叠)</t>
+  </si>
+  <si>
+    <t>闪避流 → 克制 → 暴伤流   (高闪避使暴击判定落空，迷踪压命中)</t>
+  </si>
+  <si>
+    <t>站位</t>
+  </si>
+  <si>
+    <t>队伍职责</t>
+  </si>
+  <si>
+    <t>AI 优先级</t>
+  </si>
+  <si>
+    <t>后排主C</t>
+  </si>
+  <si>
+    <t>持续削甲+高频输出</t>
+  </si>
+  <si>
+    <t>防御最低 → 暴露后排</t>
+  </si>
+  <si>
+    <t>爆发+收割</t>
+  </si>
+  <si>
+    <t>气血最低 → 攻击最高</t>
+  </si>
+  <si>
+    <t>后排副C/干扰</t>
+  </si>
+  <si>
+    <t>切后+致盲干扰</t>
+  </si>
+  <si>
+    <t>暴露后排 → 速度最低</t>
+  </si>
+  <si>
+    <t>反击流</t>
+  </si>
+  <si>
+    <t>前排承伤副C</t>
+  </si>
+  <si>
+    <t>承伤+反制+嘲讽</t>
+  </si>
+  <si>
+    <t>维持嘲讽 → 保护低血队友</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1999,13 +2387,13 @@
       <sz val="10"/>
       <color rgb="FFF2858C"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2016,351 +2404,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2368,255 +2441,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2644,7 +2475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2656,90 +2487,168 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -2750,7 +2659,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2778,154 +2687,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3175,32 +2970,32 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D16:Z63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="16.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="31.1083333333333" customWidth="1"/>
-    <col min="10" max="13" width="16.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.109375" customWidth="1"/>
+    <col min="10" max="13" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="4:4">
+    <row r="16" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D16" s="10"/>
     </row>
-    <row r="31" spans="8:26">
-      <c r="H31" s="2" t="s">
+    <row r="31" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H31" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
       <c r="S31" t="s">
         <v>1</v>
       </c>
@@ -3226,7 +3021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="8:26">
+    <row r="32" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H32" s="11" t="s">
         <v>9</v>
       </c>
@@ -3265,7 +3060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="8:26">
+    <row r="33" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
         <v>16</v>
       </c>
@@ -3303,7 +3098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="8:26">
+    <row r="34" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
         <v>22</v>
       </c>
@@ -3341,7 +3136,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="8:26">
+    <row r="35" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H35" t="s">
         <v>26</v>
       </c>
@@ -3379,7 +3174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="8:26">
+    <row r="36" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H36" t="s">
         <v>31</v>
       </c>
@@ -3417,7 +3212,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="8:26">
+    <row r="37" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H37" t="s">
         <v>36</v>
       </c>
@@ -3455,17 +3250,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="8:26">
-      <c r="H39" s="2" t="s">
+    <row r="39" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H39" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="8:26">
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+    </row>
+    <row r="40" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H40" s="11" t="s">
         <v>9</v>
       </c>
@@ -3480,7 +3275,7 @@
       </c>
       <c r="L40" s="11"/>
     </row>
-    <row r="41" spans="8:26">
+    <row r="41" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H41" t="s">
         <v>41</v>
       </c>
@@ -3494,7 +3289,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="8:26">
+    <row r="42" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H42" t="s">
         <v>45</v>
       </c>
@@ -3508,7 +3303,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="8:26">
+    <row r="43" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H43" t="s">
         <v>47</v>
       </c>
@@ -3522,7 +3317,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="8:26">
+    <row r="44" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H44" t="s">
         <v>51</v>
       </c>
@@ -3536,7 +3331,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="8:26">
+    <row r="45" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H45" t="s">
         <v>54</v>
       </c>
@@ -3550,17 +3345,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="8:26">
-      <c r="H47" s="2" t="s">
+    <row r="47" spans="8:26" x14ac:dyDescent="0.25">
+      <c r="H47" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-    </row>
-    <row r="48" spans="8:26">
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+    </row>
+    <row r="48" spans="8:26" x14ac:dyDescent="0.25">
       <c r="H48" s="11" t="s">
         <v>9</v>
       </c>
@@ -3575,7 +3370,7 @@
       </c>
       <c r="L48" s="11"/>
     </row>
-    <row r="49" spans="8:13">
+    <row r="49" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H49" t="s">
         <v>59</v>
       </c>
@@ -3589,7 +3384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="8:13">
+    <row r="50" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H50" t="s">
         <v>62</v>
       </c>
@@ -3603,7 +3398,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="8:13">
+    <row r="51" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H51" t="s">
         <v>66</v>
       </c>
@@ -3617,7 +3412,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="8:13">
+    <row r="52" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H52" t="s">
         <v>67</v>
       </c>
@@ -3631,17 +3426,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="8:13">
-      <c r="H54" s="2" t="s">
+    <row r="54" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H54" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-    </row>
-    <row r="55" spans="8:13">
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+    </row>
+    <row r="55" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H55" s="11" t="s">
         <v>9</v>
       </c>
@@ -3656,7 +3451,7 @@
       </c>
       <c r="L55" s="11"/>
     </row>
-    <row r="56" spans="8:13">
+    <row r="56" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H56" t="s">
         <v>69</v>
       </c>
@@ -3670,7 +3465,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="57" spans="8:13">
+    <row r="57" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H57" t="s">
         <v>72</v>
       </c>
@@ -3684,17 +3479,17 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="8:13">
-      <c r="H59" s="2" t="s">
+    <row r="59" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H59" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="8:13">
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+    </row>
+    <row r="60" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H60" s="11" t="s">
         <v>9</v>
       </c>
@@ -3708,7 +3503,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="8:13">
+    <row r="61" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H61" t="s">
         <v>77</v>
       </c>
@@ -3722,7 +3517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="8:13">
+    <row r="62" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H62" t="s">
         <v>79</v>
       </c>
@@ -3736,7 +3531,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="8:13">
+    <row r="63" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H63" t="s">
         <v>82</v>
       </c>
@@ -3758,27 +3553,26 @@
     <mergeCell ref="H54:M54"/>
     <mergeCell ref="H59:M59"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:O108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.775" customWidth="1"/>
-    <col min="3" max="3" width="40.8833333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.8833333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="12.6666666666667"/>
-    <col min="10" max="16" width="10.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="3" max="3" width="40.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625"/>
+    <col min="10" max="16" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>84</v>
       </c>
@@ -3794,8 +3588,8 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -3821,8 +3615,8 @@
       </c>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
       <c r="B4" s="2" t="s">
         <v>94</v>
       </c>
@@ -3846,8 +3640,8 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="2"/>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
@@ -3871,8 +3665,8 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="2"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
       <c r="B6" s="2" t="s">
         <v>108</v>
       </c>
@@ -3884,12 +3678,12 @@
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>111</v>
       </c>
@@ -3906,8 +3700,8 @@
       <c r="H8" s="2"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>112</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -3930,8 +3724,8 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="2"/>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
       <c r="B10" s="2" t="s">
         <v>94</v>
       </c>
@@ -3950,8 +3744,8 @@
       <c r="J10" s="9"/>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="2"/>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
       <c r="B11" s="2" t="s">
         <v>101</v>
       </c>
@@ -3970,8 +3764,8 @@
       <c r="J11" s="9"/>
       <c r="O11" s="6"/>
     </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="2"/>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
       <c r="B12" s="2" t="s">
         <v>108</v>
       </c>
@@ -3981,19 +3775,19 @@
       <c r="J12" s="9"/>
       <c r="O12" s="6"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="J13" s="9"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="J14" s="9"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>124</v>
       </c>
@@ -4011,8 +3805,8 @@
       <c r="J15" s="9"/>
       <c r="O15" s="6"/>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>125</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -4035,8 +3829,8 @@
       </c>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="2"/>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
       <c r="B17" s="2" t="s">
         <v>101</v>
       </c>
@@ -4044,11 +3838,11 @@
         <v>129</v>
       </c>
       <c r="J17" s="9"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="2"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
       <c r="B18" s="2" t="s">
         <v>108</v>
       </c>
@@ -4057,12 +3851,12 @@
       </c>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>131</v>
       </c>
@@ -4079,8 +3873,8 @@
       <c r="H20" s="2"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -4100,8 +3894,8 @@
       </c>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="2"/>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
       <c r="B22" s="2"/>
       <c r="C22" t="s">
         <v>133</v>
@@ -4120,12 +3914,12 @@
       </c>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>137</v>
       </c>
@@ -4142,8 +3936,8 @@
       <c r="H24" s="2"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>138</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -4157,12 +3951,12 @@
       </c>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="2"/>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
       <c r="B26" s="2"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>139</v>
       </c>
@@ -4174,8 +3968,8 @@
       </c>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
         <v>140</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -4195,8 +3989,8 @@
       </c>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="2"/>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
       <c r="B29" s="2" t="s">
         <v>94</v>
       </c>
@@ -4205,12 +3999,12 @@
       </c>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>144</v>
       </c>
@@ -4227,8 +4021,8 @@
       <c r="H31" s="2"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
         <v>145</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -4239,12 +4033,12 @@
       </c>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="2"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="13"/>
       <c r="B33" s="2"/>
       <c r="J33" s="9"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>147</v>
       </c>
@@ -4261,7 +4055,7 @@
       <c r="H34" s="2"/>
       <c r="J34" s="9"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>148</v>
       </c>
@@ -4282,7 +4076,7 @@
       </c>
       <c r="J35" s="9"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" t="s">
@@ -4299,7 +4093,7 @@
       </c>
       <c r="J36" s="9"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" t="s">
@@ -4310,15 +4104,15 @@
       </c>
       <c r="J37" s="9"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="J38" s="9"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J39" s="9"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -4336,7 +4130,7 @@
       </c>
       <c r="J40" s="9"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -4348,7 +4142,7 @@
       </c>
       <c r="J41" s="9"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -4360,7 +4154,7 @@
       </c>
       <c r="J42" s="9"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>90</v>
       </c>
@@ -4372,7 +4166,7 @@
       </c>
       <c r="J43" s="9"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -4387,7 +4181,7 @@
       </c>
       <c r="J44" s="9"/>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>92</v>
       </c>
@@ -4402,7 +4196,7 @@
       </c>
       <c r="J45" s="9"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -4417,7 +4211,7 @@
       </c>
       <c r="J46" s="9"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -4435,7 +4229,7 @@
       </c>
       <c r="J47" s="9"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>96</v>
       </c>
@@ -4453,7 +4247,7 @@
       </c>
       <c r="J48" s="9"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -4471,7 +4265,7 @@
       </c>
       <c r="J49" s="9"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -4489,7 +4283,7 @@
       </c>
       <c r="J50" s="9"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>99</v>
       </c>
@@ -4507,7 +4301,7 @@
       </c>
       <c r="J51" s="9"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -4525,7 +4319,7 @@
       </c>
       <c r="J52" s="9"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>102</v>
       </c>
@@ -4540,7 +4334,7 @@
       </c>
       <c r="J53" s="9"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -4555,7 +4349,7 @@
       </c>
       <c r="J54" s="9"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -4570,7 +4364,7 @@
       </c>
       <c r="J55" s="9"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>105</v>
       </c>
@@ -4588,7 +4382,7 @@
       </c>
       <c r="J56" s="9"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>106</v>
       </c>
@@ -4606,7 +4400,7 @@
       </c>
       <c r="J57" s="9"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>107</v>
       </c>
@@ -4624,7 +4418,7 @@
       </c>
       <c r="J58" s="9"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>109</v>
       </c>
@@ -4639,7 +4433,7 @@
       </c>
       <c r="J59" s="9"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>110</v>
       </c>
@@ -4654,7 +4448,7 @@
       </c>
       <c r="J60" s="9"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -4681,7 +4475,7 @@
       </c>
       <c r="J61" s="9"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>22</v>
       </c>
@@ -4708,7 +4502,7 @@
       </c>
       <c r="J62" s="9"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>31</v>
       </c>
@@ -4726,7 +4520,7 @@
       </c>
       <c r="J63" s="9"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -4741,7 +4535,7 @@
       </c>
       <c r="J64" s="9"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>114</v>
       </c>
@@ -4759,7 +4553,7 @@
       </c>
       <c r="J65" s="9"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -4774,7 +4568,7 @@
       </c>
       <c r="J66" s="9"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>116</v>
       </c>
@@ -4792,7 +4586,7 @@
       </c>
       <c r="J67" s="9"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>117</v>
       </c>
@@ -4807,7 +4601,7 @@
       </c>
       <c r="J68" s="9"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>118</v>
       </c>
@@ -4825,7 +4619,7 @@
       </c>
       <c r="J69" s="9"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>119</v>
       </c>
@@ -4840,7 +4634,7 @@
       </c>
       <c r="J70" s="9"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>120</v>
       </c>
@@ -4858,7 +4652,7 @@
       </c>
       <c r="J71" s="9"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>121</v>
       </c>
@@ -4872,7 +4666,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>122</v>
       </c>
@@ -4886,7 +4680,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>123</v>
       </c>
@@ -4900,7 +4694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>126</v>
       </c>
@@ -4911,7 +4705,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>41</v>
       </c>
@@ -4925,7 +4719,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>51</v>
       </c>
@@ -4939,7 +4733,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>127</v>
       </c>
@@ -4953,7 +4747,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>128</v>
       </c>
@@ -4967,7 +4761,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>129</v>
       </c>
@@ -4981,7 +4775,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>130</v>
       </c>
@@ -5007,7 +4801,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>59</v>
       </c>
@@ -5033,7 +4827,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>62</v>
       </c>
@@ -5059,7 +4853,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>66</v>
       </c>
@@ -5070,7 +4864,7 @@
         <v>228</v>
       </c>
       <c r="D84" s="4">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E84" t="s">
         <v>214</v>
@@ -5085,7 +4879,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>67</v>
       </c>
@@ -5111,7 +4905,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>133</v>
       </c>
@@ -5137,7 +4931,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>134</v>
       </c>
@@ -5163,7 +4957,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -5189,7 +4983,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>54</v>
       </c>
@@ -5215,7 +5009,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>136</v>
       </c>
@@ -5229,7 +5023,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>69</v>
       </c>
@@ -5240,7 +5034,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>72</v>
       </c>
@@ -5251,7 +5045,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>242</v>
       </c>
@@ -5277,7 +5071,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>244</v>
       </c>
@@ -5303,7 +5097,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>246</v>
       </c>
@@ -5329,7 +5123,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>249</v>
       </c>
@@ -5343,7 +5137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>251</v>
       </c>
@@ -5357,7 +5151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>253</v>
       </c>
@@ -5371,7 +5165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>255</v>
       </c>
@@ -5397,7 +5191,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>257</v>
       </c>
@@ -5411,7 +5205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>259</v>
       </c>
@@ -5437,7 +5231,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>264</v>
       </c>
@@ -5463,7 +5257,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>266</v>
       </c>
@@ -5477,7 +5271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>268</v>
       </c>
@@ -5503,7 +5297,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>274</v>
       </c>
@@ -5529,7 +5323,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>276</v>
       </c>
@@ -5555,7 +5349,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>278</v>
       </c>
@@ -5581,7 +5375,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>280</v>
       </c>
@@ -5609,31 +5403,30 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A32:A33"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A32:A33"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AB207"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="12.6666666666667" customWidth="1"/>
+    <col min="1" max="7" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -5656,21 +5449,21 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="13"/>
       <c r="D2" t="s">
         <v>287</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="13"/>
       <c r="G2" t="s">
         <v>287</v>
       </c>
@@ -5687,7 +5480,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>12</v>
       </c>
@@ -5736,7 +5529,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5785,7 +5578,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5831,7 +5624,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -5867,7 +5660,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5903,7 +5696,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -5939,7 +5732,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D9">
         <f>SUM(D3:D8)</f>
         <v>33</v>
@@ -5954,10 +5747,10 @@
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5975,7 +5768,7 @@
       </c>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -5995,7 +5788,7 @@
       </c>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -6011,7 +5804,7 @@
       </c>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -6027,7 +5820,7 @@
       </c>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -6042,7 +5835,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -6057,7 +5850,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -6073,13 +5866,13 @@
       </c>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C21">
         <f>SUM(C15:C20)</f>
         <v>390</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>315</v>
       </c>
@@ -6089,87 +5882,87 @@
       </c>
       <c r="Q22" s="2"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="Q27" s="2"/>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="Q31" s="2"/>
     </row>
-    <row r="38" spans="17:17">
+    <row r="38" spans="17:17" x14ac:dyDescent="0.25">
       <c r="Q38" s="2"/>
     </row>
-    <row r="41" spans="17:17">
+    <row r="41" spans="17:17" x14ac:dyDescent="0.25">
       <c r="Q41" s="2"/>
     </row>
-    <row r="49" spans="12:13">
+    <row r="49" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="12:13">
+    <row r="50" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
     </row>
-    <row r="51" spans="12:13">
+    <row r="51" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="12:13">
+    <row r="52" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="12:13">
+    <row r="53" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="12:13">
+    <row r="54" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="12:13">
+    <row r="55" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="12:13">
+    <row r="56" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="12:13">
+    <row r="57" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="12:13">
+    <row r="58" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="12:13">
+    <row r="59" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="12:13">
+    <row r="60" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="12:13">
+    <row r="61" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="12:13">
+    <row r="62" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="12:13">
+    <row r="63" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="12:13">
+    <row r="64" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="11:28">
+    <row r="65" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="11:28">
+    <row r="66" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L66" s="2" t="s">
         <v>316</v>
       </c>
@@ -6182,22 +5975,22 @@
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
     </row>
-    <row r="67" spans="11:28">
+    <row r="67" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="11:28">
+    <row r="68" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="11:28">
+    <row r="69" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="70" spans="11:28">
+    <row r="70" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M70" s="2" t="s">
         <v>318</v>
       </c>
@@ -6206,7 +5999,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="71" spans="11:28">
+    <row r="71" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M71" s="2" t="s">
         <v>318</v>
       </c>
@@ -6215,7 +6008,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="72" spans="11:28">
+    <row r="72" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M72" s="2" t="s">
         <v>318</v>
       </c>
@@ -6224,7 +6017,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="11:28">
+    <row r="73" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M73" s="2" t="s">
         <v>318</v>
       </c>
@@ -6233,7 +6026,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="74" spans="11:28">
+    <row r="74" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M74" s="2" t="s">
         <v>318</v>
       </c>
@@ -6242,7 +6035,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="75" spans="11:28">
+    <row r="75" spans="11:28" x14ac:dyDescent="0.25">
       <c r="M75" s="2" t="s">
         <v>318</v>
       </c>
@@ -6251,7 +6044,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="76" spans="11:28">
+    <row r="76" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="U76" t="s">
@@ -6270,40 +6063,40 @@
         <v>329</v>
       </c>
     </row>
-    <row r="77" spans="11:28">
+    <row r="77" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
     </row>
-    <row r="78" spans="11:28">
+    <row r="78" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
     </row>
-    <row r="79" spans="11:28">
+    <row r="79" spans="11:28" x14ac:dyDescent="0.25">
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="80" spans="11:28">
+    <row r="80" spans="11:28" x14ac:dyDescent="0.25">
       <c r="K80" t="s">
         <v>331</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="11:20">
+    <row r="81" spans="11:20" x14ac:dyDescent="0.25">
       <c r="K81" t="s">
         <v>332</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="11:20">
+    <row r="82" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" ht="14.4" customHeight="1" spans="11:20">
+    <row r="83" spans="11:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K83" t="s">
         <v>113</v>
       </c>
@@ -6323,7 +6116,7 @@
       <c r="S83" s="8"/>
       <c r="T83" s="8"/>
     </row>
-    <row r="84" spans="11:20">
+    <row r="84" spans="11:20" x14ac:dyDescent="0.25">
       <c r="K84" t="s">
         <v>122</v>
       </c>
@@ -6332,7 +6125,7 @@
       </c>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="11:20">
+    <row r="85" spans="11:20" x14ac:dyDescent="0.25">
       <c r="K85" t="s">
         <v>334</v>
       </c>
@@ -6341,15 +6134,15 @@
       </c>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="11:20">
+    <row r="86" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="11:20">
+    <row r="87" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="11:20">
+    <row r="88" spans="11:20" x14ac:dyDescent="0.25">
       <c r="K88" t="s">
         <v>133</v>
       </c>
@@ -6359,35 +6152,35 @@
         <v>335</v>
       </c>
     </row>
-    <row r="89" spans="11:20">
+    <row r="89" spans="11:20" x14ac:dyDescent="0.25">
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="201" spans="12:13">
+    <row r="201" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
     </row>
-    <row r="202" spans="12:13">
+    <row r="202" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
     </row>
-    <row r="203" spans="12:13">
+    <row r="203" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
     </row>
-    <row r="204" spans="12:13">
+    <row r="204" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
     </row>
-    <row r="205" spans="12:13">
+    <row r="205" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
     </row>
-    <row r="206" spans="12:13">
+    <row r="206" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
     </row>
-    <row r="207" spans="12:13">
+    <row r="207" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
     </row>
@@ -6396,22 +6189,21 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A16:X40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="12" width="8.66666666666667" customWidth="1"/>
+    <col min="7" max="12" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="16" spans="7:8">
+    <row r="16" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G16" t="s">
         <v>336</v>
       </c>
@@ -6419,7 +6211,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G17" t="s">
         <v>191</v>
       </c>
@@ -6433,7 +6225,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G18" t="s">
         <v>341</v>
       </c>
@@ -6447,7 +6239,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G19" t="s">
         <v>345</v>
       </c>
@@ -6461,7 +6253,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
         <v>348</v>
       </c>
@@ -6475,17 +6267,17 @@
         <v>351</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G22" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>353</v>
       </c>
@@ -6502,7 +6294,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>358</v>
       </c>
@@ -6522,7 +6314,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>362</v>
       </c>
@@ -6554,7 +6346,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>365</v>
       </c>
@@ -6586,7 +6378,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>367</v>
       </c>
@@ -6606,7 +6398,7 @@
         <v>89</v>
       </c>
       <c r="I29" s="4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J29" t="s">
         <v>107</v>
@@ -6621,7 +6413,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>371</v>
       </c>
@@ -6647,7 +6439,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G31" t="s">
         <v>343</v>
       </c>
@@ -6661,7 +6453,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G32" t="s">
         <v>344</v>
       </c>
@@ -6675,13 +6467,13 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
       <c r="G33" t="s">
         <v>346</v>
       </c>
@@ -6695,7 +6487,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
@@ -6715,7 +6507,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2</v>
       </c>
@@ -6732,7 +6524,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6743,7 +6535,7 @@
         <v>93</v>
       </c>
       <c r="I36" s="4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J36" t="s">
         <v>62</v>
@@ -6758,7 +6550,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>4</v>
       </c>
@@ -6778,7 +6570,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5</v>
       </c>
@@ -6798,12 +6590,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G39" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G40" t="s">
         <v>352</v>
       </c>
@@ -6836,22 +6628,21 @@
   <mergeCells count="1">
     <mergeCell ref="A33:D33"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:Q63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:Q128"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="63.125" customWidth="1"/>
-    <col min="14" max="19" width="20.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="63.109375" customWidth="1"/>
+    <col min="14" max="19" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>376</v>
       </c>
@@ -6859,7 +6650,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>378</v>
       </c>
@@ -6870,27 +6661,27 @@
         <v>380</v>
       </c>
     </row>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E3" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>385</v>
       </c>
@@ -6902,7 +6693,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>388</v>
       </c>
@@ -6910,7 +6701,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>390</v>
       </c>
@@ -6918,7 +6709,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>392</v>
       </c>
@@ -6926,7 +6717,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>394</v>
       </c>
@@ -6934,7 +6725,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>396</v>
       </c>
@@ -6942,7 +6733,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="17" spans="2:17">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>386</v>
       </c>
@@ -6950,7 +6741,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>399</v>
       </c>
@@ -6961,7 +6752,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N21" t="s">
         <v>192</v>
       </c>
@@ -6975,7 +6766,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N22" t="s">
         <v>404</v>
       </c>
@@ -6989,7 +6780,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N23" t="s">
         <v>408</v>
       </c>
@@ -7003,7 +6794,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N24" t="s">
         <v>412</v>
       </c>
@@ -7017,7 +6808,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N25" t="s">
         <v>416</v>
       </c>
@@ -7031,7 +6822,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N26" t="s">
         <v>420</v>
       </c>
@@ -7045,7 +6836,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>424</v>
       </c>
@@ -7059,7 +6850,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>1</v>
       </c>
@@ -7073,7 +6864,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>2</v>
       </c>
@@ -7087,7 +6878,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>3</v>
       </c>
@@ -7101,7 +6892,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:17">
+    <row r="32" spans="2:17" ht="15" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>4</v>
       </c>
@@ -7115,7 +6906,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>5</v>
       </c>
@@ -7132,7 +6923,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="34" spans="2:15">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>6</v>
       </c>
@@ -7146,7 +6937,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="35" spans="2:15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>7</v>
       </c>
@@ -7166,7 +6957,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="36" spans="2:15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>8</v>
       </c>
@@ -7186,7 +6977,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="37" spans="2:15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>9</v>
       </c>
@@ -7206,7 +6997,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="38" spans="2:15">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>10</v>
       </c>
@@ -7226,7 +7017,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="39" spans="2:15">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="N39" t="s">
         <v>458</v>
       </c>
@@ -7234,7 +7025,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="40" spans="2:15">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>424</v>
       </c>
@@ -7254,7 +7045,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="2:15">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>1</v>
       </c>
@@ -7277,7 +7068,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="42" spans="2:15">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>2</v>
       </c>
@@ -7300,7 +7091,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="43" spans="2:15">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>3</v>
       </c>
@@ -7323,7 +7114,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="44" spans="2:15">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>4</v>
       </c>
@@ -7346,7 +7137,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="45" spans="2:15">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>5</v>
       </c>
@@ -7369,7 +7160,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="46" spans="2:15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>6</v>
       </c>
@@ -7392,7 +7183,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="47" spans="2:15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>7</v>
       </c>
@@ -7409,7 +7200,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="48" spans="2:15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>8</v>
       </c>
@@ -7426,7 +7217,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>9</v>
       </c>
@@ -7443,7 +7234,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>10</v>
       </c>
@@ -7460,7 +7251,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>424</v>
       </c>
@@ -7477,7 +7268,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>1</v>
       </c>
@@ -7494,7 +7285,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>2</v>
       </c>
@@ -7511,7 +7302,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>3</v>
       </c>
@@ -7528,7 +7319,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>4</v>
       </c>
@@ -7545,7 +7336,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>5</v>
       </c>
@@ -7562,7 +7353,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>6</v>
       </c>
@@ -7579,7 +7370,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>7</v>
       </c>
@@ -7596,7 +7387,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>8</v>
       </c>
@@ -7613,7 +7404,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>9</v>
       </c>
@@ -7630,7 +7421,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>10</v>
       </c>
@@ -7647,19 +7438,512 @@
         <v>514</v>
       </c>
     </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B69" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B70" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B71" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B74" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B76" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B78" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="15" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B83" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B91" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="15" t="s">
+        <v>684</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B96" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B97" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="15"/>
+      <c r="B101" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D103" s="15"/>
+      <c r="E103" s="15"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D104" s="15"/>
+      <c r="E104" s="15"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D105" s="15"/>
+      <c r="E105" s="15"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B107" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B108" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B109" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="D109" s="15"/>
+      <c r="E109" s="15" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B110" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B111" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B112" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B114" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B115" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B116" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>192</v>
+      </c>
+      <c r="C124" t="s">
+        <v>727</v>
+      </c>
+      <c r="D124" t="s">
+        <v>728</v>
+      </c>
+      <c r="E124" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>404</v>
+      </c>
+      <c r="C125" t="s">
+        <v>730</v>
+      </c>
+      <c r="D125" t="s">
+        <v>731</v>
+      </c>
+      <c r="E125" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>408</v>
+      </c>
+      <c r="C126" t="s">
+        <v>730</v>
+      </c>
+      <c r="D126" t="s">
+        <v>733</v>
+      </c>
+      <c r="E126" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>416</v>
+      </c>
+      <c r="C127" t="s">
+        <v>735</v>
+      </c>
+      <c r="D127" t="s">
+        <v>736</v>
+      </c>
+      <c r="E127" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>738</v>
+      </c>
+      <c r="C128" t="s">
+        <v>739</v>
+      </c>
+      <c r="D128" t="s">
+        <v>740</v>
+      </c>
+      <c r="E128" t="s">
+        <v>741</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="I11:S40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="11" spans="9:19">
+    <row r="11" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I11" t="s">
         <v>515</v>
       </c>
@@ -7673,7 +7957,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="9:19">
+    <row r="13" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>519</v>
       </c>
@@ -7693,7 +7977,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="9:19">
+    <row r="14" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>522</v>
       </c>
@@ -7713,7 +7997,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="15" spans="9:19">
+    <row r="15" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>69</v>
       </c>
@@ -7733,7 +8017,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="16" spans="9:19">
+    <row r="16" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
         <v>82</v>
       </c>
@@ -7753,7 +8037,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="17" spans="9:19">
+    <row r="17" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I17" t="s">
         <v>530</v>
       </c>
@@ -7773,7 +8057,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="18" spans="9:19">
+    <row r="18" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I18" t="s">
         <v>533</v>
       </c>
@@ -7793,7 +8077,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="19" spans="9:19">
+    <row r="19" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I19" t="s">
         <v>26</v>
       </c>
@@ -7813,7 +8097,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="20" spans="9:19">
+    <row r="20" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>538</v>
       </c>
@@ -7833,7 +8117,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="21" spans="9:19">
+    <row r="21" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>541</v>
       </c>
@@ -7853,7 +8137,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="22" spans="9:19">
+    <row r="22" spans="9:19" x14ac:dyDescent="0.25">
       <c r="Q22" t="s">
         <v>26</v>
       </c>
@@ -7864,7 +8148,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="23" spans="9:19">
+    <row r="23" spans="9:19" x14ac:dyDescent="0.25">
       <c r="Q23" t="s">
         <v>69</v>
       </c>
@@ -7875,7 +8159,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="25" spans="9:19">
+    <row r="25" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I25" t="s">
         <v>30</v>
       </c>
@@ -7889,7 +8173,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="26" spans="9:19">
+    <row r="26" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
         <v>549</v>
       </c>
@@ -7903,7 +8187,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="27" spans="9:19">
+    <row r="27" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>553</v>
       </c>
@@ -7917,7 +8201,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="28" spans="9:19">
+    <row r="28" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I28" t="s">
         <v>557</v>
       </c>
@@ -7931,7 +8215,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="29" spans="9:19">
+    <row r="29" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I29" t="s">
         <v>561</v>
       </c>
@@ -7945,7 +8229,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="30" spans="9:19">
+    <row r="30" spans="9:19" x14ac:dyDescent="0.25">
       <c r="I30" t="s">
         <v>565</v>
       </c>
@@ -7953,25 +8237,25 @@
         <v>566</v>
       </c>
     </row>
-    <row r="35" spans="9:13">
+    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I35" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="9:13">
+    <row r="36" spans="9:13" ht="15.6" x14ac:dyDescent="0.25">
       <c r="I36" s="1" t="s">
         <v>568</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="13" t="s">
         <v>569</v>
       </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="9:13">
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+    </row>
+    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I37" t="s">
         <v>570</v>
       </c>
@@ -7979,7 +8263,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="9:13">
+    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I38" t="s">
         <v>571</v>
       </c>
@@ -7987,7 +8271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="9:13">
+    <row r="39" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I39" t="s">
         <v>572</v>
       </c>
@@ -7995,7 +8279,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="9:13">
+    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I40" t="s">
         <v>573</v>
       </c>
@@ -8007,23 +8291,22 @@
   <mergeCells count="1">
     <mergeCell ref="K36:M36"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="H8:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="8" spans="8:16">
+    <row r="8" spans="8:16" x14ac:dyDescent="0.25">
       <c r="O8" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="10" spans="8:16">
+    <row r="10" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H10" t="s">
         <v>575</v>
       </c>
@@ -8031,7 +8314,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="11" spans="8:16">
+    <row r="11" spans="8:16" x14ac:dyDescent="0.25">
       <c r="O11" t="s">
         <v>577</v>
       </c>
@@ -8039,7 +8322,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="12" spans="8:16">
+    <row r="12" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
         <v>577</v>
       </c>
@@ -8059,7 +8342,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="13" spans="8:16">
+    <row r="13" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>580</v>
       </c>
@@ -8079,7 +8362,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="14" spans="8:16">
+    <row r="14" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>585</v>
       </c>
@@ -8099,7 +8382,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="15" spans="8:16">
+    <row r="15" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H15" t="s">
         <v>590</v>
       </c>
@@ -8119,7 +8402,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="16" spans="8:16">
+    <row r="16" spans="8:16" x14ac:dyDescent="0.25">
       <c r="H16" t="s">
         <v>594</v>
       </c>
@@ -8137,23 +8420,22 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="J4:R53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="10:18">
+    <row r="4" spans="10:18" x14ac:dyDescent="0.25">
       <c r="R4" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="5" spans="10:18">
+    <row r="5" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J5" t="s">
         <v>601</v>
       </c>
@@ -8161,7 +8443,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="6" spans="10:18">
+    <row r="6" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J6" t="s">
         <v>603</v>
       </c>
@@ -8172,7 +8454,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="7" spans="10:18">
+    <row r="7" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J7" t="s">
         <v>10</v>
       </c>
@@ -8180,7 +8462,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="8" spans="10:18">
+    <row r="8" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J8" t="s">
         <v>11</v>
       </c>
@@ -8188,7 +8470,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="9" spans="10:18">
+    <row r="9" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
         <v>608</v>
       </c>
@@ -8196,17 +8478,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="10:12">
+    <row r="17" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J17" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="19" spans="10:12">
+    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="20" spans="10:12">
+    <row r="20" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>162</v>
       </c>
@@ -8217,7 +8499,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="21" spans="10:12">
+    <row r="21" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J21" t="s">
         <v>191</v>
       </c>
@@ -8228,7 +8510,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="22" spans="10:12">
+    <row r="22" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
         <v>612</v>
       </c>
@@ -8239,7 +8521,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="23" spans="10:12">
+    <row r="23" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
         <v>613</v>
       </c>
@@ -8250,7 +8532,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="10:12">
+    <row r="24" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
         <v>614</v>
       </c>
@@ -8261,7 +8543,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="25" spans="10:12">
+    <row r="25" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J25" t="s">
         <v>615</v>
       </c>
@@ -8272,22 +8554,22 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="26" spans="10:12">
+    <row r="26" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J26" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="29" spans="10:12">
+    <row r="29" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J29" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="31" spans="10:12">
+    <row r="31" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="32" spans="10:12">
+    <row r="32" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
         <v>162</v>
       </c>
@@ -8298,7 +8580,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="33" spans="10:12">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J33" t="s">
         <v>619</v>
       </c>
@@ -8309,7 +8591,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" spans="10:12">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J34" t="s">
         <v>56</v>
       </c>
@@ -8320,7 +8602,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="10:12">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J35" t="s">
         <v>52</v>
       </c>
@@ -8331,7 +8613,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="10:12">
+    <row r="36" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J36" t="s">
         <v>620</v>
       </c>
@@ -8342,7 +8624,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="37" spans="10:12">
+    <row r="37" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J37" t="s">
         <v>615</v>
       </c>
@@ -8353,27 +8635,27 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="10:12">
+    <row r="38" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J38" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="41" spans="10:12">
+    <row r="41" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J41" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="43" spans="10:12">
+    <row r="43" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J43" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="44" spans="10:12">
+    <row r="44" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J44" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="46" spans="10:12">
+    <row r="46" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J46" t="s">
         <v>162</v>
       </c>
@@ -8384,7 +8666,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="47" spans="10:12">
+    <row r="47" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J47" t="s">
         <v>625</v>
       </c>
@@ -8395,7 +8677,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="48" spans="10:12">
+    <row r="48" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J48" t="s">
         <v>627</v>
       </c>
@@ -8406,7 +8688,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="49" spans="10:12">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J49" t="s">
         <v>629</v>
       </c>
@@ -8417,7 +8699,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="50" spans="10:12">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J50" t="s">
         <v>35</v>
       </c>
@@ -8428,7 +8710,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="51" spans="10:12">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J51" t="s">
         <v>25</v>
       </c>
@@ -8439,7 +8721,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="52" spans="10:12">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J52" t="s">
         <v>39</v>
       </c>
@@ -8450,30 +8732,29 @@
         <v>633</v>
       </c>
     </row>
-    <row r="53" spans="10:12">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J53" t="s">
         <v>634</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>635</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>